--- a/resources/blank_bracket.xlsx
+++ b/resources/blank_bracket.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29826"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amgal\Documents\Data Science\KingfisherCourt\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B652936D-E5A4-4AB2-81B5-CADBB450954E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5826F305-93D8-4094-A99D-F9B842813624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3840" yWindow="3840" windowWidth="23040" windowHeight="12120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4512" yWindow="948" windowWidth="23040" windowHeight="15096" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Team_Links" sheetId="6" r:id="rId1"/>
@@ -6929,17 +6929,110 @@
     <xf numFmtId="0" fontId="46" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="33" fillId="6" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="6" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="37" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6974,33 +7067,6 @@
     <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7018,72 +7084,6 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="6" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -7091,9 +7091,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="10">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -7122,6 +7119,9 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -8376,7 +8376,7 @@
     <tableColumn id="2" xr3:uid="{767B4EBC-1D6B-4D8D-AC6F-5DAFFC73A49A}" uniqueName="2" name="School" queryTableFieldId="2" dataDxfId="9"/>
     <tableColumn id="3" xr3:uid="{714CBA45-7DDA-43B9-86A4-4C5947403F44}" uniqueName="3" name="Link" queryTableFieldId="3" dataDxfId="8"/>
     <tableColumn id="4" xr3:uid="{51A37069-17DD-4524-B091-9E772D95E297}" uniqueName="4" name="GameLogs" queryTableFieldId="4" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{16FD7BE5-C80E-4178-848D-B547195018E8}" uniqueName="6" name="PartialLink" queryTableFieldId="6" dataDxfId="0">
+    <tableColumn id="6" xr3:uid="{16FD7BE5-C80E-4178-848D-B547195018E8}" uniqueName="6" name="PartialLink" queryTableFieldId="6" dataDxfId="6">
       <calculatedColumnFormula array="1">_xlfn.TEXTSPLIT(
 _xlfn.TEXTSPLIT(Team_Links[[#This Row],[GameLogs]],"https://www.sports-reference.com/cbb/schools/",,TRUE,0,), "/",,TRUE,0)</calculatedColumnFormula>
     </tableColumn>
@@ -8386,7 +8386,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{26022D98-9C5C-4F61-B0DF-E159B216C11F}" name="Teams" displayName="Teams" ref="A1:E65" totalsRowShown="0" headerRowDxfId="6" tableBorderDxfId="5" dataCellStyle="Normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{26022D98-9C5C-4F61-B0DF-E159B216C11F}" name="Teams" displayName="Teams" ref="A1:E65" totalsRowShown="0" headerRowDxfId="5" tableBorderDxfId="4" dataCellStyle="Normal">
   <autoFilter ref="A1:E65" xr:uid="{26022D98-9C5C-4F61-B0DF-E159B216C11F}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -8395,13 +8395,13 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{ED40F7E7-3328-4259-9877-945FE5D47DC3}" name="Seed" dataDxfId="4" dataCellStyle="Normal"/>
-    <tableColumn id="3" xr3:uid="{4CDAB027-D970-460D-AAC2-EB0B9485FD8C}" name="Region" dataDxfId="3" dataCellStyle="Normal"/>
+    <tableColumn id="1" xr3:uid="{ED40F7E7-3328-4259-9877-945FE5D47DC3}" name="Seed" dataDxfId="3" dataCellStyle="Normal"/>
+    <tableColumn id="3" xr3:uid="{4CDAB027-D970-460D-AAC2-EB0B9485FD8C}" name="Region" dataDxfId="2" dataCellStyle="Normal"/>
     <tableColumn id="2" xr3:uid="{E218ED8F-68F8-429A-9939-575EF5D8461D}" name="Team" dataCellStyle="Normal"/>
-    <tableColumn id="5" xr3:uid="{5B5B6B66-69E6-43F4-9B60-841171B24FC7}" name="Hyperlink Name" dataDxfId="2">
+    <tableColumn id="5" xr3:uid="{5B5B6B66-69E6-43F4-9B60-841171B24FC7}" name="Hyperlink Name" dataDxfId="1">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Teams[[#This Row],[Team]],Team_Links[School],Team_Links[PartialLink],,0,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5DE08296-6B22-41D3-9B0D-54A014588C20}" name="Logo" dataDxfId="1" dataCellStyle="Normal">
+    <tableColumn id="4" xr3:uid="{5DE08296-6B22-41D3-9B0D-54A014588C20}" name="Logo" dataDxfId="0" dataCellStyle="Normal">
       <calculatedColumnFormula>_xlfn.IMAGE(_xlfn.CONCAT("https://cdn.ssref.net/req/202510241/tlogo/ncaa/",TEXT(Teams[[#This Row],[Hyperlink Name]],),"-2025.png"))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -16207,11 +16207,11 @@
         <v>4</v>
       </c>
       <c r="C28" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="D28" t="str">
         <f>_xlfn.XLOOKUP(Teams[[#This Row],[Team]],Team_Links[School],Team_Links[PartialLink],,0,1)</f>
-        <v>florida</v>
+        <v>drake</v>
       </c>
       <c r="E28" s="1" t="e" vm="27">
         <f>_xlfn.IMAGE(_xlfn.CONCAT("https://cdn.ssref.net/req/202510241/tlogo/ncaa/",TEXT(Teams[[#This Row],[Hyperlink Name]],),"-2025.png"))</f>
@@ -17074,7 +17074,7 @@
       </c>
       <c r="C5" s="91" t="str">
         <f t="shared" ref="C5:C36" ca="1" si="1">IF(O5="","",IF(A5=O5,B5,A5))</f>
-        <v>Air Force</v>
+        <v>Abilene Christian</v>
       </c>
       <c r="D5" s="91" t="e">
         <f t="shared" ref="D5:D36" si="2">IF(SeedType=1,0,IF(SeedType=2,VLOOKUP(O5,SeedInfo,2,FALSE)*1,MAX(VLOOKUP(O5,SeedInfo,2,FALSE)-VLOOKUP(C5,SeedInfo,2,FALSE),0)))</f>
@@ -17108,7 +17108,7 @@
       </c>
       <c r="L5" s="84">
         <f ca="1">RANDBETWEEN(90,120)</f>
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="M5" s="84" t="e" vm="66">
         <f>_xlfn.XLOOKUP(I5,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -17116,13 +17116,13 @@
       </c>
       <c r="N5" s="84">
         <f ca="1">RANDBETWEEN(90,120)</f>
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="O5" s="194" t="str">
         <f t="shared" ref="O5:O36" ca="1" si="3">IF(L5&gt;N5,G5,I5)</f>
-        <v>Abilene Christian</v>
-      </c>
-      <c r="P5" s="209" t="e" vm="65">
+        <v>Air Force</v>
+      </c>
+      <c r="P5" s="209" t="e" vm="66">
         <f ca="1">_xlfn.XLOOKUP(O5,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -17134,7 +17134,7 @@
 O5=G5,
 IF(F5&gt;J5,TRUE,FALSE),
 IF(J5&gt;F5,TRUE,FALSE))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" s="98"/>
     </row>
@@ -17183,7 +17183,7 @@
       </c>
       <c r="L6" s="82">
         <f t="shared" ref="L6:N36" ca="1" si="5">RANDBETWEEN(90,120)</f>
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="M6" s="82" t="e" vm="68">
         <f>_xlfn.XLOOKUP(I6,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -17191,7 +17191,7 @@
       </c>
       <c r="N6" s="82">
         <f t="shared" ca="1" si="5"/>
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="O6" s="189" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="L7" s="82">
         <f t="shared" ca="1" si="5"/>
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="M7" s="82" t="e" vm="70">
         <f>_xlfn.XLOOKUP(I7,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -17266,7 +17266,7 @@
       </c>
       <c r="N7" s="82">
         <f t="shared" ca="1" si="5"/>
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="O7" s="189" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -17296,7 +17296,7 @@
       </c>
       <c r="C8" s="91" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Alcorn State</v>
+        <v>Albany (NY)</v>
       </c>
       <c r="D8" s="91" t="e">
         <f t="shared" si="2"/>
@@ -17330,7 +17330,7 @@
       </c>
       <c r="L8" s="82">
         <f t="shared" ca="1" si="5"/>
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="M8" s="82" t="e" vm="72">
         <f>_xlfn.XLOOKUP(I8,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -17338,13 +17338,13 @@
       </c>
       <c r="N8" s="82">
         <f t="shared" ca="1" si="5"/>
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="O8" s="189" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Albany (NY)</v>
-      </c>
-      <c r="P8" s="204" t="e" vm="71">
+        <v>Alcorn State</v>
+      </c>
+      <c r="P8" s="204" t="e" vm="72">
         <f ca="1">_xlfn.XLOOKUP(O8,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -17353,7 +17353,7 @@
       </c>
       <c r="R8" s="6" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" s="98"/>
     </row>
@@ -17368,7 +17368,7 @@
       </c>
       <c r="C9" s="91" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Appalachian State</v>
+        <v>American</v>
       </c>
       <c r="D9" s="91" t="e">
         <f t="shared" si="2"/>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="L9" s="82">
         <f t="shared" ca="1" si="5"/>
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="M9" s="82" t="e" vm="74">
         <f>_xlfn.XLOOKUP(I9,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -17410,13 +17410,13 @@
       </c>
       <c r="N9" s="82">
         <f t="shared" ca="1" si="5"/>
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="O9" s="189" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>American</v>
-      </c>
-      <c r="P9" s="204" t="e" vm="73">
+        <v>Appalachian State</v>
+      </c>
+      <c r="P9" s="204" t="e" vm="74">
         <f ca="1">_xlfn.XLOOKUP(O9,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -17425,7 +17425,7 @@
       </c>
       <c r="R9" s="6" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" s="98"/>
     </row>
@@ -17440,7 +17440,7 @@
       </c>
       <c r="C10" s="91" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Arizona</v>
+        <v>Arizona State</v>
       </c>
       <c r="D10" s="91" t="e">
         <f t="shared" si="2"/>
@@ -17474,7 +17474,7 @@
       </c>
       <c r="L10" s="82">
         <f t="shared" ca="1" si="5"/>
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="M10" s="82" t="e" vm="76">
         <f>_xlfn.XLOOKUP(I10,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -17482,13 +17482,13 @@
       </c>
       <c r="N10" s="82">
         <f t="shared" ca="1" si="5"/>
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="O10" s="189" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Arizona State</v>
-      </c>
-      <c r="P10" s="204" t="e" vm="76">
+        <v>Arizona</v>
+      </c>
+      <c r="P10" s="204" t="e" vm="75">
         <f ca="1">_xlfn.XLOOKUP(O10,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -17497,7 +17497,7 @@
       </c>
       <c r="R10" s="6" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" s="98"/>
     </row>
@@ -17512,7 +17512,7 @@
       </c>
       <c r="C11" s="91" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Arkansas</v>
+        <v>Arkansas State</v>
       </c>
       <c r="D11" s="91" t="e">
         <f t="shared" si="2"/>
@@ -17546,7 +17546,7 @@
       </c>
       <c r="L11" s="82">
         <f t="shared" ca="1" si="5"/>
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="M11" s="82" t="e" vm="78">
         <f>_xlfn.XLOOKUP(I11,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -17554,13 +17554,13 @@
       </c>
       <c r="N11" s="82">
         <f t="shared" ca="1" si="5"/>
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="O11" s="189" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Arkansas State</v>
-      </c>
-      <c r="P11" s="204" t="e" vm="78">
+        <v>Arkansas</v>
+      </c>
+      <c r="P11" s="204" t="e" vm="77">
         <f ca="1">_xlfn.XLOOKUP(O11,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -17569,7 +17569,7 @@
       </c>
       <c r="R11" s="6" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" s="98"/>
     </row>
@@ -17584,7 +17584,7 @@
       </c>
       <c r="C12" s="91" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Arkansas-Pine Bluff</v>
+        <v>Army</v>
       </c>
       <c r="D12" s="91" t="e">
         <f t="shared" si="2"/>
@@ -17618,7 +17618,7 @@
       </c>
       <c r="L12" s="109">
         <f t="shared" ca="1" si="5"/>
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="M12" s="109" t="e" vm="80">
         <f>_xlfn.XLOOKUP(I12,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -17626,13 +17626,13 @@
       </c>
       <c r="N12" s="109">
         <f t="shared" ca="1" si="5"/>
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="O12" s="190" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Army</v>
-      </c>
-      <c r="P12" s="205" t="e" vm="80">
+        <v>Arkansas-Pine Bluff</v>
+      </c>
+      <c r="P12" s="205" t="e" vm="79">
         <f ca="1">_xlfn.XLOOKUP(O12,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -17641,7 +17641,7 @@
       </c>
       <c r="R12" s="6" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" s="98"/>
     </row>
@@ -17656,7 +17656,7 @@
       </c>
       <c r="C13" s="91" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Austin Peay</v>
+        <v>Auburn</v>
       </c>
       <c r="D13" s="91" t="e">
         <f t="shared" si="2"/>
@@ -17690,7 +17690,7 @@
       </c>
       <c r="L13" s="115">
         <f t="shared" ca="1" si="5"/>
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="M13" s="115" t="e" vm="82">
         <f>_xlfn.XLOOKUP(I13,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -17698,13 +17698,13 @@
       </c>
       <c r="N13" s="115">
         <f t="shared" ca="1" si="5"/>
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="O13" s="191" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Auburn</v>
-      </c>
-      <c r="P13" s="206" t="e" vm="81">
+        <v>Austin Peay</v>
+      </c>
+      <c r="P13" s="206" t="e" vm="82">
         <f ca="1">_xlfn.XLOOKUP(O13,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -17713,7 +17713,7 @@
       </c>
       <c r="R13" s="6" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" s="98"/>
     </row>
@@ -17762,7 +17762,7 @@
       </c>
       <c r="L14" s="83">
         <f t="shared" ca="1" si="5"/>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M14" s="83" t="e" vm="84">
         <f>_xlfn.XLOOKUP(I14,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -17770,7 +17770,7 @@
       </c>
       <c r="N14" s="83">
         <f t="shared" ca="1" si="5"/>
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="O14" s="192" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -17834,7 +17834,7 @@
       </c>
       <c r="L15" s="83">
         <f t="shared" ca="1" si="5"/>
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M15" s="83" t="e" vm="86">
         <f>_xlfn.XLOOKUP(I15,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -17842,7 +17842,7 @@
       </c>
       <c r="N15" s="83">
         <f t="shared" ca="1" si="5"/>
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O15" s="192" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -17906,7 +17906,7 @@
       </c>
       <c r="L16" s="83">
         <f t="shared" ca="1" si="5"/>
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="M16" s="83" t="e" vm="88">
         <f>_xlfn.XLOOKUP(I16,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -17914,7 +17914,7 @@
       </c>
       <c r="N16" s="83">
         <f t="shared" ca="1" si="5"/>
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="O16" s="192" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -17978,7 +17978,7 @@
       </c>
       <c r="L17" s="83">
         <f t="shared" ca="1" si="5"/>
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="M17" s="83" t="e" vm="90">
         <f>_xlfn.XLOOKUP(I17,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -17986,7 +17986,7 @@
       </c>
       <c r="N17" s="83">
         <f t="shared" ca="1" si="5"/>
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="O17" s="192" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -18008,7 +18008,7 @@
     <row r="18" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="91" t="str">
         <f t="shared" si="4"/>
-        <v>Florida</v>
+        <v>Drake</v>
       </c>
       <c r="B18" s="91" t="str">
         <f t="shared" si="0"/>
@@ -18016,7 +18016,7 @@
       </c>
       <c r="C18" s="91" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Florida</v>
+        <v>Duke</v>
       </c>
       <c r="D18" s="91" t="e">
         <f t="shared" si="2"/>
@@ -18031,7 +18031,7 @@
       </c>
       <c r="G18" s="118" t="str">
         <f>Teams!C28</f>
-        <v>Florida</v>
+        <v>Drake</v>
       </c>
       <c r="H18" s="178" t="s">
         <v>9</v>
@@ -18050,7 +18050,7 @@
       </c>
       <c r="L18" s="83">
         <f t="shared" ca="1" si="5"/>
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="M18" s="83" t="e" vm="92">
         <f>_xlfn.XLOOKUP(I18,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -18058,13 +18058,13 @@
       </c>
       <c r="N18" s="83">
         <f t="shared" ca="1" si="5"/>
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="O18" s="192" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Duke</v>
-      </c>
-      <c r="P18" s="207" t="e" vm="92">
+        <v>Drake</v>
+      </c>
+      <c r="P18" s="207" t="e" vm="91">
         <f ca="1">_xlfn.XLOOKUP(O18,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -18073,7 +18073,7 @@
       </c>
       <c r="R18" s="6" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" s="98"/>
     </row>
@@ -18088,7 +18088,7 @@
       </c>
       <c r="C19" s="91" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Brigham Young</v>
+        <v>Bradley</v>
       </c>
       <c r="D19" s="91" t="e">
         <f t="shared" si="2"/>
@@ -18122,7 +18122,7 @@
       </c>
       <c r="L19" s="83">
         <f t="shared" ca="1" si="5"/>
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="M19" s="83" t="e" vm="94">
         <f>_xlfn.XLOOKUP(I19,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -18130,13 +18130,13 @@
       </c>
       <c r="N19" s="83">
         <f t="shared" ca="1" si="5"/>
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="O19" s="192" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Bradley</v>
-      </c>
-      <c r="P19" s="207" t="e" vm="93">
+        <v>Brigham Young</v>
+      </c>
+      <c r="P19" s="207" t="e" vm="94">
         <f ca="1">_xlfn.XLOOKUP(O19,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -18145,7 +18145,7 @@
       </c>
       <c r="R19" s="6" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" s="98"/>
     </row>
@@ -18160,7 +18160,7 @@
       </c>
       <c r="C20" s="91" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Bryant</v>
+        <v>Brown</v>
       </c>
       <c r="D20" s="91" t="e">
         <f t="shared" si="2"/>
@@ -18194,7 +18194,7 @@
       </c>
       <c r="L20" s="126">
         <f t="shared" ca="1" si="5"/>
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="M20" s="126" t="e" vm="96">
         <f>_xlfn.XLOOKUP(I20,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -18202,13 +18202,13 @@
       </c>
       <c r="N20" s="126">
         <f t="shared" ca="1" si="5"/>
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="O20" s="193" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Brown</v>
-      </c>
-      <c r="P20" s="208" t="e" vm="95">
+        <v>Bryant</v>
+      </c>
+      <c r="P20" s="208" t="e" vm="96">
         <f ca="1">_xlfn.XLOOKUP(O20,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -18217,7 +18217,7 @@
       </c>
       <c r="R20" s="6" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" s="98"/>
     </row>
@@ -18232,7 +18232,7 @@
       </c>
       <c r="C21" s="91" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Buffalo</v>
+        <v>Bucknell</v>
       </c>
       <c r="D21" s="91" t="e">
         <f t="shared" si="2"/>
@@ -18266,7 +18266,7 @@
       </c>
       <c r="L21" s="97">
         <f t="shared" ca="1" si="5"/>
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="M21" s="97" t="e" vm="98">
         <f>_xlfn.XLOOKUP(I21,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -18274,13 +18274,13 @@
       </c>
       <c r="N21" s="97">
         <f t="shared" ca="1" si="5"/>
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="O21" s="188" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Bucknell</v>
-      </c>
-      <c r="P21" s="203" t="e" vm="97">
+        <v>Buffalo</v>
+      </c>
+      <c r="P21" s="203" t="e" vm="98">
         <f ca="1">_xlfn.XLOOKUP(O21,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -18289,7 +18289,7 @@
       </c>
       <c r="R21" s="6" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" s="98"/>
     </row>
@@ -18338,7 +18338,7 @@
       </c>
       <c r="L22" s="82">
         <f t="shared" ca="1" si="5"/>
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="M22" s="82" t="e" vm="100">
         <f>_xlfn.XLOOKUP(I22,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -18346,7 +18346,7 @@
       </c>
       <c r="N22" s="82">
         <f t="shared" ca="1" si="5"/>
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O22" s="189" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -18376,7 +18376,7 @@
       </c>
       <c r="C23" s="91" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Cal State Fullerton</v>
+        <v>Cal State Bakersfield</v>
       </c>
       <c r="D23" s="91" t="e">
         <f t="shared" si="2"/>
@@ -18410,7 +18410,7 @@
       </c>
       <c r="L23" s="82">
         <f t="shared" ca="1" si="5"/>
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="M23" s="82" t="e" vm="102">
         <f>_xlfn.XLOOKUP(I23,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -18418,13 +18418,13 @@
       </c>
       <c r="N23" s="82">
         <f t="shared" ca="1" si="5"/>
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="O23" s="189" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Cal State Bakersfield</v>
-      </c>
-      <c r="P23" s="204" t="e" vm="101">
+        <v>Cal State Fullerton</v>
+      </c>
+      <c r="P23" s="204" t="e" vm="102">
         <f ca="1">_xlfn.XLOOKUP(O23,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -18433,7 +18433,7 @@
       </c>
       <c r="R23" s="6" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" s="98"/>
     </row>
@@ -18448,7 +18448,7 @@
       </c>
       <c r="C24" s="91" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Cal State Northridge</v>
+        <v>California</v>
       </c>
       <c r="D24" s="91" t="e">
         <f t="shared" si="2"/>
@@ -18482,7 +18482,7 @@
       </c>
       <c r="L24" s="82">
         <f t="shared" ca="1" si="5"/>
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="M24" s="82" t="e" vm="104">
         <f>_xlfn.XLOOKUP(I24,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -18490,13 +18490,13 @@
       </c>
       <c r="N24" s="82">
         <f t="shared" ca="1" si="5"/>
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O24" s="189" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>California</v>
-      </c>
-      <c r="P24" s="204" t="e" vm="104">
+        <v>Cal State Northridge</v>
+      </c>
+      <c r="P24" s="204" t="e" vm="103">
         <f ca="1">_xlfn.XLOOKUP(O24,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -18505,7 +18505,7 @@
       </c>
       <c r="R24" s="6" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" s="98"/>
     </row>
@@ -18520,7 +18520,7 @@
       </c>
       <c r="C25" s="91" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>California Baptist</v>
+        <v>Campbell</v>
       </c>
       <c r="D25" s="91" t="e">
         <f t="shared" si="2"/>
@@ -18554,7 +18554,7 @@
       </c>
       <c r="L25" s="82">
         <f t="shared" ca="1" si="5"/>
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M25" s="82" t="e" vm="106">
         <f>_xlfn.XLOOKUP(I25,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -18562,13 +18562,13 @@
       </c>
       <c r="N25" s="82">
         <f t="shared" ca="1" si="5"/>
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="O25" s="189" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Campbell</v>
-      </c>
-      <c r="P25" s="204" t="e" vm="106">
+        <v>California Baptist</v>
+      </c>
+      <c r="P25" s="204" t="e" vm="105">
         <f ca="1">_xlfn.XLOOKUP(O25,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -18577,7 +18577,7 @@
       </c>
       <c r="R25" s="6" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" s="98"/>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="L26" s="82">
         <f t="shared" ca="1" si="5"/>
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="M26" s="82" t="e" vm="108">
         <f>_xlfn.XLOOKUP(I26,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -18634,7 +18634,7 @@
       </c>
       <c r="N26" s="82">
         <f t="shared" ca="1" si="5"/>
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="O26" s="189" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -18698,7 +18698,7 @@
       </c>
       <c r="L27" s="82">
         <f t="shared" ca="1" si="5"/>
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="M27" s="82" t="e" vm="110">
         <f>_xlfn.XLOOKUP(I27,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -18706,7 +18706,7 @@
       </c>
       <c r="N27" s="82">
         <f t="shared" ca="1" si="5"/>
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="O27" s="189" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -18770,7 +18770,7 @@
       </c>
       <c r="L28" s="109">
         <f t="shared" ca="1" si="5"/>
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="M28" s="109" t="e" vm="112">
         <f>_xlfn.XLOOKUP(I28,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -18778,7 +18778,7 @@
       </c>
       <c r="N28" s="109">
         <f t="shared" ca="1" si="5"/>
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="O28" s="190" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -18808,7 +18808,7 @@
       </c>
       <c r="C29" s="91" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Chattanooga</v>
+        <v>Chicago State</v>
       </c>
       <c r="D29" s="91" t="e">
         <f t="shared" si="2"/>
@@ -18842,7 +18842,7 @@
       </c>
       <c r="L29" s="115">
         <f t="shared" ca="1" si="5"/>
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="M29" s="115" t="e" vm="114">
         <f>_xlfn.XLOOKUP(I29,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -18850,13 +18850,13 @@
       </c>
       <c r="N29" s="115">
         <f t="shared" ca="1" si="5"/>
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="O29" s="191" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Chicago State</v>
-      </c>
-      <c r="P29" s="206" t="e" vm="114">
+        <v>Chattanooga</v>
+      </c>
+      <c r="P29" s="206" t="e" vm="113">
         <f ca="1">_xlfn.XLOOKUP(O29,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -18865,7 +18865,7 @@
       </c>
       <c r="R29" s="6" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" s="98"/>
     </row>
@@ -18914,7 +18914,7 @@
       </c>
       <c r="L30" s="83">
         <f t="shared" ca="1" si="5"/>
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="M30" s="83" t="e" vm="116">
         <f>_xlfn.XLOOKUP(I30,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -18922,7 +18922,7 @@
       </c>
       <c r="N30" s="83">
         <f t="shared" ca="1" si="5"/>
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="O30" s="192" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -18952,7 +18952,7 @@
       </c>
       <c r="C31" s="91" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Cleveland State</v>
+        <v>Coastal Carolina</v>
       </c>
       <c r="D31" s="91" t="e">
         <f t="shared" si="2"/>
@@ -18994,13 +18994,13 @@
       </c>
       <c r="N31" s="83">
         <f t="shared" ca="1" si="5"/>
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="O31" s="192" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Coastal Carolina</v>
-      </c>
-      <c r="P31" s="207" t="e" vm="118">
+        <v>Cleveland State</v>
+      </c>
+      <c r="P31" s="207" t="e" vm="117">
         <f ca="1">_xlfn.XLOOKUP(O31,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -19009,7 +19009,7 @@
       </c>
       <c r="R31" s="6" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" s="98"/>
     </row>
@@ -19058,7 +19058,7 @@
       </c>
       <c r="L32" s="83">
         <f t="shared" ca="1" si="5"/>
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="M32" s="83" t="e" vm="120">
         <f>_xlfn.XLOOKUP(I32,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -19066,7 +19066,7 @@
       </c>
       <c r="N32" s="83">
         <f t="shared" ca="1" si="5"/>
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="O32" s="192" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -19130,7 +19130,7 @@
       </c>
       <c r="L33" s="83">
         <f t="shared" ca="1" si="5"/>
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="M33" s="83" t="e" vm="122">
         <f>_xlfn.XLOOKUP(I33,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -19138,7 +19138,7 @@
       </c>
       <c r="N33" s="83">
         <f t="shared" ca="1" si="5"/>
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O33" s="192" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -19168,7 +19168,7 @@
       </c>
       <c r="C34" s="91" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Columbia</v>
+        <v>Connecticut</v>
       </c>
       <c r="D34" s="91" t="e">
         <f t="shared" si="2"/>
@@ -19202,7 +19202,7 @@
       </c>
       <c r="L34" s="83">
         <f t="shared" ca="1" si="5"/>
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="M34" s="83" t="e" vm="124">
         <f>_xlfn.XLOOKUP(I34,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -19210,13 +19210,13 @@
       </c>
       <c r="N34" s="83">
         <f t="shared" ca="1" si="5"/>
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="O34" s="192" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Connecticut</v>
-      </c>
-      <c r="P34" s="207" t="e" vm="124">
+        <v>Columbia</v>
+      </c>
+      <c r="P34" s="207" t="e" vm="123">
         <f ca="1">_xlfn.XLOOKUP(O34,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -19225,7 +19225,7 @@
       </c>
       <c r="R34" s="6" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" s="98"/>
     </row>
@@ -19240,7 +19240,7 @@
       </c>
       <c r="C35" s="91" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Coppin State</v>
+        <v>Cornell</v>
       </c>
       <c r="D35" s="91" t="e">
         <f t="shared" si="2"/>
@@ -19274,7 +19274,7 @@
       </c>
       <c r="L35" s="83">
         <f t="shared" ca="1" si="5"/>
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="M35" s="83" t="e" vm="126">
         <f>_xlfn.XLOOKUP(I35,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -19282,13 +19282,13 @@
       </c>
       <c r="N35" s="83">
         <f t="shared" ca="1" si="5"/>
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="O35" s="192" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Cornell</v>
-      </c>
-      <c r="P35" s="207" t="e" vm="126">
+        <v>Coppin State</v>
+      </c>
+      <c r="P35" s="207" t="e" vm="125">
         <f ca="1">_xlfn.XLOOKUP(O35,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -19297,7 +19297,7 @@
       </c>
       <c r="R35" s="6" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" s="98"/>
     </row>
@@ -19312,7 +19312,7 @@
       </c>
       <c r="C36" s="91" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Creighton</v>
+        <v>Dartmouth</v>
       </c>
       <c r="D36" s="91" t="e">
         <f t="shared" si="2"/>
@@ -19346,7 +19346,7 @@
       </c>
       <c r="L36" s="126">
         <f t="shared" ca="1" si="5"/>
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="M36" s="126" t="e" vm="128">
         <f>_xlfn.XLOOKUP(I36,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -19354,13 +19354,13 @@
       </c>
       <c r="N36" s="126">
         <f t="shared" ca="1" si="5"/>
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O36" s="193" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Dartmouth</v>
-      </c>
-      <c r="P36" s="208" t="e" vm="128">
+        <v>Creighton</v>
+      </c>
+      <c r="P36" s="208" t="e" vm="127">
         <f ca="1">_xlfn.XLOOKUP(O36,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -19369,7 +19369,7 @@
       </c>
       <c r="R36" s="6" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36" s="98"/>
     </row>
@@ -19399,7 +19399,7 @@
     <row r="38" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="91" t="str">
         <f ca="1">G38</f>
-        <v>Abilene Christian</v>
+        <v>Air Force</v>
       </c>
       <c r="B38" s="91" t="str">
         <f ca="1">I38</f>
@@ -19407,7 +19407,7 @@
       </c>
       <c r="C38" s="91" t="str">
         <f t="shared" ref="C38:C53" ca="1" si="8">IF(O38="","",IF(A38=O38,B38,A38))</f>
-        <v>Abilene Christian</v>
+        <v>Akron</v>
       </c>
       <c r="D38" s="91" t="e">
         <f t="shared" ref="D38:D53" si="9">IF(SeedType=1,0,IF(SeedType=2,VLOOKUP(O38,SeedInfo,2,FALSE)*2,MAX(VLOOKUP(O38,SeedInfo,2,FALSE)-VLOOKUP(C38,SeedInfo,2,FALSE),0)))</f>
@@ -19419,11 +19419,11 @@
       </c>
       <c r="F38" s="130" cm="1">
         <f t="array" aca="1" ref="F38" ca="1">_xlfn.XLOOKUP(G38,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G38" s="131" t="str">
         <f ca="1">O5</f>
-        <v>Abilene Christian</v>
+        <v>Air Force</v>
       </c>
       <c r="H38" s="181" t="s">
         <v>9</v>
@@ -19436,13 +19436,13 @@
         <f t="array" aca="1" ref="J38" ca="1">_xlfn.XLOOKUP(I38,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
         <v>8</v>
       </c>
-      <c r="K38" s="84" t="e" vm="65">
+      <c r="K38" s="84" t="e" vm="66">
         <f ca="1">_xlfn.XLOOKUP(G38,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="L38" s="84">
         <f t="shared" ref="L38:N72" ca="1" si="10">RANDBETWEEN(90,120)</f>
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="M38" s="84" t="e" vm="67">
         <f ca="1">_xlfn.XLOOKUP(I38,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -19450,13 +19450,13 @@
       </c>
       <c r="N38" s="84">
         <f t="shared" ca="1" si="10"/>
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="O38" s="194" t="str">
         <f t="shared" ref="O38:O53" ca="1" si="11">IF(L38&gt;N38,G38,I38)</f>
-        <v>Akron</v>
-      </c>
-      <c r="P38" s="209" t="e" vm="67">
+        <v>Air Force</v>
+      </c>
+      <c r="P38" s="209" t="e" vm="66">
         <f ca="1">_xlfn.XLOOKUP(O38,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -19476,11 +19476,11 @@
       </c>
       <c r="B39" s="91" t="str">
         <f t="shared" ref="B39:B53" ca="1" si="13">I39</f>
-        <v>Albany (NY)</v>
+        <v>Alcorn State</v>
       </c>
       <c r="C39" s="91" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>Albany (NY)</v>
+        <v>Alabama State</v>
       </c>
       <c r="D39" s="91" t="e">
         <f t="shared" si="9"/>
@@ -19502,11 +19502,11 @@
       </c>
       <c r="I39" s="102" t="str">
         <f ca="1">O8</f>
-        <v>Albany (NY)</v>
+        <v>Alcorn State</v>
       </c>
       <c r="J39" s="103" cm="1">
         <f t="array" aca="1" ref="J39" ca="1">_xlfn.XLOOKUP(I39,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K39" s="82" t="e" vm="70">
         <f ca="1">_xlfn.XLOOKUP(G39,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -19514,21 +19514,21 @@
       </c>
       <c r="L39" s="82">
         <f t="shared" ca="1" si="10"/>
-        <v>115</v>
-      </c>
-      <c r="M39" s="82" t="e" vm="71">
+        <v>91</v>
+      </c>
+      <c r="M39" s="82" t="e" vm="72">
         <f ca="1">_xlfn.XLOOKUP(I39,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="N39" s="82">
         <f t="shared" ca="1" si="10"/>
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="O39" s="189" t="str">
         <f t="shared" ca="1" si="11"/>
-        <v>Alabama State</v>
-      </c>
-      <c r="P39" s="204" t="e" vm="70">
+        <v>Alcorn State</v>
+      </c>
+      <c r="P39" s="204" t="e" vm="72">
         <f ca="1">_xlfn.XLOOKUP(O39,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -19544,15 +19544,15 @@
     <row r="40" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="91" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>American</v>
+        <v>Appalachian State</v>
       </c>
       <c r="B40" s="91" t="str">
         <f t="shared" ca="1" si="13"/>
-        <v>Arizona State</v>
+        <v>Arizona</v>
       </c>
       <c r="C40" s="91" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>Arizona State</v>
+        <v>Appalachian State</v>
       </c>
       <c r="D40" s="91" t="e">
         <f t="shared" si="9"/>
@@ -19563,44 +19563,44 @@
       </c>
       <c r="F40" s="100" cm="1">
         <f t="array" aca="1" ref="F40" ca="1">_xlfn.XLOOKUP(G40,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G40" s="101" t="str">
         <f ca="1">O9</f>
-        <v>American</v>
+        <v>Appalachian State</v>
       </c>
       <c r="H40" s="176" t="s">
         <v>9</v>
       </c>
       <c r="I40" s="102" t="str">
         <f ca="1">O10</f>
-        <v>Arizona State</v>
+        <v>Arizona</v>
       </c>
       <c r="J40" s="103" cm="1">
         <f t="array" aca="1" ref="J40" ca="1">_xlfn.XLOOKUP(I40,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>14</v>
-      </c>
-      <c r="K40" s="82" t="e" vm="73">
+        <v>3</v>
+      </c>
+      <c r="K40" s="82" t="e" vm="74">
         <f ca="1">_xlfn.XLOOKUP(G40,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="L40" s="82">
         <f t="shared" ca="1" si="10"/>
-        <v>111</v>
-      </c>
-      <c r="M40" s="82" t="e" vm="76">
+        <v>114</v>
+      </c>
+      <c r="M40" s="82" t="e" vm="75">
         <f ca="1">_xlfn.XLOOKUP(I40,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="N40" s="82">
         <f t="shared" ca="1" si="10"/>
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="O40" s="189" t="str">
         <f t="shared" ca="1" si="11"/>
-        <v>American</v>
-      </c>
-      <c r="P40" s="204" t="e" vm="73">
+        <v>Arizona</v>
+      </c>
+      <c r="P40" s="204" t="e" vm="75">
         <f ca="1">_xlfn.XLOOKUP(O40,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -19616,15 +19616,15 @@
     <row r="41" spans="1:19" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="91" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>Arkansas State</v>
+        <v>Arkansas</v>
       </c>
       <c r="B41" s="91" t="str">
         <f t="shared" ca="1" si="13"/>
-        <v>Army</v>
+        <v>Arkansas-Pine Bluff</v>
       </c>
       <c r="C41" s="91" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>Army</v>
+        <v>Arkansas-Pine Bluff</v>
       </c>
       <c r="D41" s="91" t="e">
         <f t="shared" si="9"/>
@@ -19635,44 +19635,44 @@
       </c>
       <c r="F41" s="135" cm="1">
         <f t="array" aca="1" ref="F41" ca="1">_xlfn.XLOOKUP(G41,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G41" s="136" t="str">
         <f ca="1">O11</f>
-        <v>Arkansas State</v>
+        <v>Arkansas</v>
       </c>
       <c r="H41" s="182" t="s">
         <v>9</v>
       </c>
       <c r="I41" s="137" t="str">
         <f ca="1">O12</f>
-        <v>Army</v>
+        <v>Arkansas-Pine Bluff</v>
       </c>
       <c r="J41" s="138" cm="1">
         <f t="array" aca="1" ref="J41" ca="1">_xlfn.XLOOKUP(I41,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>15</v>
-      </c>
-      <c r="K41" s="139" t="e" vm="78">
+        <v>2</v>
+      </c>
+      <c r="K41" s="139" t="e" vm="77">
         <f ca="1">_xlfn.XLOOKUP(G41,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="L41" s="139">
         <f t="shared" ca="1" si="10"/>
-        <v>106</v>
-      </c>
-      <c r="M41" s="139" t="e" vm="80">
+        <v>97</v>
+      </c>
+      <c r="M41" s="139" t="e" vm="79">
         <f ca="1">_xlfn.XLOOKUP(I41,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="N41" s="139">
         <f t="shared" ca="1" si="10"/>
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O41" s="195" t="str">
         <f t="shared" ca="1" si="11"/>
-        <v>Arkansas State</v>
-      </c>
-      <c r="P41" s="210" t="e" vm="78">
+        <v>Arkansas</v>
+      </c>
+      <c r="P41" s="210" t="e" vm="77">
         <f ca="1">_xlfn.XLOOKUP(O41,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -19681,14 +19681,14 @@
       </c>
       <c r="R41" s="6" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" s="98"/>
     </row>
     <row r="42" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="91" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>Auburn</v>
+        <v>Austin Peay</v>
       </c>
       <c r="B42" s="91" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -19696,7 +19696,7 @@
       </c>
       <c r="C42" s="91" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>Auburn</v>
+        <v>Austin Peay</v>
       </c>
       <c r="D42" s="91" t="e">
         <f t="shared" si="9"/>
@@ -19707,11 +19707,11 @@
       </c>
       <c r="F42" s="141" cm="1">
         <f t="array" aca="1" ref="F42" ca="1">_xlfn.XLOOKUP(G42,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G42" s="142" t="str">
         <f ca="1">O13</f>
-        <v>Auburn</v>
+        <v>Austin Peay</v>
       </c>
       <c r="H42" s="183" t="s">
         <v>9</v>
@@ -19724,13 +19724,13 @@
         <f t="array" aca="1" ref="J42" ca="1">_xlfn.XLOOKUP(I42,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
         <v>8</v>
       </c>
-      <c r="K42" s="145" t="e" vm="81">
+      <c r="K42" s="145" t="e" vm="82">
         <f ca="1">_xlfn.XLOOKUP(G42,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="L42" s="145">
         <f t="shared" ca="1" si="10"/>
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="M42" s="145" t="e" vm="83">
         <f ca="1">_xlfn.XLOOKUP(I42,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="N42" s="145">
         <f t="shared" ca="1" si="10"/>
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="O42" s="196" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -19753,7 +19753,7 @@
       </c>
       <c r="R42" s="6" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S42" s="98"/>
     </row>
@@ -19768,7 +19768,7 @@
       </c>
       <c r="C43" s="91" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>Binghamton</v>
+        <v>Belmont</v>
       </c>
       <c r="D43" s="91" t="e">
         <f t="shared" si="9"/>
@@ -19802,7 +19802,7 @@
       </c>
       <c r="L43" s="83">
         <f t="shared" ca="1" si="10"/>
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="M43" s="83" t="e" vm="88">
         <f ca="1">_xlfn.XLOOKUP(I43,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -19810,13 +19810,13 @@
       </c>
       <c r="N43" s="83">
         <f t="shared" ca="1" si="10"/>
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="O43" s="192" t="str">
         <f t="shared" ca="1" si="11"/>
-        <v>Belmont</v>
-      </c>
-      <c r="P43" s="207" t="e" vm="86">
+        <v>Binghamton</v>
+      </c>
+      <c r="P43" s="207" t="e" vm="88">
         <f ca="1">_xlfn.XLOOKUP(O43,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -19825,7 +19825,7 @@
       </c>
       <c r="R43" s="6" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S43" s="98"/>
     </row>
@@ -19836,11 +19836,11 @@
       </c>
       <c r="B44" s="91" t="str">
         <f t="shared" ca="1" si="13"/>
-        <v>Duke</v>
+        <v>Drake</v>
       </c>
       <c r="C44" s="91" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>Duke</v>
+        <v>Boise State</v>
       </c>
       <c r="D44" s="91" t="e">
         <f t="shared" si="9"/>
@@ -19862,11 +19862,11 @@
       </c>
       <c r="I44" s="119" t="str">
         <f ca="1">O18</f>
-        <v>Duke</v>
+        <v>Drake</v>
       </c>
       <c r="J44" s="120" cm="1">
         <f t="array" aca="1" ref="J44" ca="1">_xlfn.XLOOKUP(I44,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="K44" s="83" t="e" vm="89">
         <f ca="1">_xlfn.XLOOKUP(G44,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -19874,21 +19874,21 @@
       </c>
       <c r="L44" s="83">
         <f t="shared" ca="1" si="10"/>
-        <v>99</v>
-      </c>
-      <c r="M44" s="83" t="e" vm="92">
+        <v>98</v>
+      </c>
+      <c r="M44" s="83" t="e" vm="91">
         <f ca="1">_xlfn.XLOOKUP(I44,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="N44" s="83">
         <f t="shared" ca="1" si="10"/>
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="O44" s="192" t="str">
         <f t="shared" ca="1" si="11"/>
-        <v>Boise State</v>
-      </c>
-      <c r="P44" s="207" t="e" vm="89">
+        <v>Drake</v>
+      </c>
+      <c r="P44" s="207" t="e" vm="91">
         <f ca="1">_xlfn.XLOOKUP(O44,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -19904,15 +19904,15 @@
     <row r="45" spans="1:19" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="91" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>Bradley</v>
+        <v>Brigham Young</v>
       </c>
       <c r="B45" s="91" t="str">
         <f t="shared" ca="1" si="13"/>
-        <v>Brown</v>
+        <v>Bryant</v>
       </c>
       <c r="C45" s="91" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>Brown</v>
+        <v>Brigham Young</v>
       </c>
       <c r="D45" s="91" t="e">
         <f t="shared" si="9"/>
@@ -19923,44 +19923,44 @@
       </c>
       <c r="F45" s="147" cm="1">
         <f t="array" aca="1" ref="F45" ca="1">_xlfn.XLOOKUP(G45,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G45" s="148" t="str">
         <f ca="1">O19</f>
-        <v>Bradley</v>
+        <v>Brigham Young</v>
       </c>
       <c r="H45" s="184" t="s">
         <v>9</v>
       </c>
       <c r="I45" s="149" t="str">
         <f ca="1">O20</f>
-        <v>Brown</v>
+        <v>Bryant</v>
       </c>
       <c r="J45" s="150" cm="1">
         <f t="array" aca="1" ref="J45" ca="1">_xlfn.XLOOKUP(I45,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>2</v>
-      </c>
-      <c r="K45" s="151" t="e" vm="93">
+        <v>15</v>
+      </c>
+      <c r="K45" s="151" t="e" vm="94">
         <f ca="1">_xlfn.XLOOKUP(G45,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="L45" s="151">
         <f t="shared" ca="1" si="10"/>
-        <v>112</v>
-      </c>
-      <c r="M45" s="151" t="e" vm="95">
+        <v>110</v>
+      </c>
+      <c r="M45" s="151" t="e" vm="96">
         <f ca="1">_xlfn.XLOOKUP(I45,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="N45" s="151">
         <f t="shared" ca="1" si="10"/>
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="O45" s="197" t="str">
         <f t="shared" ca="1" si="11"/>
-        <v>Bradley</v>
-      </c>
-      <c r="P45" s="212" t="e" vm="93">
+        <v>Bryant</v>
+      </c>
+      <c r="P45" s="212" t="e" vm="96">
         <f ca="1">_xlfn.XLOOKUP(O45,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -19976,7 +19976,7 @@
     <row r="46" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="152" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>Bucknell</v>
+        <v>Buffalo</v>
       </c>
       <c r="B46" s="152" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -19995,11 +19995,11 @@
       </c>
       <c r="F46" s="130" cm="1">
         <f t="array" aca="1" ref="F46" ca="1">_xlfn.XLOOKUP(G46,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G46" s="131" t="str">
         <f ca="1">O21</f>
-        <v>Bucknell</v>
+        <v>Buffalo</v>
       </c>
       <c r="H46" s="181" t="s">
         <v>9</v>
@@ -20012,13 +20012,13 @@
         <f t="array" aca="1" ref="J46" ca="1">_xlfn.XLOOKUP(I46,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
         <v>9</v>
       </c>
-      <c r="K46" s="84" t="e" vm="97">
+      <c r="K46" s="84" t="e" vm="98">
         <f ca="1">_xlfn.XLOOKUP(G46,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="L46" s="84">
         <f t="shared" ca="1" si="10"/>
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="M46" s="84" t="e" vm="100">
         <f ca="1">_xlfn.XLOOKUP(I46,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -20026,13 +20026,13 @@
       </c>
       <c r="N46" s="84">
         <f t="shared" ca="1" si="10"/>
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="O46" s="194" t="str">
         <f t="shared" ca="1" si="11"/>
-        <v>Bucknell</v>
-      </c>
-      <c r="P46" s="209" t="e" vm="97">
+        <v>Buffalo</v>
+      </c>
+      <c r="P46" s="209" t="e" vm="98">
         <f ca="1">_xlfn.XLOOKUP(O46,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -20041,22 +20041,22 @@
       </c>
       <c r="R46" s="6" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S46" s="98"/>
     </row>
     <row r="47" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="152" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>Cal State Bakersfield</v>
+        <v>Cal State Fullerton</v>
       </c>
       <c r="B47" s="152" t="str">
         <f t="shared" ca="1" si="13"/>
-        <v>California</v>
+        <v>Cal State Northridge</v>
       </c>
       <c r="C47" s="152" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>Cal State Bakersfield</v>
+        <v>Cal State Fullerton</v>
       </c>
       <c r="D47" s="152" t="e">
         <f t="shared" si="9"/>
@@ -20067,44 +20067,44 @@
       </c>
       <c r="F47" s="100" cm="1">
         <f t="array" aca="1" ref="F47" ca="1">_xlfn.XLOOKUP(G47,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G47" s="101" t="str">
         <f ca="1">O23</f>
-        <v>Cal State Bakersfield</v>
+        <v>Cal State Fullerton</v>
       </c>
       <c r="H47" s="176" t="s">
         <v>9</v>
       </c>
       <c r="I47" s="102" t="str">
         <f ca="1">O24</f>
-        <v>California</v>
+        <v>Cal State Northridge</v>
       </c>
       <c r="J47" s="103" cm="1">
         <f t="array" aca="1" ref="J47" ca="1">_xlfn.XLOOKUP(I47,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>13</v>
-      </c>
-      <c r="K47" s="82" t="e" vm="101">
+        <v>4</v>
+      </c>
+      <c r="K47" s="82" t="e" vm="102">
         <f ca="1">_xlfn.XLOOKUP(G47,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="L47" s="82">
         <f t="shared" ca="1" si="10"/>
-        <v>103</v>
-      </c>
-      <c r="M47" s="82" t="e" vm="104">
+        <v>101</v>
+      </c>
+      <c r="M47" s="82" t="e" vm="103">
         <f ca="1">_xlfn.XLOOKUP(I47,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="N47" s="82">
         <f t="shared" ca="1" si="10"/>
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="O47" s="189" t="str">
         <f t="shared" ca="1" si="11"/>
-        <v>California</v>
-      </c>
-      <c r="P47" s="204" t="e" vm="104">
+        <v>Cal State Northridge</v>
+      </c>
+      <c r="P47" s="204" t="e" vm="103">
         <f ca="1">_xlfn.XLOOKUP(O47,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -20113,14 +20113,14 @@
       </c>
       <c r="R47" s="6" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S47" s="98"/>
     </row>
     <row r="48" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="152" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>Campbell</v>
+        <v>California Baptist</v>
       </c>
       <c r="B48" s="152" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -20128,7 +20128,7 @@
       </c>
       <c r="C48" s="152" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>Central Arkansas</v>
+        <v>California Baptist</v>
       </c>
       <c r="D48" s="152" t="e">
         <f t="shared" si="9"/>
@@ -20139,11 +20139,11 @@
       </c>
       <c r="F48" s="100" cm="1">
         <f t="array" aca="1" ref="F48" ca="1">_xlfn.XLOOKUP(G48,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G48" s="101" t="str">
         <f ca="1">O25</f>
-        <v>Campbell</v>
+        <v>California Baptist</v>
       </c>
       <c r="H48" s="176" t="s">
         <v>9</v>
@@ -20156,13 +20156,13 @@
         <f t="array" aca="1" ref="J48" ca="1">_xlfn.XLOOKUP(I48,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
         <v>14</v>
       </c>
-      <c r="K48" s="82" t="e" vm="106">
+      <c r="K48" s="82" t="e" vm="105">
         <f ca="1">_xlfn.XLOOKUP(G48,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="L48" s="82">
         <f t="shared" ca="1" si="10"/>
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="M48" s="82" t="e" vm="108">
         <f ca="1">_xlfn.XLOOKUP(I48,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -20170,13 +20170,13 @@
       </c>
       <c r="N48" s="82">
         <f t="shared" ca="1" si="10"/>
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="O48" s="189" t="str">
         <f t="shared" ca="1" si="11"/>
-        <v>Campbell</v>
-      </c>
-      <c r="P48" s="204" t="e" vm="106">
+        <v>Central Arkansas</v>
+      </c>
+      <c r="P48" s="204" t="e" vm="108">
         <f ca="1">_xlfn.XLOOKUP(O48,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -20185,7 +20185,7 @@
       </c>
       <c r="R48" s="6" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S48" s="98"/>
     </row>
@@ -20234,7 +20234,7 @@
       </c>
       <c r="L49" s="139">
         <f t="shared" ca="1" si="10"/>
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M49" s="139" t="e" vm="111">
         <f ca="1">_xlfn.XLOOKUP(I49,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -20242,7 +20242,7 @@
       </c>
       <c r="N49" s="139">
         <f t="shared" ca="1" si="10"/>
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="O49" s="195" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -20264,7 +20264,7 @@
     <row r="50" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="91" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>Chicago State</v>
+        <v>Chattanooga</v>
       </c>
       <c r="B50" s="91" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -20283,11 +20283,11 @@
       </c>
       <c r="F50" s="141" cm="1">
         <f t="array" aca="1" ref="F50" ca="1">_xlfn.XLOOKUP(G50,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="G50" s="142" t="str">
         <f ca="1">O29</f>
-        <v>Chicago State</v>
+        <v>Chattanooga</v>
       </c>
       <c r="H50" s="183" t="s">
         <v>9</v>
@@ -20300,13 +20300,13 @@
         <f t="array" aca="1" ref="J50" ca="1">_xlfn.XLOOKUP(I50,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
         <v>9</v>
       </c>
-      <c r="K50" s="145" t="e" vm="114">
+      <c r="K50" s="145" t="e" vm="113">
         <f ca="1">_xlfn.XLOOKUP(G50,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="L50" s="145">
         <f t="shared" ca="1" si="10"/>
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="M50" s="145" t="e" vm="116">
         <f ca="1">_xlfn.XLOOKUP(I50,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -20314,13 +20314,13 @@
       </c>
       <c r="N50" s="145">
         <f t="shared" ca="1" si="10"/>
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="O50" s="196" t="str">
         <f t="shared" ca="1" si="11"/>
-        <v>Chicago State</v>
-      </c>
-      <c r="P50" s="211" t="e" vm="114">
+        <v>Chattanooga</v>
+      </c>
+      <c r="P50" s="211" t="e" vm="113">
         <f ca="1">_xlfn.XLOOKUP(O50,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -20329,14 +20329,14 @@
       </c>
       <c r="R50" s="6" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S50" s="98"/>
     </row>
     <row r="51" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="91" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>Coastal Carolina</v>
+        <v>Cleveland State</v>
       </c>
       <c r="B51" s="91" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -20355,11 +20355,11 @@
       </c>
       <c r="F51" s="117" cm="1">
         <f t="array" aca="1" ref="F51" ca="1">_xlfn.XLOOKUP(G51,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G51" s="118" t="str">
         <f ca="1">O31</f>
-        <v>Coastal Carolina</v>
+        <v>Cleveland State</v>
       </c>
       <c r="H51" s="178" t="s">
         <v>9</v>
@@ -20372,13 +20372,13 @@
         <f t="array" aca="1" ref="J51" ca="1">_xlfn.XLOOKUP(I51,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
         <v>4</v>
       </c>
-      <c r="K51" s="83" t="e" vm="118">
+      <c r="K51" s="83" t="e" vm="117">
         <f ca="1">_xlfn.XLOOKUP(G51,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="L51" s="83">
         <f t="shared" ca="1" si="10"/>
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="M51" s="83" t="e" vm="119">
         <f ca="1">_xlfn.XLOOKUP(I51,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -20386,13 +20386,13 @@
       </c>
       <c r="N51" s="83">
         <f t="shared" ca="1" si="10"/>
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="O51" s="192" t="str">
         <f t="shared" ca="1" si="11"/>
-        <v>Coastal Carolina</v>
-      </c>
-      <c r="P51" s="207" t="e" vm="118">
+        <v>Cleveland State</v>
+      </c>
+      <c r="P51" s="207" t="e" vm="117">
         <f ca="1">_xlfn.XLOOKUP(O51,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -20412,11 +20412,11 @@
       </c>
       <c r="B52" s="91" t="str">
         <f t="shared" ca="1" si="13"/>
-        <v>Connecticut</v>
+        <v>Columbia</v>
       </c>
       <c r="C52" s="91" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>Connecticut</v>
+        <v>Colorado State</v>
       </c>
       <c r="D52" s="91" t="e">
         <f t="shared" si="9"/>
@@ -20438,11 +20438,11 @@
       </c>
       <c r="I52" s="119" t="str">
         <f ca="1">O34</f>
-        <v>Connecticut</v>
+        <v>Columbia</v>
       </c>
       <c r="J52" s="120" cm="1">
         <f t="array" aca="1" ref="J52" ca="1">_xlfn.XLOOKUP(I52,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="K52" s="83" t="e" vm="122">
         <f ca="1">_xlfn.XLOOKUP(G52,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -20450,21 +20450,21 @@
       </c>
       <c r="L52" s="83">
         <f t="shared" ca="1" si="10"/>
-        <v>112</v>
-      </c>
-      <c r="M52" s="83" t="e" vm="124">
+        <v>96</v>
+      </c>
+      <c r="M52" s="83" t="e" vm="123">
         <f ca="1">_xlfn.XLOOKUP(I52,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="N52" s="83">
         <f t="shared" ca="1" si="10"/>
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="O52" s="192" t="str">
         <f t="shared" ca="1" si="11"/>
-        <v>Colorado State</v>
-      </c>
-      <c r="P52" s="207" t="e" vm="122">
+        <v>Columbia</v>
+      </c>
+      <c r="P52" s="207" t="e" vm="123">
         <f ca="1">_xlfn.XLOOKUP(O52,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -20480,15 +20480,15 @@
     <row r="53" spans="1:19" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="91" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>Cornell</v>
+        <v>Coppin State</v>
       </c>
       <c r="B53" s="91" t="str">
         <f t="shared" ca="1" si="13"/>
-        <v>Dartmouth</v>
+        <v>Creighton</v>
       </c>
       <c r="C53" s="91" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>Dartmouth</v>
+        <v>Creighton</v>
       </c>
       <c r="D53" s="91" t="e">
         <f t="shared" si="9"/>
@@ -20499,44 +20499,44 @@
       </c>
       <c r="F53" s="147" cm="1">
         <f t="array" aca="1" ref="F53" ca="1">_xlfn.XLOOKUP(G53,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G53" s="148" t="str">
         <f ca="1">O35</f>
-        <v>Cornell</v>
+        <v>Coppin State</v>
       </c>
       <c r="H53" s="184" t="s">
         <v>9</v>
       </c>
       <c r="I53" s="149" t="str">
         <f ca="1">O36</f>
-        <v>Dartmouth</v>
+        <v>Creighton</v>
       </c>
       <c r="J53" s="150" cm="1">
         <f t="array" aca="1" ref="J53" ca="1">_xlfn.XLOOKUP(I53,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>15</v>
-      </c>
-      <c r="K53" s="151" t="e" vm="126">
+        <v>2</v>
+      </c>
+      <c r="K53" s="151" t="e" vm="125">
         <f ca="1">_xlfn.XLOOKUP(G53,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="L53" s="151">
         <f t="shared" ca="1" si="10"/>
-        <v>110</v>
-      </c>
-      <c r="M53" s="151" t="e" vm="128">
+        <v>105</v>
+      </c>
+      <c r="M53" s="151" t="e" vm="127">
         <f ca="1">_xlfn.XLOOKUP(I53,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="N53" s="151">
         <f t="shared" ca="1" si="10"/>
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="O53" s="197" t="str">
         <f t="shared" ca="1" si="11"/>
-        <v>Cornell</v>
-      </c>
-      <c r="P53" s="212" t="e" vm="126">
+        <v>Coppin State</v>
+      </c>
+      <c r="P53" s="212" t="e" vm="125">
         <f ca="1">_xlfn.XLOOKUP(O53,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -20545,7 +20545,7 @@
       </c>
       <c r="R53" s="6" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S53" s="98"/>
     </row>
@@ -20575,15 +20575,15 @@
     <row r="55" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="91" t="str">
         <f ca="1">G55</f>
-        <v>Akron</v>
+        <v>Air Force</v>
       </c>
       <c r="B55" s="91" t="str">
         <f ca="1">I55</f>
-        <v>Alabama State</v>
+        <v>Alcorn State</v>
       </c>
       <c r="C55" s="91" t="str">
         <f t="shared" ref="C55:C62" ca="1" si="14">IF(O55="","",IF(A55=O55,B55,A55))</f>
-        <v>Akron</v>
+        <v>Air Force</v>
       </c>
       <c r="D55" s="91" t="e">
         <f t="shared" ref="D55:D62" si="15">IF(SeedType=1,0,IF(SeedType=2,VLOOKUP(O55,SeedInfo,2,FALSE)*3,MAX(VLOOKUP(O55,SeedInfo,2,FALSE)-VLOOKUP(C55,SeedInfo,2,FALSE),0)))</f>
@@ -20594,44 +20594,44 @@
       </c>
       <c r="F55" s="93" cm="1">
         <f t="array" aca="1" ref="F55" ca="1">_xlfn.XLOOKUP(G55,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G55" s="94" t="str">
         <f ca="1">O38</f>
-        <v>Akron</v>
+        <v>Air Force</v>
       </c>
       <c r="H55" s="175" t="s">
         <v>9</v>
       </c>
       <c r="I55" s="95" t="str">
         <f ca="1">O39</f>
-        <v>Alabama State</v>
+        <v>Alcorn State</v>
       </c>
       <c r="J55" s="96" cm="1">
         <f t="array" aca="1" ref="J55" ca="1">_xlfn.XLOOKUP(I55,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>12</v>
-      </c>
-      <c r="K55" s="97" t="e" vm="67">
+        <v>13</v>
+      </c>
+      <c r="K55" s="97" t="e" vm="66">
         <f ca="1">_xlfn.XLOOKUP(G55,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="L55" s="97">
         <f t="shared" ca="1" si="10"/>
-        <v>109</v>
-      </c>
-      <c r="M55" s="97" t="e" vm="70">
+        <v>101</v>
+      </c>
+      <c r="M55" s="97" t="e" vm="72">
         <f ca="1">_xlfn.XLOOKUP(I55,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="N55" s="97">
         <f t="shared" ca="1" si="10"/>
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="O55" s="188" t="str">
         <f t="shared" ref="O55:O62" ca="1" si="16">IF(L55&gt;N55,G55,I55)</f>
-        <v>Alabama State</v>
-      </c>
-      <c r="P55" s="204" t="e" vm="70">
+        <v>Alcorn State</v>
+      </c>
+      <c r="P55" s="204" t="e" vm="72">
         <f ca="1">_xlfn.XLOOKUP(O55,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -20640,22 +20640,22 @@
       </c>
       <c r="R55" s="6" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S55" s="98"/>
     </row>
     <row r="56" spans="1:19" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="91" t="str">
         <f t="shared" ref="A56:A62" ca="1" si="17">G56</f>
-        <v>American</v>
+        <v>Arizona</v>
       </c>
       <c r="B56" s="91" t="str">
         <f t="shared" ref="B56:B62" ca="1" si="18">I56</f>
-        <v>Arkansas State</v>
+        <v>Arkansas</v>
       </c>
       <c r="C56" s="91" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>Arkansas State</v>
+        <v>Arkansas</v>
       </c>
       <c r="D56" s="91" t="e">
         <f t="shared" si="15"/>
@@ -20666,44 +20666,44 @@
       </c>
       <c r="F56" s="135" cm="1">
         <f t="array" aca="1" ref="F56" ca="1">_xlfn.XLOOKUP(G56,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G56" s="136" t="str">
         <f ca="1">O40</f>
-        <v>American</v>
+        <v>Arizona</v>
       </c>
       <c r="H56" s="182" t="s">
         <v>9</v>
       </c>
       <c r="I56" s="137" t="str">
         <f ca="1">O41</f>
-        <v>Arkansas State</v>
+        <v>Arkansas</v>
       </c>
       <c r="J56" s="138" cm="1">
         <f t="array" aca="1" ref="J56" ca="1">_xlfn.XLOOKUP(I56,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>10</v>
-      </c>
-      <c r="K56" s="139" t="e" vm="73">
+        <v>7</v>
+      </c>
+      <c r="K56" s="139" t="e" vm="75">
         <f ca="1">_xlfn.XLOOKUP(G56,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="L56" s="139">
         <f t="shared" ca="1" si="10"/>
-        <v>99</v>
-      </c>
-      <c r="M56" s="139" t="e" vm="78">
+        <v>103</v>
+      </c>
+      <c r="M56" s="139" t="e" vm="77">
         <f ca="1">_xlfn.XLOOKUP(I56,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="N56" s="139">
         <f t="shared" ca="1" si="10"/>
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="O56" s="195" t="str">
         <f t="shared" ca="1" si="16"/>
-        <v>American</v>
-      </c>
-      <c r="P56" s="210" t="e" vm="73">
+        <v>Arizona</v>
+      </c>
+      <c r="P56" s="210" t="e" vm="75">
         <f ca="1">_xlfn.XLOOKUP(O56,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -20723,7 +20723,7 @@
       </c>
       <c r="B57" s="91" t="str">
         <f t="shared" ca="1" si="18"/>
-        <v>Belmont</v>
+        <v>Binghamton</v>
       </c>
       <c r="C57" s="91" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -20749,11 +20749,11 @@
       </c>
       <c r="I57" s="143" t="str">
         <f ca="1">O43</f>
-        <v>Belmont</v>
+        <v>Binghamton</v>
       </c>
       <c r="J57" s="144" cm="1">
         <f t="array" aca="1" ref="J57" ca="1">_xlfn.XLOOKUP(I57,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K57" s="145" t="e" vm="83">
         <f ca="1">_xlfn.XLOOKUP(G57,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -20761,21 +20761,21 @@
       </c>
       <c r="L57" s="145">
         <f t="shared" ca="1" si="10"/>
-        <v>101</v>
-      </c>
-      <c r="M57" s="145" t="e" vm="86">
+        <v>91</v>
+      </c>
+      <c r="M57" s="145" t="e" vm="88">
         <f ca="1">_xlfn.XLOOKUP(I57,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="N57" s="145">
         <f t="shared" ca="1" si="10"/>
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="O57" s="196" t="str">
         <f t="shared" ca="1" si="16"/>
-        <v>Belmont</v>
-      </c>
-      <c r="P57" s="211" t="e" vm="86">
+        <v>Binghamton</v>
+      </c>
+      <c r="P57" s="211" t="e" vm="88">
         <f ca="1">_xlfn.XLOOKUP(O57,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -20791,15 +20791,15 @@
     <row r="58" spans="1:19" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="91" t="str">
         <f t="shared" ca="1" si="17"/>
-        <v>Boise State</v>
+        <v>Drake</v>
       </c>
       <c r="B58" s="91" t="str">
         <f t="shared" ca="1" si="18"/>
-        <v>Bradley</v>
+        <v>Bryant</v>
       </c>
       <c r="C58" s="91" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>Boise State</v>
+        <v>Bryant</v>
       </c>
       <c r="D58" s="91" t="e">
         <f t="shared" si="15"/>
@@ -20810,44 +20810,44 @@
       </c>
       <c r="F58" s="235" cm="1">
         <f t="array" aca="1" ref="F58" ca="1">_xlfn.XLOOKUP(G58,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G58" s="148" t="str">
         <f ca="1">O44</f>
-        <v>Boise State</v>
+        <v>Drake</v>
       </c>
       <c r="H58" s="184" t="s">
         <v>9</v>
       </c>
       <c r="I58" s="149" t="str">
         <f ca="1">O45</f>
-        <v>Bradley</v>
+        <v>Bryant</v>
       </c>
       <c r="J58" s="150" cm="1">
         <f t="array" aca="1" ref="J58" ca="1">_xlfn.XLOOKUP(I58,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>7</v>
-      </c>
-      <c r="K58" s="151" t="e" vm="89">
+        <v>15</v>
+      </c>
+      <c r="K58" s="151" t="e" vm="91">
         <f ca="1">_xlfn.XLOOKUP(G58,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="L58" s="151">
         <f t="shared" ca="1" si="10"/>
-        <v>104</v>
-      </c>
-      <c r="M58" s="151" t="e" vm="93">
+        <v>105</v>
+      </c>
+      <c r="M58" s="151" t="e" vm="96">
         <f ca="1">_xlfn.XLOOKUP(I58,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="N58" s="151">
         <f t="shared" ca="1" si="10"/>
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="O58" s="197" t="str">
         <f t="shared" ca="1" si="16"/>
-        <v>Bradley</v>
-      </c>
-      <c r="P58" s="212" t="e" vm="93">
+        <v>Drake</v>
+      </c>
+      <c r="P58" s="212" t="e" vm="91">
         <f ca="1">_xlfn.XLOOKUP(O58,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -20856,22 +20856,22 @@
       </c>
       <c r="R58" s="6" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S58" s="98"/>
     </row>
     <row r="59" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="152" t="str">
         <f t="shared" ca="1" si="17"/>
-        <v>Bucknell</v>
+        <v>Buffalo</v>
       </c>
       <c r="B59" s="152" t="str">
         <f t="shared" ca="1" si="18"/>
-        <v>California</v>
+        <v>Cal State Northridge</v>
       </c>
       <c r="C59" s="152" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>California</v>
+        <v>Buffalo</v>
       </c>
       <c r="D59" s="152" t="e">
         <f t="shared" si="15"/>
@@ -20882,44 +20882,44 @@
       </c>
       <c r="F59" s="130" cm="1">
         <f t="array" aca="1" ref="F59" ca="1">_xlfn.XLOOKUP(G59,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G59" s="131" t="str">
         <f ca="1">O46</f>
-        <v>Bucknell</v>
+        <v>Buffalo</v>
       </c>
       <c r="H59" s="181" t="s">
         <v>9</v>
       </c>
       <c r="I59" s="132" t="str">
         <f ca="1">O47</f>
-        <v>California</v>
+        <v>Cal State Northridge</v>
       </c>
       <c r="J59" s="133" cm="1">
         <f t="array" aca="1" ref="J59" ca="1">_xlfn.XLOOKUP(I59,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>13</v>
-      </c>
-      <c r="K59" s="84" t="e" vm="97">
+        <v>4</v>
+      </c>
+      <c r="K59" s="84" t="e" vm="98">
         <f ca="1">_xlfn.XLOOKUP(G59,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="L59" s="84">
         <f t="shared" ca="1" si="10"/>
-        <v>104</v>
-      </c>
-      <c r="M59" s="84" t="e" vm="104">
+        <v>98</v>
+      </c>
+      <c r="M59" s="84" t="e" vm="103">
         <f ca="1">_xlfn.XLOOKUP(I59,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="N59" s="84">
         <f t="shared" ca="1" si="10"/>
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="O59" s="194" t="str">
         <f t="shared" ca="1" si="16"/>
-        <v>Bucknell</v>
-      </c>
-      <c r="P59" s="209" t="e" vm="97">
+        <v>Cal State Northridge</v>
+      </c>
+      <c r="P59" s="209" t="e" vm="103">
         <f ca="1">_xlfn.XLOOKUP(O59,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -20935,7 +20935,7 @@
     <row r="60" spans="1:19" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="152" t="str">
         <f t="shared" ca="1" si="17"/>
-        <v>Campbell</v>
+        <v>Central Arkansas</v>
       </c>
       <c r="B60" s="152" t="str">
         <f t="shared" ca="1" si="18"/>
@@ -20943,7 +20943,7 @@
       </c>
       <c r="C60" s="152" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>Campbell</v>
+        <v>Charleston Southern</v>
       </c>
       <c r="D60" s="152" t="e">
         <f t="shared" si="15"/>
@@ -20954,11 +20954,11 @@
       </c>
       <c r="F60" s="135" cm="1">
         <f t="array" aca="1" ref="F60" ca="1">_xlfn.XLOOKUP(G60,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G60" s="136" t="str">
         <f ca="1">O48</f>
-        <v>Campbell</v>
+        <v>Central Arkansas</v>
       </c>
       <c r="H60" s="182" t="s">
         <v>9</v>
@@ -20971,13 +20971,13 @@
         <f t="array" aca="1" ref="J60" ca="1">_xlfn.XLOOKUP(I60,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
         <v>2</v>
       </c>
-      <c r="K60" s="139" t="e" vm="106">
+      <c r="K60" s="139" t="e" vm="108">
         <f ca="1">_xlfn.XLOOKUP(G60,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="L60" s="139">
         <f t="shared" ca="1" si="10"/>
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="M60" s="139" t="e" vm="111">
         <f ca="1">_xlfn.XLOOKUP(I60,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -20985,13 +20985,13 @@
       </c>
       <c r="N60" s="139">
         <f t="shared" ca="1" si="10"/>
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="O60" s="195" t="str">
         <f t="shared" ca="1" si="16"/>
-        <v>Charleston Southern</v>
-      </c>
-      <c r="P60" s="210" t="e" vm="111">
+        <v>Central Arkansas</v>
+      </c>
+      <c r="P60" s="210" t="e" vm="108">
         <f ca="1">_xlfn.XLOOKUP(O60,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -21000,22 +21000,22 @@
       </c>
       <c r="R60" s="6" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S60" s="98"/>
     </row>
     <row r="61" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="91" t="str">
         <f t="shared" ca="1" si="17"/>
-        <v>Chicago State</v>
+        <v>Chattanooga</v>
       </c>
       <c r="B61" s="91" t="str">
         <f t="shared" ca="1" si="18"/>
-        <v>Coastal Carolina</v>
+        <v>Cleveland State</v>
       </c>
       <c r="C61" s="91" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>Chicago State</v>
+        <v>Chattanooga</v>
       </c>
       <c r="D61" s="91" t="e">
         <f t="shared" si="15"/>
@@ -21026,44 +21026,44 @@
       </c>
       <c r="F61" s="141" cm="1">
         <f t="array" aca="1" ref="F61" ca="1">_xlfn.XLOOKUP(G61,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="G61" s="142" t="str">
         <f ca="1">O50</f>
-        <v>Chicago State</v>
+        <v>Chattanooga</v>
       </c>
       <c r="H61" s="183" t="s">
         <v>9</v>
       </c>
       <c r="I61" s="143" t="str">
         <f ca="1">O51</f>
-        <v>Coastal Carolina</v>
+        <v>Cleveland State</v>
       </c>
       <c r="J61" s="144" cm="1">
         <f t="array" aca="1" ref="J61" ca="1">_xlfn.XLOOKUP(I61,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>12</v>
-      </c>
-      <c r="K61" s="145" t="e" vm="114">
+        <v>5</v>
+      </c>
+      <c r="K61" s="145" t="e" vm="113">
         <f ca="1">_xlfn.XLOOKUP(G61,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="L61" s="145">
         <f t="shared" ca="1" si="10"/>
-        <v>102</v>
-      </c>
-      <c r="M61" s="145" t="e" vm="118">
+        <v>96</v>
+      </c>
+      <c r="M61" s="145" t="e" vm="117">
         <f ca="1">_xlfn.XLOOKUP(I61,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="N61" s="145">
         <f t="shared" ca="1" si="10"/>
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="O61" s="196" t="str">
         <f t="shared" ca="1" si="16"/>
-        <v>Coastal Carolina</v>
-      </c>
-      <c r="P61" s="211" t="e" vm="118">
+        <v>Cleveland State</v>
+      </c>
+      <c r="P61" s="211" t="e" vm="117">
         <f ca="1">_xlfn.XLOOKUP(O61,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -21072,22 +21072,22 @@
       </c>
       <c r="R61" s="6" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S61" s="98"/>
     </row>
     <row r="62" spans="1:19" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="91" t="str">
         <f t="shared" ca="1" si="17"/>
-        <v>Colorado State</v>
+        <v>Columbia</v>
       </c>
       <c r="B62" s="91" t="str">
         <f t="shared" ca="1" si="18"/>
-        <v>Cornell</v>
+        <v>Coppin State</v>
       </c>
       <c r="C62" s="91" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>Cornell</v>
+        <v>Coppin State</v>
       </c>
       <c r="D62" s="91" t="e">
         <f t="shared" si="15"/>
@@ -21098,44 +21098,44 @@
       </c>
       <c r="F62" s="147" cm="1">
         <f t="array" aca="1" ref="F62" ca="1">_xlfn.XLOOKUP(G62,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G62" s="148" t="str">
         <f ca="1">O52</f>
-        <v>Colorado State</v>
+        <v>Columbia</v>
       </c>
       <c r="H62" s="184" t="s">
         <v>9</v>
       </c>
       <c r="I62" s="149" t="str">
         <f ca="1">O53</f>
-        <v>Cornell</v>
+        <v>Coppin State</v>
       </c>
       <c r="J62" s="150" cm="1">
         <f t="array" aca="1" ref="J62" ca="1">_xlfn.XLOOKUP(I62,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>10</v>
-      </c>
-      <c r="K62" s="151" t="e" vm="122">
+        <v>7</v>
+      </c>
+      <c r="K62" s="151" t="e" vm="123">
         <f ca="1">_xlfn.XLOOKUP(G62,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="L62" s="151">
         <f t="shared" ca="1" si="10"/>
-        <v>107</v>
-      </c>
-      <c r="M62" s="151" t="e" vm="126">
+        <v>109</v>
+      </c>
+      <c r="M62" s="151" t="e" vm="125">
         <f ca="1">_xlfn.XLOOKUP(I62,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="N62" s="151">
         <f t="shared" ca="1" si="10"/>
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O62" s="197" t="str">
         <f t="shared" ca="1" si="16"/>
-        <v>Colorado State</v>
-      </c>
-      <c r="P62" s="212" t="e" vm="122">
+        <v>Columbia</v>
+      </c>
+      <c r="P62" s="212" t="e" vm="123">
         <f ca="1">_xlfn.XLOOKUP(O62,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -21144,7 +21144,7 @@
       </c>
       <c r="R62" s="6" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S62" s="98"/>
     </row>
@@ -21174,15 +21174,15 @@
     <row r="64" spans="1:19" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="91" t="str">
         <f ca="1">G64</f>
-        <v>Alabama State</v>
+        <v>Alcorn State</v>
       </c>
       <c r="B64" s="91" t="str">
         <f ca="1">I64</f>
-        <v>American</v>
+        <v>Arizona</v>
       </c>
       <c r="C64" s="91" t="str">
         <f ca="1">IF(O64="","",IF(A64=O64,B64,A64))</f>
-        <v>Alabama State</v>
+        <v>Alcorn State</v>
       </c>
       <c r="D64" s="91" t="e">
         <f>IF(SeedType=1,0,IF(SeedType=2,VLOOKUP(O64,SeedInfo,2,FALSE)*4,MAX(VLOOKUP(O64,SeedInfo,2,FALSE)-VLOOKUP(C64,SeedInfo,2,FALSE),0)))</f>
@@ -21193,44 +21193,44 @@
       </c>
       <c r="F64" s="154" cm="1">
         <f t="array" aca="1" ref="F64" ca="1">_xlfn.XLOOKUP(G64,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G64" s="155" t="str">
         <f ca="1">O55</f>
-        <v>Alabama State</v>
+        <v>Alcorn State</v>
       </c>
       <c r="H64" s="185" t="s">
         <v>9</v>
       </c>
       <c r="I64" s="156" t="str">
         <f ca="1">O56</f>
-        <v>American</v>
+        <v>Arizona</v>
       </c>
       <c r="J64" s="157" cm="1">
         <f t="array" aca="1" ref="J64" ca="1">_xlfn.XLOOKUP(I64,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>6</v>
-      </c>
-      <c r="K64" s="158" t="e" vm="70">
+        <v>3</v>
+      </c>
+      <c r="K64" s="158" t="e" vm="72">
         <f ca="1">_xlfn.XLOOKUP(G64,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="L64" s="158">
         <f t="shared" ca="1" si="10"/>
-        <v>92</v>
-      </c>
-      <c r="M64" s="158" t="e" vm="73">
+        <v>99</v>
+      </c>
+      <c r="M64" s="158" t="e" vm="75">
         <f ca="1">_xlfn.XLOOKUP(I64,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="N64" s="158">
         <f t="shared" ca="1" si="10"/>
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="O64" s="198" t="str">
         <f ca="1">IF(L64&gt;N64,G64,I64)</f>
-        <v>American</v>
-      </c>
-      <c r="P64" s="204" t="e" vm="73">
+        <v>Arizona</v>
+      </c>
+      <c r="P64" s="204" t="e" vm="75">
         <f ca="1">_xlfn.XLOOKUP(O64,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -21246,15 +21246,15 @@
     <row r="65" spans="1:19" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="91" t="str">
         <f ca="1">G65</f>
-        <v>Belmont</v>
+        <v>Binghamton</v>
       </c>
       <c r="B65" s="91" t="str">
         <f ca="1">I65</f>
-        <v>Bradley</v>
+        <v>Drake</v>
       </c>
       <c r="C65" s="91" t="str">
         <f ca="1">IF(O65="","",IF(A65=O65,B65,A65))</f>
-        <v>Belmont</v>
+        <v>Binghamton</v>
       </c>
       <c r="D65" s="91" t="e">
         <f>IF(SeedType=1,0,IF(SeedType=2,VLOOKUP(O65,SeedInfo,2,FALSE)*4,MAX(VLOOKUP(O65,SeedInfo,2,FALSE)-VLOOKUP(C65,SeedInfo,2,FALSE),0)))</f>
@@ -21265,44 +21265,44 @@
       </c>
       <c r="F65" s="160" cm="1">
         <f t="array" aca="1" ref="F65" ca="1">_xlfn.XLOOKUP(G65,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G65" s="161" t="str">
         <f ca="1">O57</f>
-        <v>Belmont</v>
+        <v>Binghamton</v>
       </c>
       <c r="H65" s="186" t="s">
         <v>9</v>
       </c>
       <c r="I65" s="162" t="str">
         <f ca="1">O58</f>
-        <v>Bradley</v>
+        <v>Drake</v>
       </c>
       <c r="J65" s="163" cm="1">
         <f t="array" aca="1" ref="J65" ca="1">_xlfn.XLOOKUP(I65,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>7</v>
-      </c>
-      <c r="K65" s="164" t="e" vm="86">
+        <v>3</v>
+      </c>
+      <c r="K65" s="164" t="e" vm="88">
         <f ca="1">_xlfn.XLOOKUP(G65,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="L65" s="164">
         <f t="shared" ca="1" si="10"/>
-        <v>100</v>
-      </c>
-      <c r="M65" s="164" t="e" vm="93">
+        <v>95</v>
+      </c>
+      <c r="M65" s="164" t="e" vm="91">
         <f ca="1">_xlfn.XLOOKUP(I65,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="N65" s="164">
         <f t="shared" ca="1" si="10"/>
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="O65" s="199" t="str">
         <f ca="1">IF(L65&gt;N65,G65,I65)</f>
-        <v>Bradley</v>
-      </c>
-      <c r="P65" s="207" t="e" vm="93">
+        <v>Drake</v>
+      </c>
+      <c r="P65" s="207" t="e" vm="91">
         <f ca="1">_xlfn.XLOOKUP(O65,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -21318,15 +21318,15 @@
     <row r="66" spans="1:19" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="91" t="str">
         <f ca="1">G66</f>
-        <v>Bucknell</v>
+        <v>Cal State Northridge</v>
       </c>
       <c r="B66" s="91" t="str">
         <f ca="1">I66</f>
-        <v>Charleston Southern</v>
+        <v>Central Arkansas</v>
       </c>
       <c r="C66" s="91" t="str">
         <f ca="1">IF(O66="","",IF(A66=O66,B66,A66))</f>
-        <v>Charleston Southern</v>
+        <v>Cal State Northridge</v>
       </c>
       <c r="D66" s="91" t="e">
         <f>IF(SeedType=1,0,IF(SeedType=2,VLOOKUP(O66,SeedInfo,2,FALSE)*4,MAX(VLOOKUP(O66,SeedInfo,2,FALSE)-VLOOKUP(C66,SeedInfo,2,FALSE),0)))</f>
@@ -21337,44 +21337,44 @@
       </c>
       <c r="F66" s="154" cm="1">
         <f t="array" aca="1" ref="F66" ca="1">_xlfn.XLOOKUP(G66,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G66" s="155" t="str">
         <f ca="1">O59</f>
-        <v>Bucknell</v>
+        <v>Cal State Northridge</v>
       </c>
       <c r="H66" s="185" t="s">
         <v>9</v>
       </c>
       <c r="I66" s="156" t="str">
         <f ca="1">O60</f>
-        <v>Charleston Southern</v>
+        <v>Central Arkansas</v>
       </c>
       <c r="J66" s="157" cm="1">
         <f t="array" aca="1" ref="J66" ca="1">_xlfn.XLOOKUP(I66,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>2</v>
-      </c>
-      <c r="K66" s="158" t="e" vm="97">
+        <v>14</v>
+      </c>
+      <c r="K66" s="158" t="e" vm="103">
         <f ca="1">_xlfn.XLOOKUP(G66,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="L66" s="158">
         <f t="shared" ca="1" si="10"/>
-        <v>120</v>
-      </c>
-      <c r="M66" s="158" t="e" vm="111">
+        <v>109</v>
+      </c>
+      <c r="M66" s="158" t="e" vm="108">
         <f ca="1">_xlfn.XLOOKUP(I66,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="N66" s="158">
         <f t="shared" ca="1" si="10"/>
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="O66" s="198" t="str">
         <f ca="1">IF(L66&gt;N66,G66,I66)</f>
-        <v>Bucknell</v>
-      </c>
-      <c r="P66" s="204" t="e" vm="97">
+        <v>Central Arkansas</v>
+      </c>
+      <c r="P66" s="204" t="e" vm="108">
         <f ca="1">_xlfn.XLOOKUP(O66,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -21383,22 +21383,22 @@
       </c>
       <c r="R66" s="6" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S66" s="98"/>
     </row>
     <row r="67" spans="1:19" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="91" t="str">
         <f ca="1">G67</f>
-        <v>Coastal Carolina</v>
+        <v>Cleveland State</v>
       </c>
       <c r="B67" s="91" t="str">
         <f ca="1">I67</f>
-        <v>Colorado State</v>
+        <v>Columbia</v>
       </c>
       <c r="C67" s="91" t="str">
         <f ca="1">IF(O67="","",IF(A67=O67,B67,A67))</f>
-        <v>Coastal Carolina</v>
+        <v>Cleveland State</v>
       </c>
       <c r="D67" s="91" t="e">
         <f>IF(SeedType=1,0,IF(SeedType=2,VLOOKUP(O67,SeedInfo,2,FALSE)*4,MAX(VLOOKUP(O67,SeedInfo,2,FALSE)-VLOOKUP(C67,SeedInfo,2,FALSE),0)))</f>
@@ -21409,44 +21409,44 @@
       </c>
       <c r="F67" s="160" cm="1">
         <f t="array" aca="1" ref="F67" ca="1">_xlfn.XLOOKUP(G67,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G67" s="161" t="str">
         <f ca="1">O61</f>
-        <v>Coastal Carolina</v>
+        <v>Cleveland State</v>
       </c>
       <c r="H67" s="186" t="s">
         <v>9</v>
       </c>
       <c r="I67" s="162" t="str">
         <f ca="1">O62</f>
-        <v>Colorado State</v>
+        <v>Columbia</v>
       </c>
       <c r="J67" s="163" cm="1">
         <f t="array" aca="1" ref="J67" ca="1">_xlfn.XLOOKUP(I67,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>11</v>
-      </c>
-      <c r="K67" s="164" t="e" vm="118">
+        <v>3</v>
+      </c>
+      <c r="K67" s="164" t="e" vm="117">
         <f ca="1">_xlfn.XLOOKUP(G67,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="L67" s="164">
         <f t="shared" ca="1" si="10"/>
-        <v>99</v>
-      </c>
-      <c r="M67" s="164" t="e" vm="122">
+        <v>109</v>
+      </c>
+      <c r="M67" s="164" t="e" vm="123">
         <f ca="1">_xlfn.XLOOKUP(I67,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="N67" s="164">
         <f t="shared" ca="1" si="10"/>
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="O67" s="199" t="str">
         <f ca="1">IF(L67&gt;N67,G67,I67)</f>
-        <v>Colorado State</v>
-      </c>
-      <c r="P67" s="207" t="e" vm="122">
+        <v>Columbia</v>
+      </c>
+      <c r="P67" s="207" t="e" vm="123">
         <f ca="1">_xlfn.XLOOKUP(O67,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -21485,15 +21485,15 @@
     <row r="69" spans="1:19" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="91" t="str">
         <f ca="1">G69</f>
-        <v>American</v>
+        <v>Arizona</v>
       </c>
       <c r="B69" s="91" t="str">
         <f ca="1">I69</f>
-        <v>Bradley</v>
+        <v>Drake</v>
       </c>
       <c r="C69" s="91" t="str">
         <f ca="1">IF(O69="","",IF(A69=O69,B69,A69))</f>
-        <v>Bradley</v>
+        <v>Drake</v>
       </c>
       <c r="D69" s="91" t="e">
         <f>IF(SeedType=1,0,IF(SeedType=2,VLOOKUP(O69,SeedInfo,2,FALSE)*5,MAX(VLOOKUP(O69,SeedInfo,2,FALSE)-VLOOKUP(C69,SeedInfo,2,FALSE),0)))</f>
@@ -21504,44 +21504,44 @@
       </c>
       <c r="F69" s="166" cm="1">
         <f t="array" aca="1" ref="F69" ca="1">_xlfn.XLOOKUP(G69,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G69" s="167" t="str">
         <f ca="1">O64</f>
-        <v>American</v>
+        <v>Arizona</v>
       </c>
       <c r="H69" s="187" t="s">
         <v>9</v>
       </c>
       <c r="I69" s="168" t="str">
         <f ca="1">O65</f>
-        <v>Bradley</v>
+        <v>Drake</v>
       </c>
       <c r="J69" s="169" cm="1">
         <f t="array" aca="1" ref="J69" ca="1">_xlfn.XLOOKUP(I69,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>7</v>
-      </c>
-      <c r="K69" s="170" t="e" vm="73">
+        <v>3</v>
+      </c>
+      <c r="K69" s="170" t="e" vm="75">
         <f ca="1">_xlfn.XLOOKUP(G69,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="L69" s="170">
         <f t="shared" ca="1" si="10"/>
-        <v>110</v>
-      </c>
-      <c r="M69" s="170" t="e" vm="93">
+        <v>119</v>
+      </c>
+      <c r="M69" s="170" t="e" vm="91">
         <f ca="1">_xlfn.XLOOKUP(I69,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="N69" s="170">
         <f t="shared" ca="1" si="10"/>
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="O69" s="200" t="str">
         <f ca="1">IF(L69&gt;N69,G69,I69)</f>
-        <v>American</v>
-      </c>
-      <c r="P69" s="210" t="e" vm="73">
+        <v>Arizona</v>
+      </c>
+      <c r="P69" s="210" t="e" vm="75">
         <f ca="1">_xlfn.XLOOKUP(O69,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -21557,15 +21557,15 @@
     <row r="70" spans="1:19" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="91" t="str">
         <f ca="1">G70</f>
-        <v>Bucknell</v>
+        <v>Central Arkansas</v>
       </c>
       <c r="B70" s="91" t="str">
         <f ca="1">I70</f>
-        <v>Colorado State</v>
+        <v>Columbia</v>
       </c>
       <c r="C70" s="91" t="str">
         <f ca="1">IF(O70="","",IF(A70=O70,B70,A70))</f>
-        <v>Colorado State</v>
+        <v>Central Arkansas</v>
       </c>
       <c r="D70" s="91" t="e">
         <f>IF(SeedType=1,0,IF(SeedType=2,VLOOKUP(O70,SeedInfo,2,FALSE)*5,MAX(VLOOKUP(O70,SeedInfo,2,FALSE)-VLOOKUP(C70,SeedInfo,2,FALSE),0)))</f>
@@ -21576,44 +21576,44 @@
       </c>
       <c r="F70" s="160" cm="1">
         <f t="array" aca="1" ref="F70" ca="1">_xlfn.XLOOKUP(G70,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G70" s="161" t="str">
         <f ca="1">O66</f>
-        <v>Bucknell</v>
+        <v>Central Arkansas</v>
       </c>
       <c r="H70" s="186" t="s">
         <v>9</v>
       </c>
       <c r="I70" s="162" t="str">
         <f ca="1">O67</f>
-        <v>Colorado State</v>
+        <v>Columbia</v>
       </c>
       <c r="J70" s="163" cm="1">
         <f t="array" aca="1" ref="J70" ca="1">_xlfn.XLOOKUP(I70,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>11</v>
-      </c>
-      <c r="K70" s="164" t="e" vm="97">
+        <v>3</v>
+      </c>
+      <c r="K70" s="164" t="e" vm="108">
         <f ca="1">_xlfn.XLOOKUP(G70,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="L70" s="164">
         <f t="shared" ca="1" si="10"/>
-        <v>113</v>
-      </c>
-      <c r="M70" s="164" t="e" vm="122">
+        <v>108</v>
+      </c>
+      <c r="M70" s="164" t="e" vm="123">
         <f ca="1">_xlfn.XLOOKUP(I70,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="N70" s="164">
         <f t="shared" ca="1" si="10"/>
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="O70" s="199" t="str">
         <f ca="1">IF(L70&gt;N70,G70,I70)</f>
-        <v>Bucknell</v>
-      </c>
-      <c r="P70" s="213" t="e" vm="97">
+        <v>Columbia</v>
+      </c>
+      <c r="P70" s="213" t="e" vm="123">
         <f ca="1">_xlfn.XLOOKUP(O70,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -21659,15 +21659,15 @@
     <row r="72" spans="1:19" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="91" t="str">
         <f ca="1">G72</f>
-        <v>American</v>
+        <v>Arizona</v>
       </c>
       <c r="B72" s="91" t="str">
         <f ca="1">I72</f>
-        <v>Bucknell</v>
+        <v>Columbia</v>
       </c>
       <c r="C72" s="91" t="str">
         <f ca="1">IF(O72="","",IF(A72=O72,B72,A72))</f>
-        <v>Bucknell</v>
+        <v>Columbia</v>
       </c>
       <c r="D72" s="91" t="e">
         <f>IF(SeedType=1,0,IF(SeedType=2,VLOOKUP(O72,SeedInfo,2,FALSE)*6,MAX(VLOOKUP(O72,SeedInfo,2,FALSE)-VLOOKUP(C72,SeedInfo,2,FALSE),0)))</f>
@@ -21678,44 +21678,44 @@
       </c>
       <c r="F72" s="154" cm="1">
         <f t="array" aca="1" ref="F72" ca="1">_xlfn.XLOOKUP(G72,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G72" s="155" t="str">
         <f ca="1">O69</f>
-        <v>American</v>
+        <v>Arizona</v>
       </c>
       <c r="H72" s="185" t="s">
         <v>9</v>
       </c>
       <c r="I72" s="156" t="str">
         <f ca="1">O70</f>
-        <v>Bucknell</v>
+        <v>Columbia</v>
       </c>
       <c r="J72" s="157" cm="1">
         <f t="array" aca="1" ref="J72" ca="1">_xlfn.XLOOKUP(I72,Teams[[#All],[Team]],Teams[[#All],[Seed]],0,0,1)</f>
-        <v>1</v>
-      </c>
-      <c r="K72" s="158" t="e" vm="73">
+        <v>3</v>
+      </c>
+      <c r="K72" s="158" t="e" vm="75">
         <f ca="1">_xlfn.XLOOKUP(G72,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="L72" s="158">
         <f t="shared" ca="1" si="10"/>
-        <v>117</v>
-      </c>
-      <c r="M72" s="158" t="e" vm="97">
+        <v>108</v>
+      </c>
+      <c r="M72" s="158" t="e" vm="123">
         <f ca="1">_xlfn.XLOOKUP(I72,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="N72" s="158">
         <f t="shared" ca="1" si="10"/>
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="O72" s="198" t="str">
         <f ca="1">IF(L72&gt;N72,G72,I72)</f>
-        <v>American</v>
-      </c>
-      <c r="P72" s="205" t="e" vm="73">
+        <v>Arizona</v>
+      </c>
+      <c r="P72" s="205" t="e" vm="75">
         <f ca="1">_xlfn.XLOOKUP(O72,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -21724,7 +21724,7 @@
       </c>
       <c r="R72" s="6" t="b">
         <f t="shared" ca="1" si="19"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S72" s="98"/>
     </row>
@@ -21810,47 +21810,47 @@
   <sheetData>
     <row r="1" spans="1:47" s="6" customFormat="1" ht="34.799999999999997" x14ac:dyDescent="0.25">
       <c r="A1" s="13"/>
-      <c r="B1" s="281" t="s">
+      <c r="B1" s="279" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="281"/>
-      <c r="D1" s="281"/>
-      <c r="E1" s="281"/>
-      <c r="F1" s="281"/>
-      <c r="G1" s="281"/>
-      <c r="H1" s="281"/>
-      <c r="I1" s="281"/>
-      <c r="J1" s="281"/>
-      <c r="K1" s="281"/>
-      <c r="L1" s="281"/>
-      <c r="M1" s="281"/>
-      <c r="N1" s="281"/>
-      <c r="O1" s="281"/>
-      <c r="P1" s="281"/>
-      <c r="Q1" s="281"/>
-      <c r="R1" s="281"/>
-      <c r="S1" s="281"/>
-      <c r="T1" s="281"/>
-      <c r="U1" s="281"/>
-      <c r="V1" s="281"/>
-      <c r="W1" s="281"/>
-      <c r="X1" s="281"/>
-      <c r="Y1" s="281"/>
-      <c r="Z1" s="281"/>
-      <c r="AA1" s="281"/>
-      <c r="AB1" s="281"/>
-      <c r="AC1" s="281"/>
-      <c r="AD1" s="281"/>
-      <c r="AE1" s="281"/>
-      <c r="AF1" s="281"/>
-      <c r="AG1" s="281"/>
-      <c r="AH1" s="281"/>
-      <c r="AI1" s="281"/>
-      <c r="AJ1" s="281"/>
-      <c r="AK1" s="281"/>
-      <c r="AL1" s="281"/>
-      <c r="AM1" s="281"/>
-      <c r="AN1" s="281"/>
+      <c r="C1" s="279"/>
+      <c r="D1" s="279"/>
+      <c r="E1" s="279"/>
+      <c r="F1" s="279"/>
+      <c r="G1" s="279"/>
+      <c r="H1" s="279"/>
+      <c r="I1" s="279"/>
+      <c r="J1" s="279"/>
+      <c r="K1" s="279"/>
+      <c r="L1" s="279"/>
+      <c r="M1" s="279"/>
+      <c r="N1" s="279"/>
+      <c r="O1" s="279"/>
+      <c r="P1" s="279"/>
+      <c r="Q1" s="279"/>
+      <c r="R1" s="279"/>
+      <c r="S1" s="279"/>
+      <c r="T1" s="279"/>
+      <c r="U1" s="279"/>
+      <c r="V1" s="279"/>
+      <c r="W1" s="279"/>
+      <c r="X1" s="279"/>
+      <c r="Y1" s="279"/>
+      <c r="Z1" s="279"/>
+      <c r="AA1" s="279"/>
+      <c r="AB1" s="279"/>
+      <c r="AC1" s="279"/>
+      <c r="AD1" s="279"/>
+      <c r="AE1" s="279"/>
+      <c r="AF1" s="279"/>
+      <c r="AG1" s="279"/>
+      <c r="AH1" s="279"/>
+      <c r="AI1" s="279"/>
+      <c r="AJ1" s="279"/>
+      <c r="AK1" s="279"/>
+      <c r="AL1" s="279"/>
+      <c r="AM1" s="279"/>
+      <c r="AN1" s="279"/>
       <c r="AO1" s="17"/>
     </row>
     <row r="2" spans="1:47" s="63" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -21882,13 +21882,13 @@
       <c r="P2" s="61"/>
       <c r="Q2" s="62"/>
       <c r="R2" s="62"/>
-      <c r="S2" s="285" t="s">
+      <c r="S2" s="281" t="s">
         <v>2</v>
       </c>
-      <c r="T2" s="285"/>
-      <c r="U2" s="285"/>
-      <c r="V2" s="285"/>
-      <c r="W2" s="285"/>
+      <c r="T2" s="281"/>
+      <c r="U2" s="281"/>
+      <c r="V2" s="281"/>
+      <c r="W2" s="281"/>
       <c r="X2" s="62"/>
       <c r="Y2" s="62"/>
       <c r="Z2" s="62"/>
@@ -21966,7 +21966,7 @@
       <c r="AM3" s="22"/>
       <c r="AN3" s="22"/>
       <c r="AO3" s="17"/>
-      <c r="AQ3" s="288"/>
+      <c r="AQ3" s="275"/>
       <c r="AU3" s="7" t="s">
         <v>17</v>
       </c>
@@ -21998,7 +21998,7 @@
       <c r="AM4" s="26"/>
       <c r="AN4" s="24"/>
       <c r="AO4" s="17"/>
-      <c r="AQ4" s="288"/>
+      <c r="AQ4" s="275"/>
     </row>
     <row r="5" spans="1:47" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="16"/>
@@ -22015,19 +22015,19 @@
       </c>
       <c r="E5" s="46">
         <f ca="1">Games!L5</f>
-        <v>111</v>
-      </c>
-      <c r="F5" s="262" t="str">
+        <v>106</v>
+      </c>
+      <c r="F5" s="256" t="str">
         <f ca="1">Games!O5</f>
-        <v>Abilene Christian</v>
-      </c>
-      <c r="G5" s="247" t="e" vm="65">
+        <v>Air Force</v>
+      </c>
+      <c r="G5" s="259" t="e" vm="66">
         <f ca="1">_xlfn.XLOOKUP(F5,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H5" s="284">
+      <c r="H5" s="280">
         <f ca="1">Games!L38</f>
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="I5" s="25"/>
       <c r="J5" s="25"/>
@@ -22045,21 +22045,21 @@
       <c r="AA5" s="25"/>
       <c r="AD5" s="25"/>
       <c r="AG5" s="25"/>
-      <c r="AH5" s="264">
+      <c r="AH5" s="251">
         <f ca="1">Games!L46</f>
-        <v>108</v>
-      </c>
-      <c r="AI5" s="297" t="e" vm="97">
+        <v>116</v>
+      </c>
+      <c r="AI5" s="247" t="e" vm="98">
         <f ca="1">_xlfn.XLOOKUP(AJ5,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AJ5" s="262" t="str">
+      <c r="AJ5" s="256" t="str">
         <f ca="1">Games!O21</f>
-        <v>Bucknell</v>
+        <v>Buffalo</v>
       </c>
       <c r="AK5" s="58">
         <f ca="1">Games!L21</f>
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="AL5" s="46" t="e" vm="97">
         <f>_xlfn.XLOOKUP(AM5,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -22073,14 +22073,14 @@
         <v>1</v>
       </c>
       <c r="AO5" s="17"/>
-      <c r="AQ5" s="288"/>
+      <c r="AQ5" s="275"/>
       <c r="AU5" s="2" t="b">
         <f>IF(AP29="x",TRUE,FALSE)</f>
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:47" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="283">
+      <c r="A6" s="255">
         <f>IF($AU$5=TRUE,1,"")</f>
         <v>1</v>
       </c>
@@ -22088,9 +22088,9 @@
       <c r="C6" s="38"/>
       <c r="D6" s="71"/>
       <c r="E6" s="47"/>
-      <c r="F6" s="263"/>
-      <c r="G6" s="248"/>
-      <c r="H6" s="265"/>
+      <c r="F6" s="257"/>
+      <c r="G6" s="260"/>
+      <c r="H6" s="252"/>
       <c r="I6" s="25"/>
       <c r="J6" s="25"/>
       <c r="L6" s="25"/>
@@ -22107,20 +22107,20 @@
       <c r="AA6" s="25"/>
       <c r="AD6" s="25"/>
       <c r="AG6" s="25"/>
-      <c r="AH6" s="265"/>
-      <c r="AI6" s="298"/>
-      <c r="AJ6" s="263"/>
+      <c r="AH6" s="252"/>
+      <c r="AI6" s="248"/>
+      <c r="AJ6" s="257"/>
       <c r="AK6" s="55"/>
       <c r="AM6" s="39"/>
       <c r="AN6" s="28"/>
-      <c r="AO6" s="287">
+      <c r="AO6" s="277">
         <f>IF($AU$5=TRUE,A66+1,"")</f>
         <v>17</v>
       </c>
-      <c r="AQ6" s="288"/>
+      <c r="AQ6" s="275"/>
     </row>
     <row r="7" spans="1:47" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="283"/>
+      <c r="A7" s="255"/>
       <c r="B7" s="27">
         <v>16</v>
       </c>
@@ -22134,25 +22134,25 @@
       </c>
       <c r="E7" s="48">
         <f ca="1">Games!N5</f>
-        <v>95</v>
-      </c>
-      <c r="F7" s="282">
+        <v>120</v>
+      </c>
+      <c r="F7" s="276">
         <f>IF($AU$5=TRUE,AO66+1,"")</f>
         <v>33</v>
       </c>
       <c r="G7" s="14"/>
       <c r="H7" s="49"/>
-      <c r="I7" s="279" t="str">
+      <c r="I7" s="265" t="str">
         <f ca="1">Games!O38</f>
-        <v>Akron</v>
-      </c>
-      <c r="J7" s="247" t="e" vm="67">
+        <v>Air Force</v>
+      </c>
+      <c r="J7" s="259" t="e" vm="66">
         <f ca="1">_xlfn.XLOOKUP(I7,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K7" s="264">
+      <c r="K7" s="251">
         <f ca="1">Games!L55</f>
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="L7" s="25"/>
       <c r="M7" s="25"/>
@@ -22167,27 +22167,27 @@
       <c r="X7" s="25"/>
       <c r="AA7" s="25"/>
       <c r="AD7" s="25"/>
-      <c r="AE7" s="264">
+      <c r="AE7" s="251">
         <f ca="1">Games!L59</f>
-        <v>104</v>
-      </c>
-      <c r="AF7" s="297" t="e" vm="97">
+        <v>98</v>
+      </c>
+      <c r="AF7" s="247" t="e" vm="98">
         <f ca="1">_xlfn.XLOOKUP(AG7,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG7" s="262" t="str">
+      <c r="AG7" s="256" t="str">
         <f ca="1">Games!O46</f>
-        <v>Bucknell</v>
+        <v>Buffalo</v>
       </c>
       <c r="AH7" s="55"/>
       <c r="AI7" s="51"/>
-      <c r="AJ7" s="282">
+      <c r="AJ7" s="276">
         <f>IF($AU$5=TRUE,F63+1,"")</f>
         <v>41</v>
       </c>
       <c r="AK7" s="59">
         <f ca="1">Games!N21</f>
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="AL7" s="46" t="e" vm="98">
         <f>_xlfn.XLOOKUP(AM7,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -22200,20 +22200,20 @@
       <c r="AN7" s="27">
         <v>16</v>
       </c>
-      <c r="AO7" s="287"/>
-      <c r="AQ7" s="288"/>
+      <c r="AO7" s="277"/>
+      <c r="AQ7" s="275"/>
     </row>
     <row r="8" spans="1:47" ht="10.199999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="16"/>
       <c r="B8" s="28"/>
       <c r="C8" s="38"/>
       <c r="D8" s="71"/>
-      <c r="F8" s="283"/>
+      <c r="F8" s="255"/>
       <c r="G8" s="15"/>
       <c r="H8" s="50"/>
-      <c r="I8" s="280"/>
-      <c r="J8" s="248"/>
-      <c r="K8" s="265"/>
+      <c r="I8" s="266"/>
+      <c r="J8" s="260"/>
+      <c r="K8" s="252"/>
       <c r="L8" s="25"/>
       <c r="M8" s="25"/>
       <c r="O8" s="25"/>
@@ -22227,15 +22227,15 @@
       <c r="X8" s="25"/>
       <c r="AA8" s="25"/>
       <c r="AD8" s="25"/>
-      <c r="AE8" s="265"/>
-      <c r="AF8" s="298"/>
-      <c r="AG8" s="263"/>
+      <c r="AE8" s="252"/>
+      <c r="AF8" s="248"/>
+      <c r="AG8" s="257"/>
       <c r="AH8" s="56"/>
-      <c r="AJ8" s="283"/>
+      <c r="AJ8" s="255"/>
       <c r="AM8" s="39"/>
       <c r="AN8" s="28"/>
       <c r="AO8" s="17"/>
-      <c r="AQ8" s="288"/>
+      <c r="AQ8" s="275"/>
     </row>
     <row r="9" spans="1:47" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="16"/>
@@ -22252,19 +22252,19 @@
       </c>
       <c r="E9" s="46">
         <f ca="1">Games!L6</f>
-        <v>112</v>
-      </c>
-      <c r="F9" s="262" t="str">
+        <v>104</v>
+      </c>
+      <c r="F9" s="256" t="str">
         <f ca="1">Games!O6</f>
         <v>Akron</v>
       </c>
-      <c r="G9" s="247" t="e" vm="67">
+      <c r="G9" s="259" t="e" vm="67">
         <f ca="1">_xlfn.XLOOKUP(F9,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H9" s="277">
+      <c r="H9" s="261">
         <f ca="1">Games!N38</f>
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="I9" s="24"/>
       <c r="J9" s="24"/>
@@ -22284,21 +22284,21 @@
       <c r="AD9" s="25"/>
       <c r="AE9" s="55"/>
       <c r="AG9" s="24"/>
-      <c r="AH9" s="269">
+      <c r="AH9" s="253">
         <f ca="1">Games!N46</f>
-        <v>98</v>
-      </c>
-      <c r="AI9" s="297" t="e" vm="100">
+        <v>92</v>
+      </c>
+      <c r="AI9" s="247" t="e" vm="100">
         <f ca="1">_xlfn.XLOOKUP(AJ9,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AJ9" s="262" t="str">
+      <c r="AJ9" s="256" t="str">
         <f ca="1">Games!O22</f>
         <v>Cal Poly</v>
       </c>
       <c r="AK9" s="58">
         <f ca="1">Games!L22</f>
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="AL9" s="46" t="e" vm="99">
         <f>_xlfn.XLOOKUP(AM9,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -22312,10 +22312,10 @@
         <v>8</v>
       </c>
       <c r="AO9" s="17"/>
-      <c r="AQ9" s="288"/>
+      <c r="AQ9" s="275"/>
     </row>
     <row r="10" spans="1:47" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="286">
+      <c r="A10" s="278">
         <f>IF($AU$5=TRUE,A6+1,"")</f>
         <v>2</v>
       </c>
@@ -22323,9 +22323,9 @@
       <c r="C10" s="38"/>
       <c r="D10" s="71"/>
       <c r="E10" s="47"/>
-      <c r="F10" s="263"/>
-      <c r="G10" s="248"/>
-      <c r="H10" s="278"/>
+      <c r="F10" s="257"/>
+      <c r="G10" s="260"/>
+      <c r="H10" s="262"/>
       <c r="I10" s="24"/>
       <c r="J10" s="24"/>
       <c r="K10" s="50"/>
@@ -22344,20 +22344,20 @@
       <c r="AD10" s="25"/>
       <c r="AE10" s="56"/>
       <c r="AG10" s="24"/>
-      <c r="AH10" s="270"/>
-      <c r="AI10" s="298"/>
-      <c r="AJ10" s="263"/>
+      <c r="AH10" s="254"/>
+      <c r="AI10" s="248"/>
+      <c r="AJ10" s="257"/>
       <c r="AK10" s="55"/>
       <c r="AM10" s="39"/>
       <c r="AN10" s="28"/>
-      <c r="AO10" s="287">
+      <c r="AO10" s="277">
         <f>IF($AU$5=TRUE,AO6+1,"")</f>
         <v>18</v>
       </c>
-      <c r="AQ10" s="288"/>
+      <c r="AQ10" s="275"/>
     </row>
     <row r="11" spans="1:47" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="286"/>
+      <c r="A11" s="278"/>
       <c r="B11" s="27">
         <v>9</v>
       </c>
@@ -22371,62 +22371,62 @@
       </c>
       <c r="E11" s="48">
         <f ca="1">Games!N6</f>
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="F11" s="24"/>
       <c r="G11" s="24"/>
-      <c r="I11" s="283">
+      <c r="I11" s="255">
         <f>IF($AU$5=TRUE,AJ63+1,"")</f>
         <v>49</v>
       </c>
       <c r="J11" s="15"/>
       <c r="K11" s="50"/>
-      <c r="L11" s="279" t="str">
+      <c r="L11" s="265" t="str">
         <f ca="1">Games!O55</f>
-        <v>Alabama State</v>
-      </c>
-      <c r="M11" s="247" t="e" vm="70">
+        <v>Alcorn State</v>
+      </c>
+      <c r="M11" s="259" t="e" vm="72">
         <f ca="1">_xlfn.XLOOKUP(L11,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N11" s="264">
+      <c r="N11" s="251">
         <f ca="1">Games!L64</f>
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="O11" s="25"/>
       <c r="P11" s="25"/>
       <c r="R11" s="25"/>
       <c r="S11" s="25"/>
-      <c r="T11" s="251" t="e" vm="73">
+      <c r="T11" s="282" t="e" vm="75">
         <f ca="1">_xlfn.XLOOKUP(S32,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="U11" s="252"/>
-      <c r="V11" s="253"/>
+      <c r="U11" s="283"/>
+      <c r="V11" s="284"/>
       <c r="W11" s="25"/>
       <c r="X11" s="25"/>
       <c r="AA11" s="25"/>
-      <c r="AB11" s="264">
+      <c r="AB11" s="251">
         <f ca="1">Games!L66</f>
-        <v>120</v>
-      </c>
-      <c r="AC11" s="249" t="e" vm="97">
+        <v>109</v>
+      </c>
+      <c r="AC11" s="249" t="e" vm="103">
         <f ca="1">_xlfn.XLOOKUP(AD11,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AD11" s="262" t="str">
+      <c r="AD11" s="256" t="str">
         <f ca="1">Games!O59</f>
-        <v>Bucknell</v>
+        <v>Cal State Northridge</v>
       </c>
       <c r="AE11" s="56"/>
-      <c r="AG11" s="283">
+      <c r="AG11" s="255">
         <f>IF($AU$5=TRUE,I59+1,"")</f>
         <v>53</v>
       </c>
       <c r="AJ11" s="24"/>
       <c r="AK11" s="59">
         <f ca="1">Games!N22</f>
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AL11" s="46" t="e" vm="100">
         <f>_xlfn.XLOOKUP(AM11,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -22439,8 +22439,8 @@
       <c r="AN11" s="27">
         <v>9</v>
       </c>
-      <c r="AO11" s="287"/>
-      <c r="AQ11" s="288"/>
+      <c r="AO11" s="277"/>
+      <c r="AQ11" s="275"/>
     </row>
     <row r="12" spans="1:47" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="16"/>
@@ -22449,27 +22449,27 @@
       <c r="D12" s="71"/>
       <c r="F12" s="24"/>
       <c r="G12" s="24"/>
-      <c r="I12" s="283"/>
+      <c r="I12" s="255"/>
       <c r="J12" s="15"/>
       <c r="K12" s="50"/>
-      <c r="L12" s="280"/>
-      <c r="M12" s="248"/>
-      <c r="N12" s="265"/>
+      <c r="L12" s="266"/>
+      <c r="M12" s="260"/>
+      <c r="N12" s="252"/>
       <c r="O12" s="25"/>
       <c r="P12" s="25"/>
       <c r="R12" s="25"/>
       <c r="S12" s="25"/>
-      <c r="T12" s="254"/>
-      <c r="U12" s="255"/>
-      <c r="V12" s="256"/>
+      <c r="T12" s="285"/>
+      <c r="U12" s="286"/>
+      <c r="V12" s="287"/>
       <c r="W12" s="25"/>
       <c r="X12" s="25"/>
       <c r="AA12" s="25"/>
-      <c r="AB12" s="265"/>
+      <c r="AB12" s="252"/>
       <c r="AC12" s="250"/>
-      <c r="AD12" s="263"/>
+      <c r="AD12" s="257"/>
       <c r="AE12" s="56"/>
-      <c r="AG12" s="283"/>
+      <c r="AG12" s="255"/>
       <c r="AJ12" s="24"/>
       <c r="AM12" s="39"/>
       <c r="AN12" s="28"/>
@@ -22490,19 +22490,19 @@
       </c>
       <c r="E13" s="46">
         <f ca="1">Games!L7</f>
-        <v>98</v>
-      </c>
-      <c r="F13" s="262" t="str">
+        <v>90</v>
+      </c>
+      <c r="F13" s="256" t="str">
         <f ca="1">Games!O7</f>
         <v>Alabama State</v>
       </c>
-      <c r="G13" s="247" t="e" vm="70">
+      <c r="G13" s="259" t="e" vm="70">
         <f ca="1">_xlfn.XLOOKUP(F13,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H13" s="264">
+      <c r="H13" s="251">
         <f ca="1">Games!L39</f>
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="I13" s="24"/>
       <c r="J13" s="24"/>
@@ -22514,9 +22514,9 @@
       <c r="P13" s="25"/>
       <c r="R13" s="25"/>
       <c r="S13" s="25"/>
-      <c r="T13" s="254"/>
-      <c r="U13" s="255"/>
-      <c r="V13" s="256"/>
+      <c r="T13" s="285"/>
+      <c r="U13" s="286"/>
+      <c r="V13" s="287"/>
       <c r="W13" s="25"/>
       <c r="X13" s="25"/>
       <c r="AA13" s="25"/>
@@ -22524,21 +22524,21 @@
       <c r="AD13" s="25"/>
       <c r="AE13" s="56"/>
       <c r="AG13" s="24"/>
-      <c r="AH13" s="264">
+      <c r="AH13" s="251">
         <f ca="1">Games!L47</f>
-        <v>103</v>
-      </c>
-      <c r="AI13" s="249" t="e" vm="101">
+        <v>101</v>
+      </c>
+      <c r="AI13" s="249" t="e" vm="102">
         <f ca="1">_xlfn.XLOOKUP(AJ13,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AJ13" s="262" t="str">
+      <c r="AJ13" s="256" t="str">
         <f ca="1">Games!O23</f>
-        <v>Cal State Bakersfield</v>
+        <v>Cal State Fullerton</v>
       </c>
       <c r="AK13" s="58">
         <f ca="1">Games!L23</f>
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="AL13" s="46" t="e" vm="101">
         <f>_xlfn.XLOOKUP(AM13,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -22555,7 +22555,7 @@
       <c r="AQ13" s="9"/>
     </row>
     <row r="14" spans="1:47" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="283">
+      <c r="A14" s="255">
         <f>IF($AU$5=TRUE,A10+1,"")</f>
         <v>3</v>
       </c>
@@ -22563,9 +22563,9 @@
       <c r="C14" s="38"/>
       <c r="D14" s="71"/>
       <c r="E14" s="49"/>
-      <c r="F14" s="263"/>
-      <c r="G14" s="248"/>
-      <c r="H14" s="265"/>
+      <c r="F14" s="257"/>
+      <c r="G14" s="260"/>
+      <c r="H14" s="252"/>
       <c r="I14" s="24"/>
       <c r="J14" s="24"/>
       <c r="K14" s="50"/>
@@ -22576,9 +22576,9 @@
       <c r="P14" s="25"/>
       <c r="R14" s="25"/>
       <c r="S14" s="25"/>
-      <c r="T14" s="254"/>
-      <c r="U14" s="255"/>
-      <c r="V14" s="256"/>
+      <c r="T14" s="285"/>
+      <c r="U14" s="286"/>
+      <c r="V14" s="287"/>
       <c r="W14" s="25"/>
       <c r="X14" s="25"/>
       <c r="AA14" s="25"/>
@@ -22586,20 +22586,20 @@
       <c r="AD14" s="25"/>
       <c r="AE14" s="56"/>
       <c r="AG14" s="24"/>
-      <c r="AH14" s="265"/>
+      <c r="AH14" s="252"/>
       <c r="AI14" s="250"/>
-      <c r="AJ14" s="263"/>
+      <c r="AJ14" s="257"/>
       <c r="AK14" s="55"/>
       <c r="AM14" s="39"/>
       <c r="AN14" s="28"/>
-      <c r="AO14" s="287">
+      <c r="AO14" s="277">
         <f>IF($AU$5=TRUE,AO10+1,"")</f>
         <v>19</v>
       </c>
-      <c r="AQ14" s="288"/>
+      <c r="AQ14" s="275"/>
     </row>
     <row r="15" spans="1:47" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="283"/>
+      <c r="A15" s="255"/>
       <c r="B15" s="27">
         <v>12</v>
       </c>
@@ -22613,25 +22613,25 @@
       </c>
       <c r="E15" s="48">
         <f ca="1">Games!N7</f>
-        <v>111</v>
-      </c>
-      <c r="F15" s="282">
+        <v>95</v>
+      </c>
+      <c r="F15" s="276">
         <f>IF($AU$5=TRUE,F7+1,"")</f>
         <v>34</v>
       </c>
       <c r="G15" s="14"/>
       <c r="H15" s="49"/>
-      <c r="I15" s="279" t="str">
+      <c r="I15" s="265" t="str">
         <f ca="1">Games!O39</f>
-        <v>Alabama State</v>
-      </c>
-      <c r="J15" s="247" t="e" vm="70">
+        <v>Alcorn State</v>
+      </c>
+      <c r="J15" s="259" t="e" vm="72">
         <f ca="1">_xlfn.XLOOKUP(I15,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K15" s="277">
+      <c r="K15" s="261">
         <f ca="1">Games!N55</f>
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="L15" s="25"/>
       <c r="M15" s="25"/>
@@ -22640,35 +22640,35 @@
       <c r="P15" s="25"/>
       <c r="R15" s="25"/>
       <c r="S15" s="25"/>
-      <c r="T15" s="254"/>
-      <c r="U15" s="255"/>
-      <c r="V15" s="256"/>
+      <c r="T15" s="285"/>
+      <c r="U15" s="286"/>
+      <c r="V15" s="287"/>
       <c r="W15" s="25"/>
       <c r="X15" s="25"/>
       <c r="AA15" s="25"/>
       <c r="AB15" s="56"/>
       <c r="AD15" s="25"/>
-      <c r="AE15" s="269">
+      <c r="AE15" s="253">
         <f ca="1">Games!N59</f>
-        <v>101</v>
-      </c>
-      <c r="AF15" s="249" t="e" vm="104">
+        <v>110</v>
+      </c>
+      <c r="AF15" s="249" t="e" vm="103">
         <f ca="1">_xlfn.XLOOKUP(AG15,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG15" s="262" t="str">
+      <c r="AG15" s="256" t="str">
         <f ca="1">Games!O47</f>
-        <v>California</v>
+        <v>Cal State Northridge</v>
       </c>
       <c r="AH15" s="55"/>
       <c r="AI15" s="51"/>
-      <c r="AJ15" s="282">
+      <c r="AJ15" s="276">
         <f>IF($AU$5=TRUE,AJ7+1,"")</f>
         <v>42</v>
       </c>
       <c r="AK15" s="59">
         <f ca="1">Games!N23</f>
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="AL15" s="46" t="e" vm="102">
         <f>_xlfn.XLOOKUP(AM15,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -22681,20 +22681,20 @@
       <c r="AN15" s="27">
         <v>12</v>
       </c>
-      <c r="AO15" s="287"/>
-      <c r="AQ15" s="288"/>
+      <c r="AO15" s="277"/>
+      <c r="AQ15" s="275"/>
     </row>
     <row r="16" spans="1:47" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="16"/>
       <c r="B16" s="28"/>
       <c r="C16" s="38"/>
       <c r="D16" s="71"/>
-      <c r="F16" s="283"/>
+      <c r="F16" s="255"/>
       <c r="G16" s="15"/>
       <c r="H16" s="50"/>
-      <c r="I16" s="280"/>
-      <c r="J16" s="248"/>
-      <c r="K16" s="278"/>
+      <c r="I16" s="266"/>
+      <c r="J16" s="260"/>
+      <c r="K16" s="262"/>
       <c r="L16" s="25"/>
       <c r="M16" s="25"/>
       <c r="N16" s="50"/>
@@ -22702,23 +22702,23 @@
       <c r="P16" s="25"/>
       <c r="R16" s="25"/>
       <c r="S16" s="25"/>
-      <c r="T16" s="254"/>
-      <c r="U16" s="255"/>
-      <c r="V16" s="256"/>
+      <c r="T16" s="285"/>
+      <c r="U16" s="286"/>
+      <c r="V16" s="287"/>
       <c r="W16" s="25"/>
       <c r="X16" s="25"/>
       <c r="AA16" s="25"/>
       <c r="AB16" s="56"/>
       <c r="AD16" s="25"/>
-      <c r="AE16" s="270"/>
+      <c r="AE16" s="254"/>
       <c r="AF16" s="250"/>
-      <c r="AG16" s="263"/>
+      <c r="AG16" s="257"/>
       <c r="AH16" s="56"/>
-      <c r="AJ16" s="283"/>
+      <c r="AJ16" s="255"/>
       <c r="AM16" s="39"/>
       <c r="AN16" s="28"/>
       <c r="AO16" s="17"/>
-      <c r="AQ16" s="288"/>
+      <c r="AQ16" s="275"/>
     </row>
     <row r="17" spans="1:43" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="16"/>
@@ -22735,19 +22735,19 @@
       </c>
       <c r="E17" s="46">
         <f ca="1">Games!L8</f>
-        <v>111</v>
-      </c>
-      <c r="F17" s="262" t="str">
+        <v>108</v>
+      </c>
+      <c r="F17" s="256" t="str">
         <f ca="1">Games!O8</f>
-        <v>Albany (NY)</v>
-      </c>
-      <c r="G17" s="247" t="e" vm="71">
+        <v>Alcorn State</v>
+      </c>
+      <c r="G17" s="259" t="e" vm="72">
         <f ca="1">_xlfn.XLOOKUP(F17,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H17" s="277">
+      <c r="H17" s="261">
         <f ca="1">Games!N39</f>
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="I17" s="24"/>
       <c r="J17" s="24"/>
@@ -22758,30 +22758,30 @@
       <c r="P17" s="25"/>
       <c r="R17" s="25"/>
       <c r="S17" s="25"/>
-      <c r="T17" s="254"/>
-      <c r="U17" s="255"/>
-      <c r="V17" s="256"/>
+      <c r="T17" s="285"/>
+      <c r="U17" s="286"/>
+      <c r="V17" s="287"/>
       <c r="W17" s="25"/>
       <c r="X17" s="25"/>
       <c r="AA17" s="25"/>
       <c r="AB17" s="56"/>
       <c r="AD17" s="25"/>
       <c r="AG17" s="24"/>
-      <c r="AH17" s="269">
+      <c r="AH17" s="253">
         <f ca="1">Games!N47</f>
-        <v>109</v>
-      </c>
-      <c r="AI17" s="249" t="e" vm="104">
+        <v>118</v>
+      </c>
+      <c r="AI17" s="249" t="e" vm="103">
         <f ca="1">_xlfn.XLOOKUP(AJ17,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AJ17" s="262" t="str">
+      <c r="AJ17" s="256" t="str">
         <f ca="1">Games!O24</f>
-        <v>California</v>
+        <v>Cal State Northridge</v>
       </c>
       <c r="AK17" s="58">
         <f ca="1">Games!L24</f>
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="AL17" s="46" t="e" vm="103">
         <f>_xlfn.XLOOKUP(AM17,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -22795,10 +22795,10 @@
         <v>4</v>
       </c>
       <c r="AO17" s="17"/>
-      <c r="AQ17" s="288"/>
+      <c r="AQ17" s="275"/>
     </row>
     <row r="18" spans="1:43" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="283">
+      <c r="A18" s="255">
         <f>IF($AU$5=TRUE,A14+1,"")</f>
         <v>4</v>
       </c>
@@ -22806,9 +22806,9 @@
       <c r="C18" s="38"/>
       <c r="D18" s="71"/>
       <c r="E18" s="49"/>
-      <c r="F18" s="263"/>
-      <c r="G18" s="248"/>
-      <c r="H18" s="278"/>
+      <c r="F18" s="257"/>
+      <c r="G18" s="260"/>
+      <c r="H18" s="262"/>
       <c r="I18" s="24"/>
       <c r="J18" s="24"/>
       <c r="L18" s="25"/>
@@ -22818,29 +22818,29 @@
       <c r="P18" s="25"/>
       <c r="R18" s="25"/>
       <c r="S18" s="25"/>
-      <c r="T18" s="254"/>
-      <c r="U18" s="255"/>
-      <c r="V18" s="256"/>
+      <c r="T18" s="285"/>
+      <c r="U18" s="286"/>
+      <c r="V18" s="287"/>
       <c r="W18" s="25"/>
       <c r="X18" s="25"/>
       <c r="AA18" s="25"/>
       <c r="AB18" s="56"/>
       <c r="AD18" s="25"/>
       <c r="AG18" s="24"/>
-      <c r="AH18" s="270"/>
+      <c r="AH18" s="254"/>
       <c r="AI18" s="250"/>
-      <c r="AJ18" s="263"/>
+      <c r="AJ18" s="257"/>
       <c r="AK18" s="55"/>
       <c r="AM18" s="39"/>
       <c r="AN18" s="28"/>
-      <c r="AO18" s="287">
+      <c r="AO18" s="277">
         <f>IF($AU$5=TRUE,AO14+1,"")</f>
         <v>20</v>
       </c>
-      <c r="AQ18" s="288"/>
+      <c r="AQ18" s="275"/>
     </row>
     <row r="19" spans="1:43" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="283"/>
+      <c r="A19" s="255"/>
       <c r="B19" s="27">
         <v>13</v>
       </c>
@@ -22854,60 +22854,60 @@
       </c>
       <c r="E19" s="48">
         <f ca="1">Games!N8</f>
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="F19" s="24"/>
       <c r="G19" s="24"/>
       <c r="I19" s="24"/>
       <c r="J19" s="24"/>
-      <c r="K19" s="266" t="s">
+      <c r="K19" s="258" t="s">
         <v>15</v>
       </c>
-      <c r="L19" s="266"/>
+      <c r="L19" s="258"/>
       <c r="M19" s="20"/>
       <c r="N19" s="50"/>
-      <c r="O19" s="279" t="str">
+      <c r="O19" s="265" t="str">
         <f ca="1">Games!O64</f>
-        <v>American</v>
-      </c>
-      <c r="P19" s="247" t="e" vm="73">
+        <v>Arizona</v>
+      </c>
+      <c r="P19" s="259" t="e" vm="75">
         <f ca="1">_xlfn.XLOOKUP(O19,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="Q19" s="264">
+      <c r="Q19" s="251">
         <f ca="1">Games!L69</f>
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="R19" s="25"/>
       <c r="S19" s="25"/>
-      <c r="T19" s="257"/>
-      <c r="U19" s="258"/>
-      <c r="V19" s="259"/>
+      <c r="T19" s="288"/>
+      <c r="U19" s="289"/>
+      <c r="V19" s="290"/>
       <c r="W19" s="25"/>
       <c r="X19" s="25"/>
-      <c r="Y19" s="264">
+      <c r="Y19" s="251">
         <f ca="1">Games!L70</f>
-        <v>113</v>
-      </c>
-      <c r="Z19" s="249" t="e" vm="97">
+        <v>108</v>
+      </c>
+      <c r="Z19" s="249" t="e" vm="108">
         <f ca="1">_xlfn.XLOOKUP(AA19,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AA19" s="262" t="str">
+      <c r="AA19" s="256" t="str">
         <f ca="1">Games!O66</f>
-        <v>Bucknell</v>
+        <v>Central Arkansas</v>
       </c>
       <c r="AB19" s="56"/>
-      <c r="AD19" s="266" t="s">
+      <c r="AD19" s="258" t="s">
         <v>3</v>
       </c>
-      <c r="AE19" s="266"/>
+      <c r="AE19" s="258"/>
       <c r="AF19" s="20"/>
       <c r="AG19" s="24"/>
       <c r="AJ19" s="24"/>
       <c r="AK19" s="59">
         <f ca="1">Games!N24</f>
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="AL19" s="46" t="e" vm="104">
         <f>_xlfn.XLOOKUP(AM19,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -22920,8 +22920,8 @@
       <c r="AN19" s="27">
         <v>13</v>
       </c>
-      <c r="AO19" s="287"/>
-      <c r="AQ19" s="288"/>
+      <c r="AO19" s="277"/>
+      <c r="AQ19" s="275"/>
     </row>
     <row r="20" spans="1:43" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A20" s="16"/>
@@ -22932,13 +22932,13 @@
       <c r="G20" s="24"/>
       <c r="I20" s="24"/>
       <c r="J20" s="24"/>
-      <c r="K20" s="266"/>
-      <c r="L20" s="266"/>
+      <c r="K20" s="258"/>
+      <c r="L20" s="258"/>
       <c r="M20" s="20"/>
       <c r="N20" s="50"/>
-      <c r="O20" s="280"/>
-      <c r="P20" s="248"/>
-      <c r="Q20" s="265"/>
+      <c r="O20" s="266"/>
+      <c r="P20" s="260"/>
+      <c r="Q20" s="252"/>
       <c r="R20" s="25"/>
       <c r="S20" s="25"/>
       <c r="T20" s="25"/>
@@ -22946,12 +22946,12 @@
       <c r="V20" s="25"/>
       <c r="W20" s="25"/>
       <c r="X20" s="25"/>
-      <c r="Y20" s="265"/>
+      <c r="Y20" s="252"/>
       <c r="Z20" s="250"/>
-      <c r="AA20" s="263"/>
+      <c r="AA20" s="257"/>
       <c r="AB20" s="56"/>
-      <c r="AD20" s="266"/>
-      <c r="AE20" s="266"/>
+      <c r="AD20" s="258"/>
+      <c r="AE20" s="258"/>
       <c r="AF20" s="20"/>
       <c r="AG20" s="24"/>
       <c r="AJ20" s="24"/>
@@ -22961,7 +22961,7 @@
       <c r="AQ20" s="10"/>
     </row>
     <row r="21" spans="1:43" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="283">
+      <c r="A21" s="255">
         <f>IF($AU$5=TRUE,A18+1,"")</f>
         <v>5</v>
       </c>
@@ -22978,19 +22978,19 @@
       </c>
       <c r="E21" s="46">
         <f ca="1">Games!L9</f>
-        <v>108</v>
-      </c>
-      <c r="F21" s="262" t="str">
+        <v>96</v>
+      </c>
+      <c r="F21" s="256" t="str">
         <f ca="1">Games!O9</f>
-        <v>American</v>
-      </c>
-      <c r="G21" s="247" t="e" vm="73">
+        <v>Appalachian State</v>
+      </c>
+      <c r="G21" s="259" t="e" vm="74">
         <f ca="1">_xlfn.XLOOKUP(F21,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H21" s="264">
+      <c r="H21" s="251">
         <f ca="1">Games!L40</f>
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="I21" s="24"/>
       <c r="J21" s="24"/>
@@ -23018,21 +23018,21 @@
         <v>59</v>
       </c>
       <c r="AG21" s="24"/>
-      <c r="AH21" s="264">
+      <c r="AH21" s="251">
         <f ca="1">Games!L48</f>
-        <v>93</v>
-      </c>
-      <c r="AI21" s="249" t="e" vm="106">
+        <v>95</v>
+      </c>
+      <c r="AI21" s="249" t="e" vm="105">
         <f ca="1">_xlfn.XLOOKUP(AJ21,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AJ21" s="262" t="str">
+      <c r="AJ21" s="256" t="str">
         <f ca="1">Games!O25</f>
-        <v>Campbell</v>
+        <v>California Baptist</v>
       </c>
       <c r="AK21" s="58">
         <f ca="1">Games!L25</f>
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AL21" s="46" t="e" vm="105">
         <f>_xlfn.XLOOKUP(AM21,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -23049,14 +23049,14 @@
       <c r="AQ21" s="9"/>
     </row>
     <row r="22" spans="1:43" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="283"/>
+      <c r="A22" s="255"/>
       <c r="B22" s="28"/>
       <c r="C22" s="38"/>
       <c r="D22" s="71"/>
       <c r="E22" s="49"/>
-      <c r="F22" s="263"/>
-      <c r="G22" s="248"/>
-      <c r="H22" s="265"/>
+      <c r="F22" s="257"/>
+      <c r="G22" s="260"/>
+      <c r="H22" s="252"/>
       <c r="I22" s="24"/>
       <c r="J22" s="24"/>
       <c r="L22" s="25"/>
@@ -23077,17 +23077,17 @@
       <c r="AB22" s="56"/>
       <c r="AD22" s="29"/>
       <c r="AG22" s="24"/>
-      <c r="AH22" s="265"/>
+      <c r="AH22" s="252"/>
       <c r="AI22" s="250"/>
-      <c r="AJ22" s="263"/>
+      <c r="AJ22" s="257"/>
       <c r="AK22" s="55"/>
       <c r="AM22" s="39"/>
       <c r="AN22" s="28"/>
-      <c r="AO22" s="287">
+      <c r="AO22" s="277">
         <f>IF($AU$5=TRUE,AO18+1,"")</f>
         <v>21</v>
       </c>
-      <c r="AQ22" s="288"/>
+      <c r="AQ22" s="275"/>
     </row>
     <row r="23" spans="1:43" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="16"/>
@@ -23104,25 +23104,25 @@
       </c>
       <c r="E23" s="48">
         <f ca="1">Games!N9</f>
-        <v>101</v>
-      </c>
-      <c r="F23" s="282">
+        <v>109</v>
+      </c>
+      <c r="F23" s="276">
         <f>IF($AU$5=TRUE,F15+1,"")</f>
         <v>35</v>
       </c>
       <c r="G23" s="14"/>
       <c r="H23" s="49"/>
-      <c r="I23" s="279" t="str">
+      <c r="I23" s="265" t="str">
         <f ca="1">Games!O40</f>
-        <v>American</v>
-      </c>
-      <c r="J23" s="247" t="e" vm="73">
+        <v>Arizona</v>
+      </c>
+      <c r="J23" s="259" t="e" vm="75">
         <f ca="1">_xlfn.XLOOKUP(I23,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K23" s="264">
+      <c r="K23" s="251">
         <f ca="1">Games!L56</f>
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="L23" s="25"/>
       <c r="M23" s="25"/>
@@ -23141,27 +23141,27 @@
       <c r="AA23" s="25"/>
       <c r="AB23" s="56"/>
       <c r="AD23" s="25"/>
-      <c r="AE23" s="264">
+      <c r="AE23" s="251">
         <f ca="1">Games!L60</f>
-        <v>117</v>
-      </c>
-      <c r="AF23" s="249" t="e" vm="106">
+        <v>115</v>
+      </c>
+      <c r="AF23" s="249" t="e" vm="108">
         <f ca="1">_xlfn.XLOOKUP(AG23,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG23" s="262" t="str">
+      <c r="AG23" s="256" t="str">
         <f ca="1">Games!O48</f>
-        <v>Campbell</v>
+        <v>Central Arkansas</v>
       </c>
       <c r="AH23" s="55"/>
       <c r="AI23" s="51"/>
-      <c r="AJ23" s="282">
+      <c r="AJ23" s="276">
         <f>IF($AU$5=TRUE,AJ15+1,"")</f>
         <v>43</v>
       </c>
       <c r="AK23" s="59">
         <f ca="1">Games!N25</f>
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="AL23" s="46" t="e" vm="106">
         <f>_xlfn.XLOOKUP(AM23,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -23174,20 +23174,20 @@
       <c r="AN23" s="27">
         <v>11</v>
       </c>
-      <c r="AO23" s="287"/>
-      <c r="AQ23" s="288"/>
+      <c r="AO23" s="277"/>
+      <c r="AQ23" s="275"/>
     </row>
     <row r="24" spans="1:43" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="16"/>
       <c r="B24" s="28"/>
       <c r="C24" s="38"/>
       <c r="D24" s="71"/>
-      <c r="F24" s="283"/>
+      <c r="F24" s="255"/>
       <c r="G24" s="15"/>
       <c r="H24" s="50"/>
-      <c r="I24" s="280"/>
-      <c r="J24" s="248"/>
-      <c r="K24" s="265"/>
+      <c r="I24" s="266"/>
+      <c r="J24" s="260"/>
+      <c r="K24" s="252"/>
       <c r="L24" s="25"/>
       <c r="M24" s="25"/>
       <c r="N24" s="50"/>
@@ -23205,15 +23205,15 @@
       <c r="AA24" s="25"/>
       <c r="AB24" s="56"/>
       <c r="AD24" s="25"/>
-      <c r="AE24" s="265"/>
+      <c r="AE24" s="252"/>
       <c r="AF24" s="250"/>
-      <c r="AG24" s="263"/>
+      <c r="AG24" s="257"/>
       <c r="AH24" s="56"/>
-      <c r="AJ24" s="283"/>
+      <c r="AJ24" s="255"/>
       <c r="AM24" s="39"/>
       <c r="AN24" s="28"/>
       <c r="AO24" s="17"/>
-      <c r="AQ24" s="288"/>
+      <c r="AQ24" s="275"/>
     </row>
     <row r="25" spans="1:43" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="16"/>
@@ -23230,19 +23230,19 @@
       </c>
       <c r="E25" s="46">
         <f ca="1">Games!L10</f>
-        <v>94</v>
-      </c>
-      <c r="F25" s="262" t="str">
+        <v>108</v>
+      </c>
+      <c r="F25" s="256" t="str">
         <f ca="1">Games!O10</f>
-        <v>Arizona State</v>
-      </c>
-      <c r="G25" s="247" t="e" vm="76">
+        <v>Arizona</v>
+      </c>
+      <c r="G25" s="259" t="e" vm="75">
         <f ca="1">_xlfn.XLOOKUP(F25,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H25" s="277">
+      <c r="H25" s="261">
         <f ca="1">Games!N40</f>
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="I25" s="24"/>
       <c r="J25" s="24"/>
@@ -23266,21 +23266,21 @@
       <c r="AD25" s="25"/>
       <c r="AE25" s="55"/>
       <c r="AG25" s="24"/>
-      <c r="AH25" s="269">
+      <c r="AH25" s="253">
         <f ca="1">Games!N48</f>
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="AI25" s="249" t="e" vm="108">
         <f ca="1">_xlfn.XLOOKUP(AJ25,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AJ25" s="262" t="str">
+      <c r="AJ25" s="256" t="str">
         <f ca="1">Games!O26</f>
         <v>Central Arkansas</v>
       </c>
       <c r="AK25" s="58">
         <f ca="1">Games!L26</f>
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="AL25" s="46" t="e" vm="107">
         <f>_xlfn.XLOOKUP(AM25,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -23294,10 +23294,10 @@
         <v>3</v>
       </c>
       <c r="AO25" s="17"/>
-      <c r="AQ25" s="288"/>
+      <c r="AQ25" s="275"/>
     </row>
     <row r="26" spans="1:43" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="283">
+      <c r="A26" s="255">
         <f>IF($AU$5=TRUE,A21+1,"")</f>
         <v>6</v>
       </c>
@@ -23305,9 +23305,9 @@
       <c r="C26" s="38"/>
       <c r="D26" s="71"/>
       <c r="E26" s="49"/>
-      <c r="F26" s="263"/>
-      <c r="G26" s="248"/>
-      <c r="H26" s="278"/>
+      <c r="F26" s="257"/>
+      <c r="G26" s="260"/>
+      <c r="H26" s="262"/>
       <c r="I26" s="24"/>
       <c r="J26" s="24"/>
       <c r="K26" s="50"/>
@@ -23330,20 +23330,20 @@
       <c r="AD26" s="25"/>
       <c r="AE26" s="56"/>
       <c r="AG26" s="24"/>
-      <c r="AH26" s="270"/>
+      <c r="AH26" s="254"/>
       <c r="AI26" s="250"/>
-      <c r="AJ26" s="263"/>
+      <c r="AJ26" s="257"/>
       <c r="AK26" s="55"/>
       <c r="AM26" s="39"/>
       <c r="AN26" s="28"/>
-      <c r="AO26" s="287">
+      <c r="AO26" s="277">
         <f>IF($AU$5=TRUE,AO22+1,"")</f>
         <v>22</v>
       </c>
-      <c r="AQ26" s="288"/>
+      <c r="AQ26" s="275"/>
     </row>
     <row r="27" spans="1:43" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="283"/>
+      <c r="A27" s="255"/>
       <c r="B27" s="27">
         <v>14</v>
       </c>
@@ -23357,70 +23357,70 @@
       </c>
       <c r="E27" s="48">
         <f ca="1">Games!N10</f>
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="F27" s="24"/>
       <c r="G27" s="24"/>
-      <c r="I27" s="283">
+      <c r="I27" s="255">
         <f>IF($AU$5=TRUE,I11+1,"")</f>
         <v>50</v>
       </c>
       <c r="J27" s="15"/>
       <c r="K27" s="50"/>
-      <c r="L27" s="279" t="str">
+      <c r="L27" s="265" t="str">
         <f ca="1">Games!O56</f>
-        <v>American</v>
-      </c>
-      <c r="M27" s="247" t="e" vm="73">
+        <v>Arizona</v>
+      </c>
+      <c r="M27" s="259" t="e" vm="75">
         <f ca="1">_xlfn.XLOOKUP(L27,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N27" s="277">
+      <c r="N27" s="261">
         <f ca="1">Games!N64</f>
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="O27" s="25"/>
       <c r="P27" s="25"/>
       <c r="Q27" s="50"/>
-      <c r="R27" s="279" t="str">
+      <c r="R27" s="265" t="str">
         <f ca="1">Games!O69</f>
-        <v>American</v>
-      </c>
-      <c r="S27" s="262"/>
-      <c r="T27" s="262"/>
-      <c r="U27" s="289" t="e" vm="73">
+        <v>Arizona</v>
+      </c>
+      <c r="S27" s="256"/>
+      <c r="T27" s="256"/>
+      <c r="U27" s="271" t="e" vm="75">
         <f ca="1">_xlfn.XLOOKUP(R27,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="V27" s="267">
+      <c r="V27" s="273">
         <f ca="1">Games!L72</f>
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="W27" s="24"/>
       <c r="X27" s="25"/>
       <c r="Y27" s="56"/>
       <c r="AA27" s="25"/>
-      <c r="AB27" s="269">
+      <c r="AB27" s="253">
         <f ca="1">Games!N66</f>
-        <v>91</v>
-      </c>
-      <c r="AC27" s="249" t="e" vm="111">
+        <v>119</v>
+      </c>
+      <c r="AC27" s="249" t="e" vm="108">
         <f ca="1">_xlfn.XLOOKUP(AD27,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AD27" s="262" t="str">
+      <c r="AD27" s="256" t="str">
         <f ca="1">Games!O60</f>
-        <v>Charleston Southern</v>
+        <v>Central Arkansas</v>
       </c>
       <c r="AE27" s="56"/>
-      <c r="AG27" s="283">
+      <c r="AG27" s="255">
         <f>IF($AU$5=TRUE,AG11+1,"")</f>
         <v>54</v>
       </c>
       <c r="AJ27" s="24"/>
       <c r="AK27" s="59">
         <f ca="1">Games!N26</f>
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="AL27" s="46" t="e" vm="108">
         <f>_xlfn.XLOOKUP(AM27,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -23433,8 +23433,8 @@
       <c r="AN27" s="27">
         <v>14</v>
       </c>
-      <c r="AO27" s="287"/>
-      <c r="AQ27" s="288"/>
+      <c r="AO27" s="277"/>
+      <c r="AQ27" s="275"/>
     </row>
     <row r="28" spans="1:43" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="16"/>
@@ -23443,29 +23443,29 @@
       <c r="D28" s="71"/>
       <c r="F28" s="24"/>
       <c r="G28" s="24"/>
-      <c r="I28" s="283"/>
+      <c r="I28" s="255"/>
       <c r="J28" s="15"/>
       <c r="K28" s="50"/>
-      <c r="L28" s="280"/>
-      <c r="M28" s="248"/>
-      <c r="N28" s="278"/>
+      <c r="L28" s="266"/>
+      <c r="M28" s="260"/>
+      <c r="N28" s="262"/>
       <c r="O28" s="25"/>
       <c r="P28" s="25"/>
       <c r="Q28" s="50"/>
-      <c r="R28" s="280"/>
-      <c r="S28" s="263"/>
-      <c r="T28" s="263"/>
-      <c r="U28" s="290"/>
-      <c r="V28" s="268"/>
+      <c r="R28" s="266"/>
+      <c r="S28" s="257"/>
+      <c r="T28" s="257"/>
+      <c r="U28" s="272"/>
+      <c r="V28" s="274"/>
       <c r="W28" s="24"/>
       <c r="X28" s="25"/>
       <c r="Y28" s="56"/>
       <c r="AA28" s="25"/>
-      <c r="AB28" s="270"/>
+      <c r="AB28" s="254"/>
       <c r="AC28" s="250"/>
-      <c r="AD28" s="263"/>
+      <c r="AD28" s="257"/>
       <c r="AE28" s="56"/>
-      <c r="AG28" s="283"/>
+      <c r="AG28" s="255"/>
       <c r="AJ28" s="24"/>
       <c r="AM28" s="39"/>
       <c r="AN28" s="28"/>
@@ -23486,19 +23486,19 @@
       </c>
       <c r="E29" s="46">
         <f ca="1">Games!L11</f>
-        <v>101</v>
-      </c>
-      <c r="F29" s="262" t="str">
+        <v>111</v>
+      </c>
+      <c r="F29" s="256" t="str">
         <f ca="1">Games!O11</f>
-        <v>Arkansas State</v>
-      </c>
-      <c r="G29" s="247" t="e" vm="78">
+        <v>Arkansas</v>
+      </c>
+      <c r="G29" s="259" t="e" vm="77">
         <f ca="1">_xlfn.XLOOKUP(F29,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H29" s="264">
+      <c r="H29" s="251">
         <f ca="1">Games!L41</f>
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="I29" s="24"/>
       <c r="J29" s="24"/>
@@ -23520,21 +23520,21 @@
       <c r="AD29" s="25"/>
       <c r="AE29" s="56"/>
       <c r="AG29" s="24"/>
-      <c r="AH29" s="264">
+      <c r="AH29" s="251">
         <f ca="1">Games!L49</f>
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI29" s="249" t="e" vm="110">
         <f ca="1">_xlfn.XLOOKUP(AJ29,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AJ29" s="262" t="str">
+      <c r="AJ29" s="256" t="str">
         <f ca="1">Games!O27</f>
         <v>Central Michigan</v>
       </c>
       <c r="AK29" s="58">
         <f ca="1">Games!L27</f>
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="AL29" s="46" t="e" vm="109">
         <f>_xlfn.XLOOKUP(AM29,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -23556,7 +23556,7 @@
       </c>
     </row>
     <row r="30" spans="1:43" ht="10.199999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="283">
+      <c r="A30" s="255">
         <f>IF($AU$5=TRUE,A26+1,"")</f>
         <v>7</v>
       </c>
@@ -23564,9 +23564,9 @@
       <c r="C30" s="38"/>
       <c r="D30" s="71"/>
       <c r="E30" s="49"/>
-      <c r="F30" s="263"/>
-      <c r="G30" s="248"/>
-      <c r="H30" s="265"/>
+      <c r="F30" s="257"/>
+      <c r="G30" s="260"/>
+      <c r="H30" s="252"/>
       <c r="I30" s="24"/>
       <c r="J30" s="24"/>
       <c r="K30" s="50"/>
@@ -23587,19 +23587,19 @@
       <c r="AD30" s="25"/>
       <c r="AE30" s="56"/>
       <c r="AG30" s="24"/>
-      <c r="AH30" s="265"/>
+      <c r="AH30" s="252"/>
       <c r="AI30" s="250"/>
-      <c r="AJ30" s="263"/>
+      <c r="AJ30" s="257"/>
       <c r="AK30" s="55"/>
       <c r="AM30" s="39"/>
       <c r="AN30" s="28"/>
-      <c r="AO30" s="287">
+      <c r="AO30" s="277">
         <f>IF($AU$5=TRUE,AO26+1,"")</f>
         <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:43" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="283"/>
+      <c r="A31" s="255"/>
       <c r="B31" s="27">
         <v>10</v>
       </c>
@@ -23613,25 +23613,25 @@
       </c>
       <c r="E31" s="48">
         <f ca="1">Games!N11</f>
-        <v>113</v>
-      </c>
-      <c r="F31" s="282">
+        <v>104</v>
+      </c>
+      <c r="F31" s="276">
         <f>IF($AU$5=TRUE,F23+1,"")</f>
         <v>36</v>
       </c>
       <c r="G31" s="14"/>
       <c r="H31" s="49"/>
-      <c r="I31" s="279" t="str">
+      <c r="I31" s="265" t="str">
         <f ca="1">Games!O41</f>
-        <v>Arkansas State</v>
-      </c>
-      <c r="J31" s="247" t="e" vm="78">
+        <v>Arkansas</v>
+      </c>
+      <c r="J31" s="259" t="e" vm="77">
         <f ca="1">_xlfn.XLOOKUP(I31,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K31" s="277">
+      <c r="K31" s="261">
         <f ca="1">Games!N56</f>
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="L31" s="25"/>
       <c r="M31" s="25"/>
@@ -23639,38 +23639,38 @@
       <c r="P31" s="25"/>
       <c r="Q31" s="50"/>
       <c r="R31" s="4"/>
-      <c r="S31" s="255" t="s">
+      <c r="S31" s="286" t="s">
         <v>0</v>
       </c>
-      <c r="T31" s="255"/>
-      <c r="U31" s="255"/>
-      <c r="V31" s="255"/>
-      <c r="W31" s="255"/>
+      <c r="T31" s="286"/>
+      <c r="U31" s="286"/>
+      <c r="V31" s="286"/>
+      <c r="W31" s="286"/>
       <c r="X31" s="5"/>
       <c r="Y31" s="56"/>
       <c r="AA31" s="25"/>
       <c r="AD31" s="25"/>
-      <c r="AE31" s="269">
+      <c r="AE31" s="253">
         <f ca="1">Games!N60</f>
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="AF31" s="249" t="e" vm="111">
         <f ca="1">_xlfn.XLOOKUP(AG31,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG31" s="262" t="str">
+      <c r="AG31" s="256" t="str">
         <f ca="1">Games!O49</f>
         <v>Charleston Southern</v>
       </c>
       <c r="AH31" s="55"/>
       <c r="AI31" s="51"/>
-      <c r="AJ31" s="282">
+      <c r="AJ31" s="276">
         <f>IF($AU$5=TRUE,AJ23+1,"")</f>
         <v>44</v>
       </c>
       <c r="AK31" s="59">
         <f ca="1">Games!N27</f>
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="AL31" s="46" t="e" vm="110">
         <f>_xlfn.XLOOKUP(AM31,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -23683,42 +23683,42 @@
       <c r="AN31" s="27">
         <v>10</v>
       </c>
-      <c r="AO31" s="287"/>
+      <c r="AO31" s="277"/>
     </row>
     <row r="32" spans="1:43" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="16"/>
       <c r="B32" s="28"/>
       <c r="C32" s="38"/>
       <c r="D32" s="71"/>
-      <c r="F32" s="283"/>
+      <c r="F32" s="255"/>
       <c r="G32" s="15"/>
       <c r="H32" s="50"/>
-      <c r="I32" s="280"/>
-      <c r="J32" s="248"/>
-      <c r="K32" s="278"/>
+      <c r="I32" s="266"/>
+      <c r="J32" s="260"/>
+      <c r="K32" s="262"/>
       <c r="L32" s="25"/>
       <c r="M32" s="25"/>
       <c r="O32" s="25"/>
       <c r="P32" s="25"/>
       <c r="Q32" s="50"/>
       <c r="R32" s="30"/>
-      <c r="S32" s="271" t="str">
+      <c r="S32" s="293" t="str">
         <f ca="1">Games!O72</f>
-        <v>American</v>
-      </c>
-      <c r="T32" s="272"/>
-      <c r="U32" s="272"/>
-      <c r="V32" s="272"/>
-      <c r="W32" s="273"/>
+        <v>Arizona</v>
+      </c>
+      <c r="T32" s="294"/>
+      <c r="U32" s="294"/>
+      <c r="V32" s="294"/>
+      <c r="W32" s="295"/>
       <c r="X32" s="31"/>
       <c r="Y32" s="56"/>
       <c r="AA32" s="25"/>
       <c r="AD32" s="25"/>
-      <c r="AE32" s="270"/>
+      <c r="AE32" s="254"/>
       <c r="AF32" s="250"/>
-      <c r="AG32" s="263"/>
+      <c r="AG32" s="257"/>
       <c r="AH32" s="56"/>
-      <c r="AJ32" s="283"/>
+      <c r="AJ32" s="255"/>
       <c r="AM32" s="39"/>
       <c r="AN32" s="28"/>
       <c r="AO32" s="17"/>
@@ -23738,19 +23738,19 @@
       </c>
       <c r="E33" s="46">
         <f ca="1">Games!L12</f>
-        <v>93</v>
-      </c>
-      <c r="F33" s="262" t="str">
+        <v>100</v>
+      </c>
+      <c r="F33" s="256" t="str">
         <f ca="1">Games!O12</f>
-        <v>Army</v>
-      </c>
-      <c r="G33" s="247" t="e" vm="80">
+        <v>Arkansas-Pine Bluff</v>
+      </c>
+      <c r="G33" s="259" t="e" vm="79">
         <f ca="1">_xlfn.XLOOKUP(F33,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H33" s="277">
+      <c r="H33" s="261">
         <f ca="1">Games!N41</f>
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I33" s="24"/>
       <c r="J33" s="24"/>
@@ -23760,31 +23760,31 @@
       <c r="P33" s="25"/>
       <c r="Q33" s="50"/>
       <c r="R33" s="30"/>
-      <c r="S33" s="274"/>
-      <c r="T33" s="275"/>
-      <c r="U33" s="275"/>
-      <c r="V33" s="275"/>
-      <c r="W33" s="276"/>
+      <c r="S33" s="296"/>
+      <c r="T33" s="297"/>
+      <c r="U33" s="297"/>
+      <c r="V33" s="297"/>
+      <c r="W33" s="298"/>
       <c r="X33" s="31"/>
       <c r="Y33" s="56"/>
       <c r="AA33" s="25"/>
       <c r="AD33" s="25"/>
       <c r="AG33" s="24"/>
-      <c r="AH33" s="269">
+      <c r="AH33" s="253">
         <f ca="1">Games!N49</f>
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="AI33" s="249" t="e" vm="111">
         <f ca="1">_xlfn.XLOOKUP(AJ33,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AJ33" s="262" t="str">
+      <c r="AJ33" s="256" t="str">
         <f ca="1">Games!O28</f>
         <v>Charleston Southern</v>
       </c>
       <c r="AK33" s="58">
         <f ca="1">Games!L28</f>
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="AL33" s="46" t="e" vm="111">
         <f>_xlfn.XLOOKUP(AM33,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -23801,7 +23801,7 @@
       <c r="AQ33" s="9"/>
     </row>
     <row r="34" spans="1:43" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="283">
+      <c r="A34" s="255">
         <f>IF($AU$5=TRUE,A30+1,"")</f>
         <v>8</v>
       </c>
@@ -23809,9 +23809,9 @@
       <c r="C34" s="38"/>
       <c r="D34" s="71"/>
       <c r="E34" s="49"/>
-      <c r="F34" s="263"/>
-      <c r="G34" s="248"/>
-      <c r="H34" s="278"/>
+      <c r="F34" s="257"/>
+      <c r="G34" s="260"/>
+      <c r="H34" s="262"/>
       <c r="I34" s="24"/>
       <c r="J34" s="24"/>
       <c r="L34" s="25"/>
@@ -23830,20 +23830,20 @@
       <c r="AA34" s="25"/>
       <c r="AD34" s="25"/>
       <c r="AG34" s="24"/>
-      <c r="AH34" s="270"/>
+      <c r="AH34" s="254"/>
       <c r="AI34" s="250"/>
-      <c r="AJ34" s="263"/>
+      <c r="AJ34" s="257"/>
       <c r="AK34" s="55"/>
       <c r="AM34" s="39"/>
       <c r="AN34" s="28"/>
-      <c r="AO34" s="287">
+      <c r="AO34" s="277">
         <f>IF($AU$5=TRUE,AO30+1,"")</f>
         <v>24</v>
       </c>
-      <c r="AQ34" s="288"/>
+      <c r="AQ34" s="275"/>
     </row>
     <row r="35" spans="1:43" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="283"/>
+      <c r="A35" s="255"/>
       <c r="B35" s="27">
         <v>15</v>
       </c>
@@ -23857,7 +23857,7 @@
       </c>
       <c r="E35" s="48">
         <f ca="1">Games!N12</f>
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="F35" s="24"/>
       <c r="G35" s="24"/>
@@ -23873,12 +23873,12 @@
       <c r="Q35" s="50"/>
       <c r="R35" s="25"/>
       <c r="S35" s="25"/>
-      <c r="T35" s="283">
+      <c r="T35" s="255">
         <f>IF($AU$5=TRUE,AA35+1,"")</f>
         <v>63</v>
       </c>
-      <c r="U35" s="283"/>
-      <c r="V35" s="283"/>
+      <c r="U35" s="255"/>
+      <c r="V35" s="255"/>
       <c r="W35" s="25"/>
       <c r="X35" s="25"/>
       <c r="Y35" s="56"/>
@@ -23891,7 +23891,7 @@
       <c r="AJ35" s="24"/>
       <c r="AK35" s="59">
         <f ca="1">Games!N28</f>
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AL35" s="46" t="e" vm="112">
         <f>_xlfn.XLOOKUP(AM35,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -23904,8 +23904,8 @@
       <c r="AN35" s="27">
         <v>15</v>
       </c>
-      <c r="AO35" s="287"/>
-      <c r="AQ35" s="288"/>
+      <c r="AO35" s="277"/>
+      <c r="AQ35" s="275"/>
     </row>
     <row r="36" spans="1:43" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="16"/>
@@ -23936,7 +23936,7 @@
       <c r="AM36" s="39"/>
       <c r="AN36" s="28"/>
       <c r="AO36" s="17"/>
-      <c r="AQ36" s="288"/>
+      <c r="AQ36" s="275"/>
     </row>
     <row r="37" spans="1:43" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="16"/>
@@ -23953,19 +23953,19 @@
       </c>
       <c r="E37" s="46">
         <f ca="1">Games!L13</f>
-        <v>113</v>
-      </c>
-      <c r="F37" s="262" t="str">
+        <v>104</v>
+      </c>
+      <c r="F37" s="256" t="str">
         <f ca="1">Games!O13</f>
-        <v>Auburn</v>
-      </c>
-      <c r="G37" s="247" t="e" vm="81">
+        <v>Austin Peay</v>
+      </c>
+      <c r="G37" s="259" t="e" vm="82">
         <f ca="1">_xlfn.XLOOKUP(F37,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H37" s="264">
+      <c r="H37" s="251">
         <f ca="1">Games!L42</f>
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="I37" s="24"/>
       <c r="J37" s="24"/>
@@ -23985,21 +23985,21 @@
       <c r="AA37" s="25"/>
       <c r="AD37" s="25"/>
       <c r="AG37" s="24"/>
-      <c r="AH37" s="264">
+      <c r="AH37" s="251">
         <f ca="1">Games!L50</f>
-        <v>114</v>
-      </c>
-      <c r="AI37" s="249" t="e" vm="114">
+        <v>116</v>
+      </c>
+      <c r="AI37" s="249" t="e" vm="113">
         <f ca="1">_xlfn.XLOOKUP(AJ37,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AJ37" s="262" t="str">
+      <c r="AJ37" s="256" t="str">
         <f ca="1">Games!O29</f>
-        <v>Chicago State</v>
+        <v>Chattanooga</v>
       </c>
       <c r="AK37" s="58">
         <f ca="1">Games!L29</f>
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="AL37" s="46" t="e" vm="113">
         <f>_xlfn.XLOOKUP(AM37,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -24013,10 +24013,10 @@
         <v>1</v>
       </c>
       <c r="AO37" s="17"/>
-      <c r="AQ37" s="288"/>
+      <c r="AQ37" s="275"/>
     </row>
     <row r="38" spans="1:43" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="283">
+      <c r="A38" s="255">
         <f>IF($AU$5=TRUE,A34+1,"")</f>
         <v>9</v>
       </c>
@@ -24024,9 +24024,9 @@
       <c r="C38" s="38"/>
       <c r="D38" s="71"/>
       <c r="E38" s="49"/>
-      <c r="F38" s="263"/>
-      <c r="G38" s="248"/>
-      <c r="H38" s="265"/>
+      <c r="F38" s="257"/>
+      <c r="G38" s="260"/>
+      <c r="H38" s="252"/>
       <c r="I38" s="24"/>
       <c r="J38" s="24"/>
       <c r="L38" s="25"/>
@@ -24045,19 +24045,19 @@
       <c r="AA38" s="25"/>
       <c r="AD38" s="25"/>
       <c r="AG38" s="24"/>
-      <c r="AH38" s="265"/>
+      <c r="AH38" s="252"/>
       <c r="AI38" s="250"/>
-      <c r="AJ38" s="263"/>
+      <c r="AJ38" s="257"/>
       <c r="AK38" s="55"/>
       <c r="AM38" s="39"/>
       <c r="AN38" s="28"/>
-      <c r="AO38" s="287">
+      <c r="AO38" s="277">
         <f>IF($AU$5=TRUE,AO34+1,"")</f>
         <v>25</v>
       </c>
     </row>
     <row r="39" spans="1:43" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="283"/>
+      <c r="A39" s="255"/>
       <c r="B39" s="27">
         <v>16</v>
       </c>
@@ -24071,25 +24071,25 @@
       </c>
       <c r="E39" s="48">
         <f ca="1">Games!N13</f>
-        <v>97</v>
-      </c>
-      <c r="F39" s="282">
+        <v>113</v>
+      </c>
+      <c r="F39" s="276">
         <f>IF($AU$5=TRUE,F31+1,"")</f>
         <v>37</v>
       </c>
       <c r="G39" s="14"/>
       <c r="H39" s="49"/>
-      <c r="I39" s="279" t="str">
+      <c r="I39" s="265" t="str">
         <f ca="1">Games!O42</f>
         <v>Ball State</v>
       </c>
-      <c r="J39" s="247" t="e" vm="83">
+      <c r="J39" s="259" t="e" vm="83">
         <f ca="1">_xlfn.XLOOKUP(I39,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K39" s="264">
+      <c r="K39" s="251">
         <f ca="1">Games!L57</f>
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="L39" s="25"/>
       <c r="M39" s="25"/>
@@ -24098,44 +24098,44 @@
       <c r="Q39" s="50"/>
       <c r="R39" s="25"/>
       <c r="S39" s="25"/>
-      <c r="T39" s="267">
+      <c r="T39" s="273">
         <f ca="1">Games!N72</f>
-        <v>91</v>
-      </c>
-      <c r="U39" s="293" t="e" vm="97">
+        <v>95</v>
+      </c>
+      <c r="U39" s="267" t="e" vm="123">
         <f ca="1">_xlfn.XLOOKUP(V39,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="V39" s="262" t="str">
+      <c r="V39" s="256" t="str">
         <f ca="1">Games!O70</f>
-        <v>Bucknell</v>
-      </c>
-      <c r="W39" s="262"/>
-      <c r="X39" s="295"/>
+        <v>Columbia</v>
+      </c>
+      <c r="W39" s="256"/>
+      <c r="X39" s="269"/>
       <c r="Y39" s="56"/>
       <c r="AA39" s="25"/>
       <c r="AD39" s="25"/>
-      <c r="AE39" s="269">
+      <c r="AE39" s="253">
         <f ca="1">Games!L61</f>
-        <v>102</v>
-      </c>
-      <c r="AF39" s="249" t="e" vm="114">
+        <v>96</v>
+      </c>
+      <c r="AF39" s="249" t="e" vm="113">
         <f ca="1">_xlfn.XLOOKUP(AG39,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG39" s="262" t="str">
+      <c r="AG39" s="256" t="str">
         <f ca="1">Games!O50</f>
-        <v>Chicago State</v>
+        <v>Chattanooga</v>
       </c>
       <c r="AH39" s="55"/>
       <c r="AI39" s="51"/>
-      <c r="AJ39" s="282">
+      <c r="AJ39" s="276">
         <f>IF($AU$5=TRUE,AJ31+1,"")</f>
         <v>45</v>
       </c>
       <c r="AK39" s="59">
         <f ca="1">Games!N29</f>
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="AL39" s="46" t="e" vm="114">
         <f>_xlfn.XLOOKUP(AM39,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -24148,19 +24148,19 @@
       <c r="AN39" s="27">
         <v>16</v>
       </c>
-      <c r="AO39" s="287"/>
+      <c r="AO39" s="277"/>
     </row>
     <row r="40" spans="1:43" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="16"/>
       <c r="B40" s="28"/>
       <c r="C40" s="38"/>
       <c r="D40" s="71"/>
-      <c r="F40" s="283"/>
+      <c r="F40" s="255"/>
       <c r="G40" s="15"/>
       <c r="H40" s="50"/>
-      <c r="I40" s="280"/>
-      <c r="J40" s="248"/>
-      <c r="K40" s="265"/>
+      <c r="I40" s="266"/>
+      <c r="J40" s="260"/>
+      <c r="K40" s="252"/>
       <c r="L40" s="25"/>
       <c r="M40" s="25"/>
       <c r="O40" s="25"/>
@@ -24168,19 +24168,19 @@
       <c r="Q40" s="50"/>
       <c r="R40" s="25"/>
       <c r="S40" s="25"/>
-      <c r="T40" s="268"/>
-      <c r="U40" s="294"/>
-      <c r="V40" s="263"/>
-      <c r="W40" s="263"/>
-      <c r="X40" s="296"/>
+      <c r="T40" s="274"/>
+      <c r="U40" s="268"/>
+      <c r="V40" s="257"/>
+      <c r="W40" s="257"/>
+      <c r="X40" s="270"/>
       <c r="Y40" s="56"/>
       <c r="AA40" s="25"/>
       <c r="AD40" s="25"/>
-      <c r="AE40" s="270"/>
+      <c r="AE40" s="254"/>
       <c r="AF40" s="250"/>
-      <c r="AG40" s="263"/>
+      <c r="AG40" s="257"/>
       <c r="AH40" s="56"/>
-      <c r="AJ40" s="283"/>
+      <c r="AJ40" s="255"/>
       <c r="AM40" s="39"/>
       <c r="AN40" s="28"/>
       <c r="AO40" s="17"/>
@@ -24200,19 +24200,19 @@
       </c>
       <c r="E41" s="46">
         <f ca="1">Games!L14</f>
-        <v>111</v>
-      </c>
-      <c r="F41" s="262" t="str">
+        <v>112</v>
+      </c>
+      <c r="F41" s="256" t="str">
         <f ca="1">Games!O14</f>
         <v>Ball State</v>
       </c>
-      <c r="G41" s="247" t="e" vm="83">
+      <c r="G41" s="259" t="e" vm="83">
         <f ca="1">_xlfn.XLOOKUP(F41,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H41" s="277">
+      <c r="H41" s="261">
         <f ca="1">Games!N42</f>
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="I41" s="24"/>
       <c r="J41" s="24"/>
@@ -24234,21 +24234,21 @@
       <c r="AD41" s="25"/>
       <c r="AE41" s="55"/>
       <c r="AG41" s="24"/>
-      <c r="AH41" s="269">
+      <c r="AH41" s="253">
         <f ca="1">Games!N50</f>
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="AI41" s="249" t="e" vm="116">
         <f ca="1">_xlfn.XLOOKUP(AJ41,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AJ41" s="262" t="str">
+      <c r="AJ41" s="256" t="str">
         <f ca="1">Games!O30</f>
         <v>Clemson</v>
       </c>
       <c r="AK41" s="58">
         <f ca="1">Games!L30</f>
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="AL41" s="46" t="e" vm="115">
         <f>_xlfn.XLOOKUP(AM41,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -24264,7 +24264,7 @@
       <c r="AO41" s="17"/>
     </row>
     <row r="42" spans="1:43" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="283">
+      <c r="A42" s="255">
         <f>IF($AU$5=TRUE,A38+1,"")</f>
         <v>10</v>
       </c>
@@ -24272,9 +24272,9 @@
       <c r="C42" s="38"/>
       <c r="D42" s="71"/>
       <c r="E42" s="49"/>
-      <c r="F42" s="263"/>
-      <c r="G42" s="248"/>
-      <c r="H42" s="278"/>
+      <c r="F42" s="257"/>
+      <c r="G42" s="260"/>
+      <c r="H42" s="262"/>
       <c r="I42" s="24"/>
       <c r="J42" s="24"/>
       <c r="K42" s="50"/>
@@ -24295,19 +24295,19 @@
       <c r="AD42" s="25"/>
       <c r="AE42" s="56"/>
       <c r="AG42" s="24"/>
-      <c r="AH42" s="270"/>
+      <c r="AH42" s="254"/>
       <c r="AI42" s="250"/>
-      <c r="AJ42" s="263"/>
+      <c r="AJ42" s="257"/>
       <c r="AK42" s="55"/>
       <c r="AM42" s="39"/>
       <c r="AN42" s="28"/>
-      <c r="AO42" s="287">
+      <c r="AO42" s="277">
         <f>IF($AU$5=TRUE,AO38+1,"")</f>
         <v>26</v>
       </c>
     </row>
     <row r="43" spans="1:43" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="283"/>
+      <c r="A43" s="255"/>
       <c r="B43" s="27">
         <v>9</v>
       </c>
@@ -24321,27 +24321,27 @@
       </c>
       <c r="E43" s="48">
         <f ca="1">Games!N14</f>
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="F43" s="24"/>
       <c r="G43" s="24"/>
-      <c r="I43" s="283">
+      <c r="I43" s="255">
         <f>IF($AU$5=TRUE,I27+1,"")</f>
         <v>51</v>
       </c>
       <c r="J43" s="15"/>
       <c r="K43" s="50"/>
-      <c r="L43" s="279" t="str">
+      <c r="L43" s="265" t="str">
         <f ca="1">Games!O57</f>
-        <v>Belmont</v>
-      </c>
-      <c r="M43" s="247" t="e" vm="86">
+        <v>Binghamton</v>
+      </c>
+      <c r="M43" s="259" t="e" vm="88">
         <f ca="1">_xlfn.XLOOKUP(L43,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N43" s="264">
+      <c r="N43" s="251">
         <f ca="1">Games!L65</f>
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="O43" s="25"/>
       <c r="P43" s="25"/>
@@ -24355,27 +24355,27 @@
       <c r="X43" s="25"/>
       <c r="Y43" s="56"/>
       <c r="AA43" s="25"/>
-      <c r="AB43" s="264">
+      <c r="AB43" s="251">
         <f ca="1">Games!L67</f>
-        <v>99</v>
-      </c>
-      <c r="AC43" s="249" t="e" vm="118">
+        <v>109</v>
+      </c>
+      <c r="AC43" s="249" t="e" vm="117">
         <f ca="1">_xlfn.XLOOKUP(AD43,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AD43" s="291" t="str">
+      <c r="AD43" s="263" t="str">
         <f ca="1">Games!O61</f>
-        <v>Coastal Carolina</v>
+        <v>Cleveland State</v>
       </c>
       <c r="AE43" s="56"/>
-      <c r="AG43" s="283">
+      <c r="AG43" s="255">
         <f>IF($AU$5=TRUE,AG27+1,"")</f>
         <v>55</v>
       </c>
       <c r="AJ43" s="24"/>
       <c r="AK43" s="59">
         <f ca="1">Games!N30</f>
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="AL43" s="46" t="e" vm="116">
         <f>_xlfn.XLOOKUP(AM43,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -24388,7 +24388,7 @@
       <c r="AN43" s="27">
         <v>9</v>
       </c>
-      <c r="AO43" s="287"/>
+      <c r="AO43" s="277"/>
     </row>
     <row r="44" spans="1:43" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="16"/>
@@ -24397,12 +24397,12 @@
       <c r="D44" s="71"/>
       <c r="F44" s="24"/>
       <c r="G44" s="24"/>
-      <c r="I44" s="283"/>
+      <c r="I44" s="255"/>
       <c r="J44" s="15"/>
       <c r="K44" s="50"/>
-      <c r="L44" s="280"/>
-      <c r="M44" s="248"/>
-      <c r="N44" s="265"/>
+      <c r="L44" s="266"/>
+      <c r="M44" s="260"/>
+      <c r="N44" s="252"/>
       <c r="O44" s="25"/>
       <c r="P44" s="25"/>
       <c r="Q44" s="50"/>
@@ -24415,11 +24415,11 @@
       <c r="X44" s="25"/>
       <c r="Y44" s="56"/>
       <c r="AA44" s="25"/>
-      <c r="AB44" s="265"/>
+      <c r="AB44" s="252"/>
       <c r="AC44" s="250"/>
-      <c r="AD44" s="292"/>
+      <c r="AD44" s="264"/>
       <c r="AE44" s="56"/>
-      <c r="AG44" s="283"/>
+      <c r="AG44" s="255"/>
       <c r="AJ44" s="24"/>
       <c r="AM44" s="39"/>
       <c r="AN44" s="28"/>
@@ -24440,19 +24440,19 @@
       </c>
       <c r="E45" s="46">
         <f ca="1">Games!L15</f>
-        <v>91</v>
-      </c>
-      <c r="F45" s="262" t="str">
+        <v>90</v>
+      </c>
+      <c r="F45" s="256" t="str">
         <f ca="1">Games!O15</f>
         <v>Belmont</v>
       </c>
-      <c r="G45" s="247" t="e" vm="86">
+      <c r="G45" s="259" t="e" vm="86">
         <f ca="1">_xlfn.XLOOKUP(F45,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H45" s="264">
+      <c r="H45" s="251">
         <f ca="1">Games!L43</f>
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="I45" s="24"/>
       <c r="J45" s="24"/>
@@ -24476,17 +24476,17 @@
       <c r="AD45" s="25"/>
       <c r="AE45" s="56"/>
       <c r="AG45" s="24"/>
-      <c r="AH45" s="264">
+      <c r="AH45" s="251">
         <f ca="1">Games!L51</f>
-        <v>109</v>
-      </c>
-      <c r="AI45" s="249" t="e" vm="118">
+        <v>105</v>
+      </c>
+      <c r="AI45" s="249" t="e" vm="117">
         <f ca="1">_xlfn.XLOOKUP(AJ45,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AJ45" s="262" t="str">
+      <c r="AJ45" s="256" t="str">
         <f ca="1">Games!O31</f>
-        <v>Coastal Carolina</v>
+        <v>Cleveland State</v>
       </c>
       <c r="AK45" s="58">
         <f ca="1">Games!L31</f>
@@ -24506,7 +24506,7 @@
       <c r="AO45" s="17"/>
     </row>
     <row r="46" spans="1:43" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="283">
+      <c r="A46" s="255">
         <f>IF($AU$5=TRUE,A42+1,"")</f>
         <v>11</v>
       </c>
@@ -24514,9 +24514,9 @@
       <c r="C46" s="38"/>
       <c r="D46" s="71"/>
       <c r="E46" s="49"/>
-      <c r="F46" s="263"/>
-      <c r="G46" s="248"/>
-      <c r="H46" s="265"/>
+      <c r="F46" s="257"/>
+      <c r="G46" s="260"/>
+      <c r="H46" s="252"/>
       <c r="I46" s="24"/>
       <c r="J46" s="24"/>
       <c r="K46" s="50"/>
@@ -24539,19 +24539,19 @@
       <c r="AD46" s="25"/>
       <c r="AE46" s="56"/>
       <c r="AG46" s="24"/>
-      <c r="AH46" s="265"/>
+      <c r="AH46" s="252"/>
       <c r="AI46" s="250"/>
-      <c r="AJ46" s="263"/>
+      <c r="AJ46" s="257"/>
       <c r="AK46" s="55"/>
       <c r="AM46" s="39"/>
       <c r="AN46" s="28"/>
-      <c r="AO46" s="287">
+      <c r="AO46" s="277">
         <f>IF($AU$5=TRUE,AO42+1,"")</f>
         <v>27</v>
       </c>
     </row>
     <row r="47" spans="1:43" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="283"/>
+      <c r="A47" s="255"/>
       <c r="B47" s="27">
         <v>12</v>
       </c>
@@ -24565,25 +24565,25 @@
       </c>
       <c r="E47" s="48">
         <f ca="1">Games!N15</f>
-        <v>105</v>
-      </c>
-      <c r="F47" s="282">
+        <v>101</v>
+      </c>
+      <c r="F47" s="276">
         <f>IF($AU$5=TRUE,F39+1,"")</f>
         <v>38</v>
       </c>
       <c r="G47" s="14"/>
       <c r="H47" s="49"/>
-      <c r="I47" s="279" t="str">
+      <c r="I47" s="265" t="str">
         <f ca="1">Games!O43</f>
-        <v>Belmont</v>
-      </c>
-      <c r="J47" s="247" t="e" vm="86">
+        <v>Binghamton</v>
+      </c>
+      <c r="J47" s="259" t="e" vm="88">
         <f ca="1">_xlfn.XLOOKUP(I47,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K47" s="277">
+      <c r="K47" s="261">
         <f ca="1">Games!N57</f>
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="L47" s="25"/>
       <c r="M47" s="25"/>
@@ -24602,27 +24602,27 @@
       <c r="AA47" s="25"/>
       <c r="AB47" s="56"/>
       <c r="AD47" s="25"/>
-      <c r="AE47" s="269">
+      <c r="AE47" s="253">
         <f ca="1">Games!N61</f>
-        <v>120</v>
-      </c>
-      <c r="AF47" s="249" t="e" vm="118">
+        <v>104</v>
+      </c>
+      <c r="AF47" s="249" t="e" vm="117">
         <f ca="1">_xlfn.XLOOKUP(AG47,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG47" s="262" t="str">
+      <c r="AG47" s="256" t="str">
         <f ca="1">Games!O51</f>
-        <v>Coastal Carolina</v>
+        <v>Cleveland State</v>
       </c>
       <c r="AH47" s="55"/>
       <c r="AI47" s="51"/>
-      <c r="AJ47" s="282">
+      <c r="AJ47" s="276">
         <f>IF($AU$5=TRUE,AJ39+1,"")</f>
         <v>46</v>
       </c>
       <c r="AK47" s="59">
         <f ca="1">Games!N31</f>
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="AL47" s="46" t="e" vm="118">
         <f>_xlfn.XLOOKUP(AM47,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -24635,19 +24635,19 @@
       <c r="AN47" s="27">
         <v>12</v>
       </c>
-      <c r="AO47" s="287"/>
+      <c r="AO47" s="277"/>
     </row>
     <row r="48" spans="1:43" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="16"/>
       <c r="B48" s="28"/>
       <c r="C48" s="38"/>
       <c r="D48" s="71"/>
-      <c r="F48" s="283"/>
+      <c r="F48" s="255"/>
       <c r="G48" s="15"/>
       <c r="H48" s="50"/>
-      <c r="I48" s="280"/>
-      <c r="J48" s="248"/>
-      <c r="K48" s="278"/>
+      <c r="I48" s="266"/>
+      <c r="J48" s="260"/>
+      <c r="K48" s="262"/>
       <c r="L48" s="25"/>
       <c r="M48" s="25"/>
       <c r="N48" s="50"/>
@@ -24665,11 +24665,11 @@
       <c r="AA48" s="25"/>
       <c r="AB48" s="56"/>
       <c r="AD48" s="25"/>
-      <c r="AE48" s="270"/>
+      <c r="AE48" s="254"/>
       <c r="AF48" s="250"/>
-      <c r="AG48" s="263"/>
+      <c r="AG48" s="257"/>
       <c r="AH48" s="56"/>
-      <c r="AJ48" s="283"/>
+      <c r="AJ48" s="255"/>
       <c r="AM48" s="39"/>
       <c r="AN48" s="28"/>
       <c r="AO48" s="17"/>
@@ -24689,19 +24689,19 @@
       </c>
       <c r="E49" s="46">
         <f ca="1">Games!L16</f>
-        <v>112</v>
-      </c>
-      <c r="F49" s="262" t="str">
+        <v>91</v>
+      </c>
+      <c r="F49" s="256" t="str">
         <f ca="1">Games!O16</f>
         <v>Binghamton</v>
       </c>
-      <c r="G49" s="247" t="e" vm="88">
+      <c r="G49" s="259" t="e" vm="88">
         <f ca="1">_xlfn.XLOOKUP(F49,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H49" s="277">
+      <c r="H49" s="261">
         <f ca="1">Games!N43</f>
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="I49" s="24"/>
       <c r="J49" s="24"/>
@@ -24723,21 +24723,21 @@
       <c r="AB49" s="56"/>
       <c r="AD49" s="25"/>
       <c r="AG49" s="24"/>
-      <c r="AH49" s="269">
+      <c r="AH49" s="253">
         <f ca="1">Games!N51</f>
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="AI49" s="249" t="e" vm="119">
         <f ca="1">_xlfn.XLOOKUP(AJ49,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AJ49" s="262" t="str">
+      <c r="AJ49" s="256" t="str">
         <f ca="1">Games!O32</f>
         <v>Colgate</v>
       </c>
       <c r="AK49" s="58">
         <f ca="1">Games!L32</f>
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="AL49" s="46" t="e" vm="119">
         <f>_xlfn.XLOOKUP(AM49,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -24753,7 +24753,7 @@
       <c r="AO49" s="17"/>
     </row>
     <row r="50" spans="1:41" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="283">
+      <c r="A50" s="255">
         <f>IF($AU$5=TRUE,A46+1,"")</f>
         <v>12</v>
       </c>
@@ -24761,9 +24761,9 @@
       <c r="C50" s="38"/>
       <c r="D50" s="71"/>
       <c r="E50" s="49"/>
-      <c r="F50" s="263"/>
-      <c r="G50" s="248"/>
-      <c r="H50" s="278"/>
+      <c r="F50" s="257"/>
+      <c r="G50" s="260"/>
+      <c r="H50" s="262"/>
       <c r="I50" s="24"/>
       <c r="J50" s="24"/>
       <c r="L50" s="25"/>
@@ -24784,19 +24784,19 @@
       <c r="AB50" s="56"/>
       <c r="AD50" s="25"/>
       <c r="AG50" s="24"/>
-      <c r="AH50" s="270"/>
+      <c r="AH50" s="254"/>
       <c r="AI50" s="250"/>
-      <c r="AJ50" s="263"/>
+      <c r="AJ50" s="257"/>
       <c r="AK50" s="55"/>
       <c r="AM50" s="39"/>
       <c r="AN50" s="28"/>
-      <c r="AO50" s="287">
+      <c r="AO50" s="277">
         <f>IF($AU$5=TRUE,AO46+1,"")</f>
         <v>28</v>
       </c>
     </row>
     <row r="51" spans="1:41" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A51" s="283"/>
+      <c r="A51" s="255"/>
       <c r="B51" s="27">
         <v>13</v>
       </c>
@@ -24810,29 +24810,29 @@
       </c>
       <c r="E51" s="48">
         <f ca="1">Games!N16</f>
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="F51" s="24"/>
       <c r="G51" s="24"/>
       <c r="I51" s="24"/>
       <c r="J51" s="24"/>
-      <c r="K51" s="266" t="s">
+      <c r="K51" s="258" t="s">
         <v>4</v>
       </c>
-      <c r="L51" s="266"/>
+      <c r="L51" s="258"/>
       <c r="M51" s="20"/>
       <c r="N51" s="50"/>
-      <c r="O51" s="279" t="str">
+      <c r="O51" s="265" t="str">
         <f ca="1">Games!O65</f>
-        <v>Bradley</v>
-      </c>
-      <c r="P51" s="247" t="e" vm="93">
+        <v>Drake</v>
+      </c>
+      <c r="P51" s="259" t="e" vm="91">
         <f ca="1">_xlfn.XLOOKUP(O51,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="Q51" s="277">
+      <c r="Q51" s="261">
         <f ca="1">Games!N69</f>
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="R51" s="25"/>
       <c r="S51" s="25"/>
@@ -24841,29 +24841,29 @@
       <c r="V51" s="25"/>
       <c r="W51" s="25"/>
       <c r="X51" s="25"/>
-      <c r="Y51" s="269">
+      <c r="Y51" s="253">
         <f ca="1">Games!N70</f>
-        <v>104</v>
-      </c>
-      <c r="Z51" s="249" t="e" vm="122">
+        <v>116</v>
+      </c>
+      <c r="Z51" s="249" t="e" vm="123">
         <f ca="1">_xlfn.XLOOKUP(AA51,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AA51" s="262" t="str">
+      <c r="AA51" s="256" t="str">
         <f ca="1">Games!O67</f>
-        <v>Colorado State</v>
+        <v>Columbia</v>
       </c>
       <c r="AB51" s="56"/>
-      <c r="AD51" s="266" t="s">
+      <c r="AD51" s="258" t="s">
         <v>14</v>
       </c>
-      <c r="AE51" s="266"/>
+      <c r="AE51" s="258"/>
       <c r="AF51" s="20"/>
       <c r="AG51" s="24"/>
       <c r="AJ51" s="24"/>
       <c r="AK51" s="59">
         <f ca="1">Games!N32</f>
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="AL51" s="46" t="e" vm="120">
         <f>_xlfn.XLOOKUP(AM51,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -24876,7 +24876,7 @@
       <c r="AN51" s="27">
         <v>13</v>
       </c>
-      <c r="AO51" s="287"/>
+      <c r="AO51" s="277"/>
     </row>
     <row r="52" spans="1:41" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A52" s="16"/>
@@ -24887,13 +24887,13 @@
       <c r="G52" s="24"/>
       <c r="I52" s="24"/>
       <c r="J52" s="24"/>
-      <c r="K52" s="266"/>
-      <c r="L52" s="266"/>
+      <c r="K52" s="258"/>
+      <c r="L52" s="258"/>
       <c r="M52" s="20"/>
       <c r="N52" s="50"/>
-      <c r="O52" s="280"/>
-      <c r="P52" s="248"/>
-      <c r="Q52" s="278"/>
+      <c r="O52" s="266"/>
+      <c r="P52" s="260"/>
+      <c r="Q52" s="262"/>
       <c r="R52" s="25"/>
       <c r="S52" s="25"/>
       <c r="T52" s="25"/>
@@ -24901,12 +24901,12 @@
       <c r="V52" s="25"/>
       <c r="W52" s="25"/>
       <c r="X52" s="25"/>
-      <c r="Y52" s="270"/>
+      <c r="Y52" s="254"/>
       <c r="Z52" s="250"/>
-      <c r="AA52" s="263"/>
+      <c r="AA52" s="257"/>
       <c r="AB52" s="56"/>
-      <c r="AD52" s="266"/>
-      <c r="AE52" s="266"/>
+      <c r="AD52" s="258"/>
+      <c r="AE52" s="258"/>
       <c r="AF52" s="20"/>
       <c r="AG52" s="24"/>
       <c r="AJ52" s="24"/>
@@ -24929,19 +24929,19 @@
       </c>
       <c r="E53" s="46">
         <f ca="1">Games!L17</f>
-        <v>103</v>
-      </c>
-      <c r="F53" s="262" t="str">
+        <v>115</v>
+      </c>
+      <c r="F53" s="256" t="str">
         <f ca="1">Games!O17</f>
         <v>Boise State</v>
       </c>
-      <c r="G53" s="247" t="e" vm="89">
+      <c r="G53" s="259" t="e" vm="89">
         <f ca="1">_xlfn.XLOOKUP(F53,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H53" s="264">
+      <c r="H53" s="251">
         <f ca="1">Games!L44</f>
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I53" s="24"/>
       <c r="J53" s="24"/>
@@ -24968,21 +24968,21 @@
         <v>60</v>
       </c>
       <c r="AG53" s="24"/>
-      <c r="AH53" s="264">
+      <c r="AH53" s="251">
         <f ca="1">Games!L52</f>
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="AI53" s="249" t="e" vm="122">
         <f ca="1">_xlfn.XLOOKUP(AJ53,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AJ53" s="262" t="str">
+      <c r="AJ53" s="256" t="str">
         <f ca="1">Games!O33</f>
         <v>Colorado State</v>
       </c>
       <c r="AK53" s="58">
         <f ca="1">Games!L33</f>
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="AL53" s="46" t="e" vm="121">
         <f>_xlfn.XLOOKUP(AM53,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -24998,7 +24998,7 @@
       <c r="AO53" s="17"/>
     </row>
     <row r="54" spans="1:41" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="283">
+      <c r="A54" s="255">
         <f>IF($AU$5=TRUE,A50+1,"")</f>
         <v>13</v>
       </c>
@@ -25006,9 +25006,9 @@
       <c r="C54" s="38"/>
       <c r="D54" s="71"/>
       <c r="E54" s="49"/>
-      <c r="F54" s="263"/>
-      <c r="G54" s="248"/>
-      <c r="H54" s="265"/>
+      <c r="F54" s="257"/>
+      <c r="G54" s="260"/>
+      <c r="H54" s="252"/>
       <c r="I54" s="24"/>
       <c r="J54" s="24"/>
       <c r="L54" s="25"/>
@@ -25027,19 +25027,19 @@
       <c r="AB54" s="56"/>
       <c r="AD54" s="25"/>
       <c r="AG54" s="24"/>
-      <c r="AH54" s="265"/>
+      <c r="AH54" s="252"/>
       <c r="AI54" s="250"/>
-      <c r="AJ54" s="263"/>
+      <c r="AJ54" s="257"/>
       <c r="AK54" s="55"/>
       <c r="AM54" s="39"/>
       <c r="AN54" s="28"/>
-      <c r="AO54" s="287">
+      <c r="AO54" s="277">
         <f>IF($AU$5=TRUE,AO50+1,"")</f>
         <v>29</v>
       </c>
     </row>
     <row r="55" spans="1:41" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="283"/>
+      <c r="A55" s="255"/>
       <c r="B55" s="27">
         <v>11</v>
       </c>
@@ -25053,25 +25053,25 @@
       </c>
       <c r="E55" s="48">
         <f ca="1">Games!N17</f>
-        <v>94</v>
-      </c>
-      <c r="F55" s="282">
+        <v>100</v>
+      </c>
+      <c r="F55" s="276">
         <f>IF($AU$5=TRUE,F47+1,"")</f>
         <v>39</v>
       </c>
       <c r="G55" s="14"/>
       <c r="H55" s="49"/>
-      <c r="I55" s="279" t="str">
+      <c r="I55" s="265" t="str">
         <f ca="1">Games!O44</f>
-        <v>Boise State</v>
-      </c>
-      <c r="J55" s="247" t="e" vm="89">
+        <v>Drake</v>
+      </c>
+      <c r="J55" s="259" t="e" vm="91">
         <f ca="1">_xlfn.XLOOKUP(I55,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K55" s="264">
+      <c r="K55" s="251">
         <f ca="1">Games!L58</f>
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L55" s="25"/>
       <c r="M55" s="25"/>
@@ -25088,27 +25088,27 @@
       <c r="AA55" s="25"/>
       <c r="AB55" s="56"/>
       <c r="AD55" s="25"/>
-      <c r="AE55" s="264">
+      <c r="AE55" s="251">
         <f ca="1">Games!L62</f>
-        <v>107</v>
-      </c>
-      <c r="AF55" s="249" t="e" vm="122">
+        <v>109</v>
+      </c>
+      <c r="AF55" s="249" t="e" vm="123">
         <f ca="1">_xlfn.XLOOKUP(AG55,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG55" s="262" t="str">
+      <c r="AG55" s="256" t="str">
         <f ca="1">Games!O52</f>
-        <v>Colorado State</v>
+        <v>Columbia</v>
       </c>
       <c r="AH55" s="55"/>
       <c r="AI55" s="51"/>
-      <c r="AJ55" s="282">
+      <c r="AJ55" s="276">
         <f>IF($AU$5=TRUE,AJ47+1,"")</f>
         <v>47</v>
       </c>
       <c r="AK55" s="59">
         <f ca="1">Games!N33</f>
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AL55" s="46" t="e" vm="122">
         <f>_xlfn.XLOOKUP(AM55,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -25121,19 +25121,19 @@
       <c r="AN55" s="32">
         <v>11</v>
       </c>
-      <c r="AO55" s="287"/>
+      <c r="AO55" s="277"/>
     </row>
     <row r="56" spans="1:41" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="16"/>
       <c r="B56" s="28"/>
       <c r="C56" s="38"/>
       <c r="D56" s="71"/>
-      <c r="F56" s="283"/>
+      <c r="F56" s="255"/>
       <c r="G56" s="15"/>
       <c r="H56" s="50"/>
-      <c r="I56" s="280"/>
-      <c r="J56" s="248"/>
-      <c r="K56" s="265"/>
+      <c r="I56" s="266"/>
+      <c r="J56" s="260"/>
+      <c r="K56" s="252"/>
       <c r="L56" s="25"/>
       <c r="M56" s="25"/>
       <c r="N56" s="50"/>
@@ -25149,11 +25149,11 @@
       <c r="AA56" s="25"/>
       <c r="AB56" s="56"/>
       <c r="AD56" s="25"/>
-      <c r="AE56" s="265"/>
+      <c r="AE56" s="252"/>
       <c r="AF56" s="250"/>
-      <c r="AG56" s="263"/>
+      <c r="AG56" s="257"/>
       <c r="AH56" s="56"/>
-      <c r="AJ56" s="283"/>
+      <c r="AJ56" s="255"/>
       <c r="AM56" s="39"/>
       <c r="AN56" s="28"/>
       <c r="AO56" s="17"/>
@@ -25165,7 +25165,7 @@
       </c>
       <c r="C57" s="36" t="str">
         <f>Games!G18</f>
-        <v>Florida</v>
+        <v>Drake</v>
       </c>
       <c r="D57" s="70" t="e" vm="91">
         <f>_xlfn.XLOOKUP(C57,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -25173,19 +25173,19 @@
       </c>
       <c r="E57" s="46">
         <f ca="1">Games!L18</f>
-        <v>119</v>
-      </c>
-      <c r="F57" s="262" t="str">
+        <v>110</v>
+      </c>
+      <c r="F57" s="256" t="str">
         <f ca="1">Games!O18</f>
-        <v>Duke</v>
-      </c>
-      <c r="G57" s="247" t="e" vm="92">
+        <v>Drake</v>
+      </c>
+      <c r="G57" s="259" t="e" vm="91">
         <f ca="1">_xlfn.XLOOKUP(F57,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H57" s="277">
+      <c r="H57" s="261">
         <f ca="1">Games!N44</f>
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="I57" s="24"/>
       <c r="J57" s="24"/>
@@ -25207,21 +25207,21 @@
       <c r="AD57" s="25"/>
       <c r="AE57" s="55"/>
       <c r="AG57" s="24"/>
-      <c r="AH57" s="269">
+      <c r="AH57" s="253">
         <f ca="1">Games!N52</f>
-        <v>91</v>
-      </c>
-      <c r="AI57" s="249" t="e" vm="124">
+        <v>103</v>
+      </c>
+      <c r="AI57" s="249" t="e" vm="123">
         <f ca="1">_xlfn.XLOOKUP(AJ57,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AJ57" s="262" t="str">
+      <c r="AJ57" s="256" t="str">
         <f ca="1">Games!O34</f>
-        <v>Connecticut</v>
+        <v>Columbia</v>
       </c>
       <c r="AK57" s="58">
         <f ca="1">Games!L34</f>
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="AL57" s="46" t="e" vm="123">
         <f>_xlfn.XLOOKUP(AM57,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -25237,7 +25237,7 @@
       <c r="AO57" s="17"/>
     </row>
     <row r="58" spans="1:41" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="283">
+      <c r="A58" s="255">
         <f>IF($AU$5=TRUE,A54+1,"")</f>
         <v>14</v>
       </c>
@@ -25245,9 +25245,9 @@
       <c r="C58" s="38"/>
       <c r="D58" s="71"/>
       <c r="E58" s="49"/>
-      <c r="F58" s="263"/>
-      <c r="G58" s="248"/>
-      <c r="H58" s="278"/>
+      <c r="F58" s="257"/>
+      <c r="G58" s="260"/>
+      <c r="H58" s="262"/>
       <c r="I58" s="24"/>
       <c r="J58" s="24"/>
       <c r="K58" s="50"/>
@@ -25268,19 +25268,19 @@
       <c r="AD58" s="25"/>
       <c r="AE58" s="56"/>
       <c r="AG58" s="24"/>
-      <c r="AH58" s="270"/>
+      <c r="AH58" s="254"/>
       <c r="AI58" s="250"/>
-      <c r="AJ58" s="263"/>
+      <c r="AJ58" s="257"/>
       <c r="AK58" s="55"/>
       <c r="AM58" s="39"/>
       <c r="AN58" s="28"/>
-      <c r="AO58" s="287">
+      <c r="AO58" s="277">
         <f>IF($AU$5=TRUE,AO54+1,"")</f>
         <v>30</v>
       </c>
     </row>
     <row r="59" spans="1:41" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="283"/>
+      <c r="A59" s="255"/>
       <c r="B59" s="27">
         <v>14</v>
       </c>
@@ -25294,27 +25294,27 @@
       </c>
       <c r="E59" s="48">
         <f ca="1">Games!N18</f>
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="F59" s="24"/>
       <c r="G59" s="24"/>
-      <c r="I59" s="283">
+      <c r="I59" s="255">
         <f>IF($AU$5=TRUE,I43+1,"")</f>
         <v>52</v>
       </c>
       <c r="J59" s="15"/>
       <c r="K59" s="50"/>
-      <c r="L59" s="279" t="str">
+      <c r="L59" s="265" t="str">
         <f ca="1">Games!O58</f>
-        <v>Bradley</v>
-      </c>
-      <c r="M59" s="247" t="e" vm="93">
+        <v>Drake</v>
+      </c>
+      <c r="M59" s="259" t="e" vm="91">
         <f ca="1">_xlfn.XLOOKUP(L59,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N59" s="277">
+      <c r="N59" s="261">
         <f ca="1">Games!N65</f>
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="O59" s="25"/>
       <c r="P59" s="25"/>
@@ -25326,27 +25326,27 @@
       <c r="W59" s="25"/>
       <c r="X59" s="25"/>
       <c r="AA59" s="25"/>
-      <c r="AB59" s="269">
+      <c r="AB59" s="253">
         <f ca="1">Games!N67</f>
-        <v>119</v>
-      </c>
-      <c r="AC59" s="249" t="e" vm="122">
+        <v>114</v>
+      </c>
+      <c r="AC59" s="249" t="e" vm="123">
         <f ca="1">_xlfn.XLOOKUP(AD59,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AD59" s="262" t="str">
+      <c r="AD59" s="256" t="str">
         <f ca="1">Games!O62</f>
-        <v>Colorado State</v>
+        <v>Columbia</v>
       </c>
       <c r="AE59" s="56"/>
-      <c r="AG59" s="283">
+      <c r="AG59" s="255">
         <f>IF($AU$5=TRUE,AG43+1,"")</f>
         <v>56</v>
       </c>
       <c r="AJ59" s="24"/>
       <c r="AK59" s="59">
         <f ca="1">Games!N34</f>
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="AL59" s="46" t="e" vm="124">
         <f>_xlfn.XLOOKUP(AM59,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -25359,7 +25359,7 @@
       <c r="AN59" s="27">
         <v>14</v>
       </c>
-      <c r="AO59" s="287"/>
+      <c r="AO59" s="277"/>
     </row>
     <row r="60" spans="1:41" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="16"/>
@@ -25368,12 +25368,12 @@
       <c r="D60" s="71"/>
       <c r="F60" s="24"/>
       <c r="G60" s="24"/>
-      <c r="I60" s="283"/>
+      <c r="I60" s="255"/>
       <c r="J60" s="15"/>
       <c r="K60" s="50"/>
-      <c r="L60" s="280"/>
-      <c r="M60" s="248"/>
-      <c r="N60" s="278"/>
+      <c r="L60" s="266"/>
+      <c r="M60" s="260"/>
+      <c r="N60" s="262"/>
       <c r="O60" s="25"/>
       <c r="P60" s="25"/>
       <c r="Q60" s="25"/>
@@ -25385,11 +25385,11 @@
       <c r="W60" s="25"/>
       <c r="X60" s="25"/>
       <c r="AA60" s="25"/>
-      <c r="AB60" s="270"/>
+      <c r="AB60" s="254"/>
       <c r="AC60" s="250"/>
-      <c r="AD60" s="263"/>
+      <c r="AD60" s="257"/>
       <c r="AE60" s="56"/>
-      <c r="AG60" s="283"/>
+      <c r="AG60" s="255"/>
       <c r="AJ60" s="24"/>
       <c r="AM60" s="39"/>
       <c r="AN60" s="28"/>
@@ -25410,19 +25410,19 @@
       </c>
       <c r="E61" s="46">
         <f ca="1">Games!L19</f>
-        <v>114</v>
-      </c>
-      <c r="F61" s="262" t="str">
+        <v>91</v>
+      </c>
+      <c r="F61" s="256" t="str">
         <f ca="1">Games!O19</f>
-        <v>Bradley</v>
-      </c>
-      <c r="G61" s="247" t="e" vm="93">
+        <v>Brigham Young</v>
+      </c>
+      <c r="G61" s="259" t="e" vm="94">
         <f ca="1">_xlfn.XLOOKUP(F61,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H61" s="264">
+      <c r="H61" s="251">
         <f ca="1">Games!L45</f>
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I61" s="24"/>
       <c r="J61" s="24"/>
@@ -25443,21 +25443,21 @@
       <c r="AD61" s="25"/>
       <c r="AE61" s="56"/>
       <c r="AG61" s="24"/>
-      <c r="AH61" s="264">
+      <c r="AH61" s="251">
         <f ca="1">Games!L53</f>
-        <v>110</v>
-      </c>
-      <c r="AI61" s="249" t="e" vm="126">
+        <v>105</v>
+      </c>
+      <c r="AI61" s="249" t="e" vm="125">
         <f ca="1">_xlfn.XLOOKUP(AJ61,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AJ61" s="262" t="str">
+      <c r="AJ61" s="256" t="str">
         <f ca="1">Games!O35</f>
-        <v>Cornell</v>
+        <v>Coppin State</v>
       </c>
       <c r="AK61" s="58">
         <f ca="1">Games!L35</f>
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="AL61" s="46" t="e" vm="125">
         <f>_xlfn.XLOOKUP(AM61,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -25473,7 +25473,7 @@
       <c r="AO61" s="17"/>
     </row>
     <row r="62" spans="1:41" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="283">
+      <c r="A62" s="255">
         <f>IF($AU$5=TRUE,A58+1,"")</f>
         <v>15</v>
       </c>
@@ -25481,9 +25481,9 @@
       <c r="C62" s="38"/>
       <c r="D62" s="71"/>
       <c r="E62" s="49"/>
-      <c r="F62" s="263"/>
-      <c r="G62" s="248"/>
-      <c r="H62" s="265"/>
+      <c r="F62" s="257"/>
+      <c r="G62" s="260"/>
+      <c r="H62" s="252"/>
       <c r="I62" s="24"/>
       <c r="J62" s="24"/>
       <c r="K62" s="50"/>
@@ -25503,19 +25503,19 @@
       <c r="AD62" s="25"/>
       <c r="AE62" s="56"/>
       <c r="AG62" s="24"/>
-      <c r="AH62" s="265"/>
+      <c r="AH62" s="252"/>
       <c r="AI62" s="250"/>
-      <c r="AJ62" s="263"/>
+      <c r="AJ62" s="257"/>
       <c r="AK62" s="55"/>
       <c r="AM62" s="39"/>
       <c r="AN62" s="28"/>
-      <c r="AO62" s="287">
+      <c r="AO62" s="277">
         <f>IF($AU$5=TRUE,AO58+1,"")</f>
         <v>31</v>
       </c>
     </row>
     <row r="63" spans="1:41" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="283"/>
+      <c r="A63" s="255"/>
       <c r="B63" s="27">
         <v>10</v>
       </c>
@@ -25529,25 +25529,25 @@
       </c>
       <c r="E63" s="48">
         <f ca="1">Games!N19</f>
-        <v>113</v>
-      </c>
-      <c r="F63" s="282">
+        <v>102</v>
+      </c>
+      <c r="F63" s="276">
         <f>IF($AU$5=TRUE,F55+1,"")</f>
         <v>40</v>
       </c>
       <c r="G63" s="14"/>
       <c r="H63" s="49"/>
-      <c r="I63" s="279" t="str">
+      <c r="I63" s="265" t="str">
         <f ca="1">Games!O45</f>
-        <v>Bradley</v>
-      </c>
-      <c r="J63" s="247" t="e" vm="93">
+        <v>Bryant</v>
+      </c>
+      <c r="J63" s="259" t="e" vm="96">
         <f ca="1">_xlfn.XLOOKUP(I63,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K63" s="277">
+      <c r="K63" s="261">
         <f ca="1">Games!N58</f>
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="L63" s="25"/>
       <c r="M63" s="25"/>
@@ -25565,27 +25565,27 @@
       <c r="Z63" s="57"/>
       <c r="AA63" s="25"/>
       <c r="AD63" s="25"/>
-      <c r="AE63" s="269">
+      <c r="AE63" s="253">
         <f ca="1">Games!N62</f>
-        <v>103</v>
-      </c>
-      <c r="AF63" s="249" t="e" vm="126">
+        <v>101</v>
+      </c>
+      <c r="AF63" s="249" t="e" vm="125">
         <f ca="1">_xlfn.XLOOKUP(AG63,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG63" s="262" t="str">
+      <c r="AG63" s="256" t="str">
         <f ca="1">Games!O53</f>
-        <v>Cornell</v>
+        <v>Coppin State</v>
       </c>
       <c r="AH63" s="55"/>
       <c r="AI63" s="51"/>
-      <c r="AJ63" s="282">
+      <c r="AJ63" s="276">
         <f>IF($AU$5=TRUE,AJ55+1,"")</f>
         <v>48</v>
       </c>
       <c r="AK63" s="59">
         <f ca="1">Games!N35</f>
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="AL63" s="46" t="e" vm="126">
         <f>_xlfn.XLOOKUP(AM63,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -25598,19 +25598,19 @@
       <c r="AN63" s="27">
         <v>10</v>
       </c>
-      <c r="AO63" s="287"/>
+      <c r="AO63" s="277"/>
     </row>
     <row r="64" spans="1:41" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="16"/>
       <c r="B64" s="28"/>
       <c r="C64" s="38"/>
       <c r="D64" s="71"/>
-      <c r="F64" s="283"/>
+      <c r="F64" s="255"/>
       <c r="G64" s="15"/>
       <c r="H64" s="50"/>
-      <c r="I64" s="280"/>
-      <c r="J64" s="248"/>
-      <c r="K64" s="278"/>
+      <c r="I64" s="266"/>
+      <c r="J64" s="260"/>
+      <c r="K64" s="262"/>
       <c r="L64" s="25"/>
       <c r="M64" s="25"/>
       <c r="O64" s="25"/>
@@ -25626,11 +25626,11 @@
       <c r="Z64" s="57"/>
       <c r="AA64" s="25"/>
       <c r="AD64" s="25"/>
-      <c r="AE64" s="270"/>
+      <c r="AE64" s="254"/>
       <c r="AF64" s="250"/>
-      <c r="AG64" s="263"/>
+      <c r="AG64" s="257"/>
       <c r="AH64" s="56"/>
-      <c r="AJ64" s="283"/>
+      <c r="AJ64" s="255"/>
       <c r="AM64" s="39"/>
       <c r="AN64" s="28"/>
       <c r="AO64" s="17"/>
@@ -25650,19 +25650,19 @@
       </c>
       <c r="E65" s="46">
         <f ca="1">Games!L20</f>
-        <v>111</v>
-      </c>
-      <c r="F65" s="262" t="str">
+        <v>97</v>
+      </c>
+      <c r="F65" s="256" t="str">
         <f ca="1">Games!O20</f>
-        <v>Brown</v>
-      </c>
-      <c r="G65" s="247" t="e" vm="95">
+        <v>Bryant</v>
+      </c>
+      <c r="G65" s="259" t="e" vm="96">
         <f ca="1">_xlfn.XLOOKUP(F65,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H65" s="277">
+      <c r="H65" s="261">
         <f ca="1">Games!N45</f>
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="I65" s="25"/>
       <c r="J65" s="25"/>
@@ -25682,21 +25682,21 @@
       <c r="AA65" s="25"/>
       <c r="AD65" s="25"/>
       <c r="AG65" s="24"/>
-      <c r="AH65" s="269">
+      <c r="AH65" s="253">
         <f ca="1">Games!N53</f>
-        <v>103</v>
-      </c>
-      <c r="AI65" s="249" t="e" vm="128">
+        <v>97</v>
+      </c>
+      <c r="AI65" s="249" t="e" vm="127">
         <f ca="1">_xlfn.XLOOKUP(AJ65,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AJ65" s="262" t="str">
+      <c r="AJ65" s="256" t="str">
         <f ca="1">Games!O36</f>
-        <v>Dartmouth</v>
+        <v>Creighton</v>
       </c>
       <c r="AK65" s="58">
         <f ca="1">Games!L36</f>
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="AL65" s="46" t="e" vm="127">
         <f>_xlfn.XLOOKUP(AM65,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -25712,7 +25712,7 @@
       <c r="AO65" s="17"/>
     </row>
     <row r="66" spans="1:41" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="283">
+      <c r="A66" s="255">
         <f>IF($AU$5=TRUE,A62+1,"")</f>
         <v>16</v>
       </c>
@@ -25720,41 +25720,41 @@
       <c r="C66" s="38"/>
       <c r="D66" s="71"/>
       <c r="E66" s="49"/>
-      <c r="F66" s="263"/>
-      <c r="G66" s="248"/>
-      <c r="H66" s="278"/>
+      <c r="F66" s="257"/>
+      <c r="G66" s="260"/>
+      <c r="H66" s="262"/>
       <c r="I66" s="25"/>
       <c r="J66" s="25"/>
       <c r="L66" s="25"/>
       <c r="M66" s="25"/>
-      <c r="O66" s="261"/>
-      <c r="P66" s="261"/>
-      <c r="Q66" s="261"/>
-      <c r="R66" s="261"/>
-      <c r="S66" s="261"/>
-      <c r="T66" s="261"/>
-      <c r="U66" s="261"/>
-      <c r="V66" s="261"/>
-      <c r="W66" s="261"/>
-      <c r="X66" s="261"/>
-      <c r="Y66" s="261"/>
-      <c r="Z66" s="261"/>
-      <c r="AA66" s="261"/>
+      <c r="O66" s="292"/>
+      <c r="P66" s="292"/>
+      <c r="Q66" s="292"/>
+      <c r="R66" s="292"/>
+      <c r="S66" s="292"/>
+      <c r="T66" s="292"/>
+      <c r="U66" s="292"/>
+      <c r="V66" s="292"/>
+      <c r="W66" s="292"/>
+      <c r="X66" s="292"/>
+      <c r="Y66" s="292"/>
+      <c r="Z66" s="292"/>
+      <c r="AA66" s="292"/>
       <c r="AD66" s="25"/>
       <c r="AG66" s="24"/>
-      <c r="AH66" s="270"/>
+      <c r="AH66" s="254"/>
       <c r="AI66" s="250"/>
-      <c r="AJ66" s="263"/>
+      <c r="AJ66" s="257"/>
       <c r="AK66" s="55"/>
       <c r="AM66" s="39"/>
       <c r="AN66" s="28"/>
-      <c r="AO66" s="287">
+      <c r="AO66" s="277">
         <f>IF($AU$5=TRUE,AO62+1,"")</f>
         <v>32</v>
       </c>
     </row>
     <row r="67" spans="1:41" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="283"/>
+      <c r="A67" s="255"/>
       <c r="B67" s="27">
         <v>15</v>
       </c>
@@ -25768,7 +25768,7 @@
       </c>
       <c r="E67" s="48">
         <f ca="1">Games!N20</f>
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="F67" s="25"/>
       <c r="G67" s="25"/>
@@ -25776,25 +25776,25 @@
       <c r="J67" s="25"/>
       <c r="L67" s="25"/>
       <c r="M67" s="25"/>
-      <c r="O67" s="260"/>
-      <c r="P67" s="260"/>
-      <c r="Q67" s="260"/>
-      <c r="R67" s="260"/>
-      <c r="S67" s="260"/>
-      <c r="T67" s="260"/>
-      <c r="U67" s="260"/>
-      <c r="V67" s="260"/>
-      <c r="W67" s="260"/>
-      <c r="X67" s="260"/>
-      <c r="Y67" s="260"/>
-      <c r="Z67" s="260"/>
-      <c r="AA67" s="260"/>
+      <c r="O67" s="291"/>
+      <c r="P67" s="291"/>
+      <c r="Q67" s="291"/>
+      <c r="R67" s="291"/>
+      <c r="S67" s="291"/>
+      <c r="T67" s="291"/>
+      <c r="U67" s="291"/>
+      <c r="V67" s="291"/>
+      <c r="W67" s="291"/>
+      <c r="X67" s="291"/>
+      <c r="Y67" s="291"/>
+      <c r="Z67" s="291"/>
+      <c r="AA67" s="291"/>
       <c r="AD67" s="25"/>
       <c r="AG67" s="25"/>
       <c r="AJ67" s="24"/>
       <c r="AK67" s="59">
         <f ca="1">Games!N36</f>
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AL67" s="46" t="e" vm="128">
         <f>_xlfn.XLOOKUP(AM67,Teams!$C:$C,Teams!$E:$E,,0,1)</f>
@@ -25807,7 +25807,7 @@
       <c r="AN67" s="27">
         <v>15</v>
       </c>
-      <c r="AO67" s="287"/>
+      <c r="AO67" s="277"/>
     </row>
     <row r="68" spans="1:41" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A68" s="13"/>
@@ -25848,57 +25848,189 @@
     <row r="70" spans="1:41" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="258">
-    <mergeCell ref="AI5:AI6"/>
-    <mergeCell ref="AI9:AI10"/>
-    <mergeCell ref="AI13:AI14"/>
-    <mergeCell ref="AI17:AI18"/>
-    <mergeCell ref="AI21:AI22"/>
-    <mergeCell ref="AI25:AI26"/>
-    <mergeCell ref="AI29:AI30"/>
-    <mergeCell ref="AI33:AI34"/>
-    <mergeCell ref="AI37:AI38"/>
-    <mergeCell ref="AE7:AE8"/>
-    <mergeCell ref="AE15:AE16"/>
-    <mergeCell ref="AG11:AG12"/>
-    <mergeCell ref="AD11:AD12"/>
-    <mergeCell ref="AD19:AE20"/>
-    <mergeCell ref="Q19:Q20"/>
-    <mergeCell ref="AG23:AG24"/>
-    <mergeCell ref="AE23:AE24"/>
-    <mergeCell ref="P19:P20"/>
-    <mergeCell ref="Z19:Z20"/>
-    <mergeCell ref="AG7:AG8"/>
-    <mergeCell ref="AF23:AF24"/>
-    <mergeCell ref="AF7:AF8"/>
-    <mergeCell ref="K63:K64"/>
-    <mergeCell ref="AE31:AE32"/>
-    <mergeCell ref="N43:N44"/>
-    <mergeCell ref="T35:V35"/>
-    <mergeCell ref="AE55:AE56"/>
-    <mergeCell ref="AB43:AB44"/>
-    <mergeCell ref="AA51:AA52"/>
-    <mergeCell ref="AD43:AD44"/>
-    <mergeCell ref="O51:O52"/>
-    <mergeCell ref="U39:U40"/>
-    <mergeCell ref="P51:P52"/>
-    <mergeCell ref="Z51:Z52"/>
-    <mergeCell ref="V39:X40"/>
-    <mergeCell ref="AC43:AC44"/>
-    <mergeCell ref="AD27:AD28"/>
-    <mergeCell ref="AD59:AD60"/>
-    <mergeCell ref="U27:U28"/>
-    <mergeCell ref="AC27:AC28"/>
-    <mergeCell ref="V27:V28"/>
-    <mergeCell ref="R27:T28"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="J39:J40"/>
-    <mergeCell ref="M27:M28"/>
-    <mergeCell ref="K39:K40"/>
-    <mergeCell ref="N27:N28"/>
-    <mergeCell ref="L27:L28"/>
-    <mergeCell ref="Q51:Q52"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="L43:L44"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="AC11:AC12"/>
+    <mergeCell ref="T11:V19"/>
+    <mergeCell ref="AF15:AF16"/>
+    <mergeCell ref="O67:AA67"/>
+    <mergeCell ref="O66:AA66"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F37:F38"/>
+    <mergeCell ref="H37:H38"/>
+    <mergeCell ref="K55:K56"/>
+    <mergeCell ref="K51:L52"/>
+    <mergeCell ref="T39:T40"/>
+    <mergeCell ref="AB27:AB28"/>
+    <mergeCell ref="AA19:AA20"/>
+    <mergeCell ref="S32:W33"/>
+    <mergeCell ref="Y19:Y20"/>
+    <mergeCell ref="S31:W31"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="AC59:AC60"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="K23:K24"/>
+    <mergeCell ref="K31:K32"/>
+    <mergeCell ref="O19:O20"/>
+    <mergeCell ref="B1:AN1"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="K15:K16"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="AG15:AG16"/>
+    <mergeCell ref="AJ7:AJ8"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="S2:W2"/>
+    <mergeCell ref="AB11:AB12"/>
+    <mergeCell ref="AJ5:AJ6"/>
+    <mergeCell ref="AH5:AH6"/>
+    <mergeCell ref="AJ9:AJ10"/>
+    <mergeCell ref="AH9:AH10"/>
+    <mergeCell ref="AJ13:AJ14"/>
+    <mergeCell ref="AJ15:AJ16"/>
+    <mergeCell ref="AJ63:AJ64"/>
+    <mergeCell ref="AJ57:AJ58"/>
+    <mergeCell ref="AH65:AH66"/>
+    <mergeCell ref="AJ65:AJ66"/>
+    <mergeCell ref="AH61:AH62"/>
+    <mergeCell ref="AI41:AI42"/>
+    <mergeCell ref="AI45:AI46"/>
+    <mergeCell ref="AI49:AI50"/>
+    <mergeCell ref="AI53:AI54"/>
+    <mergeCell ref="AI57:AI58"/>
+    <mergeCell ref="AI61:AI62"/>
+    <mergeCell ref="AI65:AI66"/>
+    <mergeCell ref="AJ45:AJ46"/>
+    <mergeCell ref="AG39:AG40"/>
+    <mergeCell ref="AE63:AE64"/>
+    <mergeCell ref="AG63:AG64"/>
+    <mergeCell ref="F63:F64"/>
+    <mergeCell ref="F61:F62"/>
+    <mergeCell ref="H61:H62"/>
+    <mergeCell ref="J55:J56"/>
+    <mergeCell ref="H33:H34"/>
+    <mergeCell ref="F57:F58"/>
+    <mergeCell ref="H57:H58"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="AF63:AF64"/>
+    <mergeCell ref="AF55:AF56"/>
+    <mergeCell ref="AF47:AF48"/>
+    <mergeCell ref="G61:G62"/>
+    <mergeCell ref="M43:M44"/>
+    <mergeCell ref="Y51:Y52"/>
+    <mergeCell ref="AB59:AB60"/>
+    <mergeCell ref="G57:G58"/>
+    <mergeCell ref="G53:G54"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="K19:L20"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="G33:G34"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="J63:J64"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="I63:I64"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="AH29:AH30"/>
+    <mergeCell ref="AJ29:AJ30"/>
+    <mergeCell ref="AJ37:AJ38"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="F53:F54"/>
+    <mergeCell ref="H53:H54"/>
+    <mergeCell ref="I55:I56"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="I39:I40"/>
+    <mergeCell ref="AH45:AH46"/>
+    <mergeCell ref="AE47:AE48"/>
+    <mergeCell ref="AG59:AG60"/>
+    <mergeCell ref="AG55:AG56"/>
+    <mergeCell ref="AH57:AH58"/>
+    <mergeCell ref="I59:I60"/>
+    <mergeCell ref="M59:M60"/>
+    <mergeCell ref="N59:N60"/>
+    <mergeCell ref="AO62:AO63"/>
+    <mergeCell ref="AO66:AO67"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="AO26:AO27"/>
+    <mergeCell ref="AO30:AO31"/>
+    <mergeCell ref="AO34:AO35"/>
+    <mergeCell ref="AJ61:AJ62"/>
+    <mergeCell ref="AE39:AE40"/>
+    <mergeCell ref="AH49:AH50"/>
+    <mergeCell ref="AJ49:AJ50"/>
+    <mergeCell ref="AH53:AH54"/>
+    <mergeCell ref="AJ53:AJ54"/>
+    <mergeCell ref="AJ47:AJ48"/>
+    <mergeCell ref="AD51:AE52"/>
+    <mergeCell ref="AG47:AG48"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="AO22:AO23"/>
+    <mergeCell ref="F65:F66"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="L59:L60"/>
+    <mergeCell ref="AO50:AO51"/>
+    <mergeCell ref="AO54:AO55"/>
+    <mergeCell ref="AO58:AO59"/>
+    <mergeCell ref="AO38:AO39"/>
+    <mergeCell ref="AO42:AO43"/>
+    <mergeCell ref="AO46:AO47"/>
+    <mergeCell ref="AJ41:AJ42"/>
+    <mergeCell ref="AJ39:AJ40"/>
+    <mergeCell ref="AH41:AH42"/>
+    <mergeCell ref="AH37:AH38"/>
+    <mergeCell ref="AJ55:AJ56"/>
     <mergeCell ref="AH25:AH26"/>
     <mergeCell ref="AH33:AH34"/>
     <mergeCell ref="AG43:AG44"/>
@@ -25923,189 +26055,57 @@
     <mergeCell ref="AG27:AG28"/>
     <mergeCell ref="AG31:AG32"/>
     <mergeCell ref="AJ33:AJ34"/>
-    <mergeCell ref="AO50:AO51"/>
-    <mergeCell ref="AO54:AO55"/>
-    <mergeCell ref="AO58:AO59"/>
-    <mergeCell ref="AO38:AO39"/>
-    <mergeCell ref="AO42:AO43"/>
-    <mergeCell ref="AO46:AO47"/>
-    <mergeCell ref="AJ41:AJ42"/>
-    <mergeCell ref="AJ39:AJ40"/>
-    <mergeCell ref="AH41:AH42"/>
-    <mergeCell ref="AH37:AH38"/>
-    <mergeCell ref="AJ55:AJ56"/>
-    <mergeCell ref="AO62:AO63"/>
-    <mergeCell ref="AO66:AO67"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="F31:F32"/>
-    <mergeCell ref="F39:F40"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="F55:F56"/>
-    <mergeCell ref="AO26:AO27"/>
-    <mergeCell ref="AO30:AO31"/>
-    <mergeCell ref="AO34:AO35"/>
-    <mergeCell ref="AJ61:AJ62"/>
-    <mergeCell ref="AE39:AE40"/>
-    <mergeCell ref="AH49:AH50"/>
-    <mergeCell ref="AJ49:AJ50"/>
-    <mergeCell ref="AH53:AH54"/>
-    <mergeCell ref="AJ53:AJ54"/>
-    <mergeCell ref="AJ47:AJ48"/>
-    <mergeCell ref="AD51:AE52"/>
-    <mergeCell ref="AG47:AG48"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="AO22:AO23"/>
-    <mergeCell ref="F65:F66"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="L59:L60"/>
-    <mergeCell ref="AH29:AH30"/>
-    <mergeCell ref="AJ29:AJ30"/>
-    <mergeCell ref="AJ37:AJ38"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="F53:F54"/>
-    <mergeCell ref="H53:H54"/>
-    <mergeCell ref="I55:I56"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="I39:I40"/>
-    <mergeCell ref="AH45:AH46"/>
-    <mergeCell ref="AE47:AE48"/>
-    <mergeCell ref="AG59:AG60"/>
-    <mergeCell ref="AG55:AG56"/>
-    <mergeCell ref="AH57:AH58"/>
-    <mergeCell ref="I59:I60"/>
-    <mergeCell ref="M59:M60"/>
-    <mergeCell ref="N59:N60"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="J63:J64"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="I27:I28"/>
-    <mergeCell ref="I63:I64"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="G37:G38"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="H29:H30"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="K19:L20"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="G33:G34"/>
-    <mergeCell ref="AG39:AG40"/>
-    <mergeCell ref="AE63:AE64"/>
-    <mergeCell ref="AG63:AG64"/>
-    <mergeCell ref="F63:F64"/>
-    <mergeCell ref="F61:F62"/>
-    <mergeCell ref="H61:H62"/>
-    <mergeCell ref="J55:J56"/>
-    <mergeCell ref="H33:H34"/>
-    <mergeCell ref="F57:F58"/>
-    <mergeCell ref="H57:H58"/>
-    <mergeCell ref="H45:H46"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="AF63:AF64"/>
-    <mergeCell ref="AF55:AF56"/>
-    <mergeCell ref="AF47:AF48"/>
-    <mergeCell ref="G61:G62"/>
-    <mergeCell ref="M43:M44"/>
-    <mergeCell ref="Y51:Y52"/>
-    <mergeCell ref="AB59:AB60"/>
-    <mergeCell ref="G57:G58"/>
-    <mergeCell ref="G53:G54"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="AJ63:AJ64"/>
-    <mergeCell ref="AJ57:AJ58"/>
-    <mergeCell ref="AH65:AH66"/>
-    <mergeCell ref="AJ65:AJ66"/>
-    <mergeCell ref="AH61:AH62"/>
-    <mergeCell ref="AI41:AI42"/>
-    <mergeCell ref="AI45:AI46"/>
-    <mergeCell ref="AI49:AI50"/>
-    <mergeCell ref="AI53:AI54"/>
-    <mergeCell ref="AI57:AI58"/>
-    <mergeCell ref="AI61:AI62"/>
-    <mergeCell ref="AI65:AI66"/>
-    <mergeCell ref="AJ45:AJ46"/>
-    <mergeCell ref="B1:AN1"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="K15:K16"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="AG15:AG16"/>
-    <mergeCell ref="AJ7:AJ8"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="N11:N12"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="S2:W2"/>
-    <mergeCell ref="AB11:AB12"/>
-    <mergeCell ref="AJ5:AJ6"/>
-    <mergeCell ref="AH5:AH6"/>
-    <mergeCell ref="AJ9:AJ10"/>
-    <mergeCell ref="AH9:AH10"/>
-    <mergeCell ref="AJ13:AJ14"/>
-    <mergeCell ref="AJ15:AJ16"/>
-    <mergeCell ref="M11:M12"/>
-    <mergeCell ref="AC11:AC12"/>
-    <mergeCell ref="T11:V19"/>
-    <mergeCell ref="AF15:AF16"/>
-    <mergeCell ref="O67:AA67"/>
-    <mergeCell ref="O66:AA66"/>
-    <mergeCell ref="F33:F34"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="F37:F38"/>
-    <mergeCell ref="H37:H38"/>
-    <mergeCell ref="K55:K56"/>
-    <mergeCell ref="K51:L52"/>
-    <mergeCell ref="T39:T40"/>
-    <mergeCell ref="AB27:AB28"/>
-    <mergeCell ref="AA19:AA20"/>
-    <mergeCell ref="S32:W33"/>
-    <mergeCell ref="Y19:Y20"/>
-    <mergeCell ref="S31:W31"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="AC59:AC60"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="K23:K24"/>
-    <mergeCell ref="K31:K32"/>
-    <mergeCell ref="O19:O20"/>
+    <mergeCell ref="AD27:AD28"/>
+    <mergeCell ref="AD59:AD60"/>
+    <mergeCell ref="U27:U28"/>
+    <mergeCell ref="AC27:AC28"/>
+    <mergeCell ref="V27:V28"/>
+    <mergeCell ref="R27:T28"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="J39:J40"/>
+    <mergeCell ref="M27:M28"/>
+    <mergeCell ref="K39:K40"/>
+    <mergeCell ref="N27:N28"/>
+    <mergeCell ref="L27:L28"/>
+    <mergeCell ref="Q51:Q52"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="L43:L44"/>
+    <mergeCell ref="K63:K64"/>
+    <mergeCell ref="AE31:AE32"/>
+    <mergeCell ref="N43:N44"/>
+    <mergeCell ref="T35:V35"/>
+    <mergeCell ref="AE55:AE56"/>
+    <mergeCell ref="AB43:AB44"/>
+    <mergeCell ref="AA51:AA52"/>
+    <mergeCell ref="AD43:AD44"/>
+    <mergeCell ref="O51:O52"/>
+    <mergeCell ref="U39:U40"/>
+    <mergeCell ref="P51:P52"/>
+    <mergeCell ref="Z51:Z52"/>
+    <mergeCell ref="V39:X40"/>
+    <mergeCell ref="AC43:AC44"/>
+    <mergeCell ref="AE7:AE8"/>
+    <mergeCell ref="AE15:AE16"/>
+    <mergeCell ref="AG11:AG12"/>
+    <mergeCell ref="AD11:AD12"/>
+    <mergeCell ref="AD19:AE20"/>
+    <mergeCell ref="Q19:Q20"/>
+    <mergeCell ref="AG23:AG24"/>
+    <mergeCell ref="AE23:AE24"/>
+    <mergeCell ref="P19:P20"/>
+    <mergeCell ref="Z19:Z20"/>
+    <mergeCell ref="AG7:AG8"/>
+    <mergeCell ref="AF23:AF24"/>
+    <mergeCell ref="AF7:AF8"/>
+    <mergeCell ref="AI5:AI6"/>
+    <mergeCell ref="AI9:AI10"/>
+    <mergeCell ref="AI13:AI14"/>
+    <mergeCell ref="AI17:AI18"/>
+    <mergeCell ref="AI21:AI22"/>
+    <mergeCell ref="AI25:AI26"/>
+    <mergeCell ref="AI29:AI30"/>
+    <mergeCell ref="AI33:AI34"/>
+    <mergeCell ref="AI37:AI38"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <dataValidations disablePrompts="1" count="1">
